--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -1523,13 +1523,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.668634560185</v>
+        <v>46079.83530122685</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.54858754629</v>
+        <v>46092.71525421296</v>
       </c>
       <c r="D4" s="5">
-        <v>46128.42978174768</v>
+        <v>46128.59644841435</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1572,13 +1572,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.66863482639</v>
+        <v>46079.835301493054</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.548555138885</v>
+        <v>46092.715221805556</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.548588645834</v>
+        <v>46092.715255312505</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1637,13 +1637,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.66863506944</v>
+        <v>46079.83530173611</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.54855576389</v>
+        <v>46092.71522243056</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.548587997684</v>
+        <v>46092.71525466435</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1702,13 +1702,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.66863528935</v>
+        <v>46079.835301956016</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.54855623843</v>
+        <v>46092.71522290509</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.54858858796</v>
+        <v>46092.71525525463</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1767,13 +1767,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.66863550926</v>
+        <v>46079.835302175925</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.548556724534</v>
+        <v>46092.715223391206</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.43571546296</v>
+        <v>46128.602382129626</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1832,13 +1832,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.66863571759</v>
+        <v>46079.835302384265</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.54855746528</v>
+        <v>46092.71522413194</v>
       </c>
       <c r="D9" s="8">
-        <v>46128.42986638889</v>
+        <v>46128.596533055555</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1897,11 +1897,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.6686359375</v>
+        <v>46079.835302604166</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46142.494600081016</v>
+        <v>46142.66126674769</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1944,13 +1944,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.66863619213</v>
+        <v>46079.835302858795</v>
       </c>
       <c r="C11" s="8">
-        <v>46142.4945922801</v>
+        <v>46142.661258946755</v>
       </c>
       <c r="D11" s="8">
-        <v>46142.494593958334</v>
+        <v>46142.661260625</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -2009,11 +2009,11 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.66863646991</v>
+        <v>46079.83530313657</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46133.41044717593</v>
+        <v>46133.57711384259</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2072,13 +2072,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46079.668636689814</v>
+        <v>46079.83530335648</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.34823659722</v>
+        <v>46114.51490326389</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.34825142361</v>
+        <v>46114.51491809028</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2125,13 +2125,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46079.668634594906</v>
+        <v>46079.83530126157</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.347688657406</v>
+        <v>46114.51435532408</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.34770583334</v>
+        <v>46114.5143725</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2190,13 +2190,13 @@
         <v>66</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.66863526621</v>
+        <v>46079.83530193287</v>
       </c>
       <c r="C15" s="8">
-        <v>46111.62614576389</v>
+        <v>46111.792812430554</v>
       </c>
       <c r="D15" s="8">
-        <v>46111.62616248842</v>
+        <v>46111.79282915509</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>67</v>
@@ -2255,13 +2255,13 @@
         <v>69</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.66863559028</v>
+        <v>46079.83530225694</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.34779292824</v>
+        <v>46114.51445959491</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.347810555555</v>
+        <v>46114.51447722223</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>70</v>
@@ -2320,13 +2320,13 @@
         <v>72</v>
       </c>
       <c r="B17" s="8">
-        <v>46080.34358465278</v>
+        <v>46080.51025131944</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34815204861</v>
+        <v>46114.51481871528</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.34816729167</v>
+        <v>46114.51483395833</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>73</v>
@@ -2385,13 +2385,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.668635891205</v>
+        <v>46079.83530255787</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.348217025465</v>
+        <v>46114.51488369213</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.34823753472</v>
+        <v>46114.51490420139</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2450,13 +2450,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.668636180555</v>
+        <v>46079.83530284722</v>
       </c>
       <c r="C19" s="8">
-        <v>46128.26519445602</v>
+        <v>46128.431861122684</v>
       </c>
       <c r="D19" s="8">
-        <v>46128.26520855324</v>
+        <v>46128.4318752199</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2503,13 +2503,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.66863646991</v>
+        <v>46079.83530313657</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3773302662</v>
+        <v>46097.54399693287</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.62616730324</v>
+        <v>46111.79283396991</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2568,13 +2568,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.66863677083</v>
+        <v>46079.8353034375</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.34827811342</v>
+        <v>46114.514944780094</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.3482946875</v>
+        <v>46114.514961354165</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2633,13 +2633,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.668637083334</v>
+        <v>46079.83530375</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.34829836806</v>
+        <v>46114.51496503472</v>
       </c>
       <c r="D22" s="5">
-        <v>46142.494598923615</v>
+        <v>46142.66126559028</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2698,13 +2698,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.66863738426</v>
+        <v>46079.835304050925</v>
       </c>
       <c r="C23" s="8">
-        <v>46128.26517543981</v>
+        <v>46128.43184210648</v>
       </c>
       <c r="D23" s="8">
-        <v>46128.834950358796</v>
+        <v>46129.00161702547</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2763,13 +2763,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.668634560185</v>
+        <v>46079.83530122685</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.598931064815</v>
+        <v>46114.765597731486</v>
       </c>
       <c r="D24" s="5">
-        <v>46114.59894895833</v>
+        <v>46114.765615625</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2828,13 +2828,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.70764284722</v>
+        <v>46079.87430951389</v>
       </c>
       <c r="C25" s="8">
-        <v>46114.34837186342</v>
+        <v>46114.515038530095</v>
       </c>
       <c r="D25" s="8">
-        <v>46114.348401828705</v>
+        <v>46114.51506849537</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>102</v>
@@ -2893,13 +2893,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46080.34373289352</v>
+        <v>46080.51039956018</v>
       </c>
       <c r="C26" s="5">
-        <v>46114.34842267361</v>
+        <v>46114.515089340275</v>
       </c>
       <c r="D26" s="5">
-        <v>46158.82912270833</v>
+        <v>46158.995789374996</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2958,11 +2958,11 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.668634918984</v>
+        <v>46079.83530158565</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46158.82588434027</v>
+        <v>46158.992551006944</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -3005,11 +3005,11 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.66863519676</v>
+        <v>46079.83530186342</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.68161929398</v>
+        <v>46169.848285960645</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -3068,13 +3068,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.668635462964</v>
+        <v>46079.83530212963</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.37739233796</v>
+        <v>46097.544059004635</v>
       </c>
       <c r="D29" s="8">
-        <v>46169.68174571759</v>
+        <v>46169.848412384265</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3129,11 +3129,11 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.66863569444</v>
+        <v>46079.83530236111</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.681722361114</v>
+        <v>46169.84838902778</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3188,11 +3188,11 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.668636030096</v>
+        <v>46079.83530269676</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46182.512565682875</v>
+        <v>46182.67923234953</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3251,13 +3251,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.668636284725</v>
+        <v>46079.83530295139</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.512557939815</v>
+        <v>46182.67922460648</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.51255994213</v>
+        <v>46182.6792266088</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3312,11 +3312,11 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.66863652778</v>
+        <v>46079.83530319444</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46182.51256512731</v>
+        <v>46182.67923179398</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3371,11 +3371,11 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.66863457176</v>
+        <v>46079.835301238425</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.68166318287</v>
+        <v>46169.84832984954</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3434,13 +3434,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.66863482639</v>
+        <v>46079.835301493054</v>
       </c>
       <c r="C35" s="8">
-        <v>46114.59961186342</v>
+        <v>46114.76627853009</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.68181603009</v>
+        <v>46169.84848269676</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3495,11 +3495,11 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.66863512732</v>
+        <v>46079.83530179398</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.68179884259</v>
+        <v>46169.84846550926</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3554,13 +3554,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.668635486116</v>
+        <v>46079.83530215277</v>
       </c>
       <c r="C37" s="8">
-        <v>46114.65071625</v>
+        <v>46114.81738291666</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.681829548615</v>
+        <v>46169.84849621527</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3615,11 +3615,11 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46079.66863675926</v>
+        <v>46079.83530342593</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.68167704861</v>
+        <v>46169.848343715275</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3678,11 +3678,11 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46079.668637002316</v>
+        <v>46079.83530366898</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46169.681862592595</v>
+        <v>46169.84852925926</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3737,11 +3737,11 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.66863418982</v>
+        <v>46079.83530085648</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.68189270834</v>
+        <v>46169.848559375</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3796,13 +3796,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.668635752314</v>
+        <v>46079.835302418986</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.59903686342</v>
+        <v>46114.765703530094</v>
       </c>
       <c r="D41" s="8">
-        <v>46147.026725324075</v>
+        <v>46147.193391990746</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3861,13 +3861,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.668636030096</v>
+        <v>46079.83530269676</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.59897114584</v>
+        <v>46114.765637812496</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.598972430555</v>
+        <v>46114.765639097226</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3922,13 +3922,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.668636296294</v>
+        <v>46079.835302962965</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.599022407405</v>
+        <v>46114.76568907408</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.59902407408</v>
+        <v>46114.765690740736</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3983,13 +3983,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.707824467594</v>
+        <v>46079.87449113426</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.59944146991</v>
+        <v>46114.76610813657</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.59945268519</v>
+        <v>46114.76611935185</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4048,13 +4048,13 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.70790026621</v>
+        <v>46079.87456693287</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.59938703704</v>
+        <v>46114.7660537037</v>
       </c>
       <c r="D45" s="8">
-        <v>46114.599388206014</v>
+        <v>46114.766054872685</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4109,13 +4109,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.70800302083</v>
+        <v>46079.8746696875</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.59942802083</v>
+        <v>46114.7660946875</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.599429814814</v>
+        <v>46114.766096481486</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4170,11 +4170,11 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.668636585644</v>
+        <v>46079.835303252315</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46127.52115996528</v>
+        <v>46127.68782663194</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4219,13 +4219,13 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.668636863425</v>
+        <v>46079.8353035301</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.62879984954</v>
+        <v>46114.7954665162</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.6288166088</v>
+        <v>46114.79548327546</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4284,13 +4284,13 @@
         <v>178</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.668634016205</v>
+        <v>46079.83530068287</v>
       </c>
       <c r="C49" s="8">
-        <v>46127.521092986106</v>
+        <v>46127.68775965278</v>
       </c>
       <c r="D49" s="8">
-        <v>46156.03380072917</v>
+        <v>46156.20046739583</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>179</v>
@@ -4349,13 +4349,13 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46087.46219618055</v>
+        <v>46087.628862847225</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.521146377316</v>
+        <v>46127.68781304398</v>
       </c>
       <c r="D50" s="5">
-        <v>46158.82925711806</v>
+        <v>46158.99592378472</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>183</v>
@@ -4414,11 +4414,11 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46087.46223626158</v>
+        <v>46087.62890292824</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46127.5235468287</v>
+        <v>46127.69021349537</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4477,11 +4477,11 @@
         <v>190</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.66863438657</v>
+        <v>46079.835301053245</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46080.412538530094</v>
+        <v>46080.57920519676</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4530,11 +4530,11 @@
         <v>193</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.66863467592</v>
+        <v>46079.835301342595</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46149.02519299768</v>
+        <v>46149.19185966435</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>194</v>
@@ -4593,11 +4593,11 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.668634953705</v>
+        <v>46079.83530162037</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46151.02536006944</v>
+        <v>46151.19202673611</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4656,11 +4656,11 @@
         <v>203</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.6686352199</v>
+        <v>46079.835301886575</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46080.41253865741</v>
+        <v>46080.57920532407</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>204</v>
@@ -4709,11 +4709,11 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.668635497685</v>
+        <v>46079.835302164356</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46162.00428087963</v>
+        <v>46162.1709475463</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>205</v>
@@ -4772,11 +4772,11 @@
         <v>210</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.668635752314</v>
+        <v>46079.835302418986</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46183.00924875</v>
+        <v>46183.175915416665</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>211</v>
@@ -4835,11 +4835,11 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.66863600694</v>
+        <v>46079.835302673615</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46185.03823997686</v>
+        <v>46185.204906643514</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4898,11 +4898,11 @@
         <v>218</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.668636250004</v>
+        <v>46079.83530291667</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46158.82918858796</v>
+        <v>46158.99585525463</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>191</v>
@@ -4951,11 +4951,11 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.66863559028</v>
+        <v>46079.83530225694</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46090.637920486115</v>
+        <v>46090.80458715278</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -5014,11 +5014,11 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.66863518518</v>
+        <v>46079.835301851854</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46090.6379175926</v>
+        <v>46090.804584259255</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>56</v>
@@ -5077,11 +5077,11 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.7092312037</v>
+        <v>46079.87589787037</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46114.59944542824</v>
+        <v>46114.766112094905</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5140,11 +5140,11 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.66863652778</v>
+        <v>46079.83530319444</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46158.82579047454</v>
+        <v>46158.992457141205</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5203,11 +5203,11 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.66863596065</v>
+        <v>46079.83530262731</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46114.650739375</v>
+        <v>46114.817406041664</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5266,11 +5266,11 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.668636296294</v>
+        <v>46079.835302962965</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46158.8292571412</v>
+        <v>46158.99592380787</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5319,11 +5319,11 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46079.66863662037</v>
+        <v>46079.83530328704</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46158.82925702546</v>
+        <v>46158.99592369213</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>217</v>
@@ -5382,11 +5382,11 @@
         <v>239</v>
       </c>
       <c r="B67" s="8">
-        <v>46079.66863695602</v>
+        <v>46079.83530362268</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46127.52116150463</v>
+        <v>46127.6878281713</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>240</v>
@@ -5445,11 +5445,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46079.66863731481</v>
+        <v>46079.83530398148</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46127.52116212963</v>
+        <v>46127.6878287963</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5508,11 +5508,11 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46079.668637627314</v>
+        <v>46079.835304293985</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46127.52116265046</v>
+        <v>46127.68782931713</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>248</v>
@@ -5571,11 +5571,11 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46080.32605201389</v>
+        <v>46080.49271868056</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46127.52116314815</v>
+        <v>46127.687829814815</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>251</v>
@@ -5634,11 +5634,11 @@
         <v>253</v>
       </c>
       <c r="B71" s="8">
-        <v>46079.668637939816</v>
+        <v>46079.83530460648</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46158.829257060184</v>
+        <v>46158.99592372685</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>188</v>
@@ -5697,11 +5697,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46079.66863826389</v>
+        <v>46079.83530493056</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46090.63800759259</v>
+        <v>46090.804674259256</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>257</v>
@@ -5760,11 +5760,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46079.66863478009</v>
+        <v>46079.83530144676</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46090.51004356482</v>
+        <v>46090.67671023148</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5807,11 +5807,11 @@
         <v>262</v>
       </c>
       <c r="B74" s="5">
-        <v>46079.66863515046</v>
+        <v>46079.83530181713</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46090.63806557871</v>
+        <v>46090.80473224537</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>263</v>
@@ -5868,11 +5868,11 @@
         <v>265</v>
       </c>
       <c r="B75" s="8">
-        <v>46079.668635740745</v>
+        <v>46079.8353024074</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46097.47623357639</v>
+        <v>46097.64290024305</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>57</v>
@@ -5931,11 +5931,11 @@
         <v>268</v>
       </c>
       <c r="B76" s="5">
-        <v>46079.668636030096</v>
+        <v>46079.83530269676</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.63820487268</v>
+        <v>46090.80487153935</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>269</v>
@@ -5994,11 +5994,11 @@
         <v>271</v>
       </c>
       <c r="B77" s="8">
-        <v>46079.66863640046</v>
+        <v>46079.83530306713</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46090.63829269676</v>
+        <v>46090.80495936342</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>272</v>
@@ -6057,11 +6057,11 @@
         <v>274</v>
       </c>
       <c r="B78" s="5">
-        <v>46079.66863666667</v>
+        <v>46079.83530333333</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46090.51001115741</v>
+        <v>46090.67667782407</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>275</v>
@@ -6104,11 +6104,11 @@
         <v>277</v>
       </c>
       <c r="B79" s="8">
-        <v>46079.66863696759</v>
+        <v>46079.83530363426</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.63836675926</v>
+        <v>46090.805033425924</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>278</v>
@@ -6167,11 +6167,11 @@
         <v>281</v>
       </c>
       <c r="B80" s="5">
-        <v>46079.66863729167</v>
+        <v>46079.83530395833</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.348227361115</v>
+        <v>46114.51489402778</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>282</v>
@@ -6230,11 +6230,11 @@
         <v>284</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.507380740746</v>
+        <v>46090.6740474074</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.51155083333</v>
+        <v>46090.6782175</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>285</v>
@@ -6283,11 +6283,11 @@
         <v>287</v>
       </c>
       <c r="B82" s="5">
-        <v>46090.50756469907</v>
+        <v>46090.674231365745</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46090.638442048614</v>
+        <v>46090.80510871528</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>288</v>
@@ -6346,11 +6346,11 @@
         <v>290</v>
       </c>
       <c r="B83" s="8">
-        <v>46090.50777542824</v>
+        <v>46090.67444209491</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46090.63843890047</v>
+        <v>46090.80510556713</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>291</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -392,6 +392,9 @@
     <t>Generación OC Tableros  ot 4265 - ot 4266,Fabricación Tablero  ot 4265 - ot 4266</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1213459189153331</t>
   </si>
   <si>
@@ -663,9 +666,6 @@
   </si>
   <si>
     <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213459189207075</t>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46182.67923234953</v>
+        <v>46190.18467553241</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3242,13 +3242,13 @@
       <c r="T31" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="U31" s="10" t="s">
-        <v>59</v>
+      <c r="U31" s="12" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46079.83530295139</v>
@@ -3260,7 +3260,7 @@
         <v>46182.6792266088</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3293,7 +3293,7 @@
         <v>90</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3309,7 +3309,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46079.83530319444</v>
@@ -3319,7 +3319,7 @@
         <v>46182.67923179398</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3349,10 +3349,10 @@
         <v>121</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3368,7 +3368,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46079.835301238425</v>
@@ -3378,7 +3378,7 @@
         <v>46169.84832984954</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3408,7 +3408,7 @@
         <v>107</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>107</v>
@@ -3431,7 +3431,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B35" s="8">
         <v>46079.835301493054</v>
@@ -3443,7 +3443,7 @@
         <v>46169.84848269676</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3470,13 +3470,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>87</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3492,7 +3492,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46079.83530179398</v>
@@ -3502,7 +3502,7 @@
         <v>46169.84846550926</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3529,13 +3529,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="8">
         <v>46079.83530215277</v>
@@ -3563,7 +3563,7 @@
         <v>46169.84849621527</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -3590,13 +3590,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3612,7 +3612,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46079.83530342593</v>
@@ -3622,7 +3622,7 @@
         <v>46169.848343715275</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3652,7 +3652,7 @@
         <v>107</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>107</v>
@@ -3675,7 +3675,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>46079.83530366898</v>
@@ -3685,7 +3685,7 @@
         <v>46169.84852925926</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
@@ -3712,13 +3712,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>93</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46079.83530085648</v>
@@ -3744,7 +3744,7 @@
         <v>46169.848559375</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -3771,13 +3771,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46079.835302418986</v>
@@ -3805,16 +3805,16 @@
         <v>46147.193391990746</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I41" s="8">
         <v>46097</v>
@@ -3835,7 +3835,7 @@
         <v>107</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>107</v>
@@ -3858,7 +3858,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46079.83530269676</v>
@@ -3870,16 +3870,16 @@
         <v>46114.765639097226</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I42" s="5">
         <v>46097</v>
@@ -3897,13 +3897,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3919,7 +3919,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46079.835302962965</v>
@@ -3931,16 +3931,16 @@
         <v>46114.765690740736</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I43" s="8">
         <v>46115</v>
@@ -3958,13 +3958,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3980,7 +3980,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46079.87449113426</v>
@@ -3992,16 +3992,16 @@
         <v>46114.76611935185</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I44" s="5">
         <v>46097</v>
@@ -4022,7 +4022,7 @@
         <v>107</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>107</v>
@@ -4045,7 +4045,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46079.87456693287</v>
@@ -4057,16 +4057,16 @@
         <v>46114.766054872685</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I45" s="8">
         <v>46097</v>
@@ -4084,13 +4084,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>102</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4106,7 +4106,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46079.8746696875</v>
@@ -4118,16 +4118,16 @@
         <v>46114.766096481486</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I46" s="5">
         <v>46126</v>
@@ -4145,13 +4145,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46079.835303252315</v>
@@ -4177,7 +4177,7 @@
         <v>46127.68782663194</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>25</v>
@@ -4201,7 +4201,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>26</v>
@@ -4216,7 +4216,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46079.8353035301</v>
@@ -4228,16 +4228,16 @@
         <v>46114.79548327546</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I48" s="5">
         <v>46093</v>
@@ -4255,13 +4255,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>70</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="5">
         <v>46093</v>
@@ -4281,7 +4281,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46079.83530068287</v>
@@ -4293,16 +4293,16 @@
         <v>46156.20046739583</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I49" s="8">
         <v>46149</v>
@@ -4320,13 +4320,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="8">
         <v>46149</v>
@@ -4346,7 +4346,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46087.628862847225</v>
@@ -4358,16 +4358,16 @@
         <v>46158.99592378472</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I50" s="5">
         <v>46156</v>
@@ -4385,13 +4385,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q50" s="5">
         <v>46156</v>
@@ -4411,7 +4411,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B51" s="8">
         <v>46087.62890292824</v>
@@ -4421,16 +4421,16 @@
         <v>46127.69021349537</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I51" s="8">
         <v>46243</v>
@@ -4448,13 +4448,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="8">
         <v>46243</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46079.835301053245</v>
@@ -4484,7 +4484,7 @@
         <v>46080.57920519676</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4508,7 +4508,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4527,7 +4527,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46079.835301342595</v>
@@ -4537,16 +4537,16 @@
         <v>46149.19185966435</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I53" s="8">
         <v>46147</v>
@@ -4564,13 +4564,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q53" s="8">
         <v>46147</v>
@@ -4590,7 +4590,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46079.83530162037</v>
@@ -4600,16 +4600,16 @@
         <v>46151.19202673611</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I54" s="5">
         <v>46149</v>
@@ -4627,13 +4627,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q54" s="5">
         <v>46149</v>
@@ -4653,7 +4653,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B55" s="8">
         <v>46079.835301886575</v>
@@ -4663,7 +4663,7 @@
         <v>46080.57920532407</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4687,7 +4687,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4706,7 +4706,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46079.835302164356</v>
@@ -4716,16 +4716,16 @@
         <v>46162.1709475463</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I56" s="5">
         <v>46153</v>
@@ -4743,13 +4743,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="5">
         <v>46153</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B57" s="8">
         <v>46079.835302418986</v>
@@ -4779,16 +4779,16 @@
         <v>46183.175915416665</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I57" s="8">
         <v>46162</v>
@@ -4806,13 +4806,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q57" s="8">
         <v>46162</v>
@@ -4827,7 +4827,7 @@
         <v>58</v>
       </c>
       <c r="U57" s="12" t="s">
-        <v>214</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4842,16 +4842,16 @@
         <v>46185.204906643514</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I58" s="5">
         <v>46191</v>
@@ -4869,7 +4869,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>216</v>
@@ -4890,7 +4890,7 @@
         <v>58</v>
       </c>
       <c r="U58" s="12" t="s">
-        <v>214</v>
+        <v>123</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4905,7 +4905,7 @@
         <v>46158.99585525463</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -4964,10 +4964,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I60" s="5">
         <v>46212</v>
@@ -4985,7 +4985,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>118</v>
@@ -5027,10 +5027,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I61" s="8">
         <v>46198</v>
@@ -5048,10 +5048,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>224</v>
@@ -5090,10 +5090,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I62" s="5">
         <v>46204</v>
@@ -5111,10 +5111,10 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>227</v>
@@ -5153,10 +5153,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I63" s="8">
         <v>46149</v>
@@ -5174,10 +5174,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>230</v>
@@ -5216,10 +5216,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I64" s="5">
         <v>46234</v>
@@ -5237,10 +5237,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>233</v>
@@ -5356,7 +5356,7 @@
         <v>235</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>238</v>
@@ -5641,7 +5641,7 @@
         <v>46158.99592372685</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5734,7 +5734,7 @@
         <v>235</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>258</v>
@@ -5944,10 +5944,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I76" s="5">
         <v>46251</v>
@@ -6007,10 +6007,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I77" s="8">
         <v>46252</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -4776,7 +4776,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46183.175915416665</v>
+        <v>46190.25036958333</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>212</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -4776,7 +4776,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46190.25036958333</v>
+        <v>46191.1671537963</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>212</v>
@@ -4826,8 +4826,8 @@
       <c r="T57" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="U57" s="12" t="s">
-        <v>123</v>
+      <c r="U57" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -4479,9 +4479,11 @@
       <c r="B52" s="5">
         <v>46079.835301053245</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46191.79630699074</v>
+      </c>
       <c r="D52" s="5">
-        <v>46080.57920519676</v>
+        <v>46191.79631972223</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4516,10 +4518,10 @@
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
       <c r="S52" s="6">
-        <v>0</v>
-      </c>
-      <c r="T52" s="11" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="T52" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U52" s="10" t="s">
         <v>59</v>
@@ -4532,9 +4534,11 @@
       <c r="B53" s="8">
         <v>46079.835301342595</v>
       </c>
-      <c r="C53" s="9"/>
+      <c r="C53" s="8">
+        <v>46191.79629</v>
+      </c>
       <c r="D53" s="8">
-        <v>46149.19185966435</v>
+        <v>46191.79630796296</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>195</v>
@@ -4579,10 +4583,10 @@
         <v>46148</v>
       </c>
       <c r="S53" s="9">
-        <v>0</v>
-      </c>
-      <c r="T53" s="12" t="s">
-        <v>85</v>
+        <v>1</v>
+      </c>
+      <c r="T53" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U53" s="11" t="s">
         <v>32</v>
@@ -4595,9 +4599,11 @@
       <c r="B54" s="5">
         <v>46079.83530162037</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46191.79562175926</v>
+      </c>
       <c r="D54" s="5">
-        <v>46151.19202673611</v>
+        <v>46191.7963069213</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4642,10 +4648,10 @@
         <v>46150</v>
       </c>
       <c r="S54" s="6">
-        <v>0</v>
-      </c>
-      <c r="T54" s="11" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="T54" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="U54" s="11" t="s">
         <v>32</v>
@@ -4713,7 +4719,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46162.1709475463</v>
+        <v>46191.795639421296</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4760,8 +4766,8 @@
       <c r="S56" s="6">
         <v>0</v>
       </c>
-      <c r="T56" s="11" t="s">
-        <v>58</v>
+      <c r="T56" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="U56" s="11" t="s">
         <v>32</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -2456,7 +2456,7 @@
         <v>46128.431861122684</v>
       </c>
       <c r="D19" s="8">
-        <v>46128.4318752199</v>
+        <v>46191.801118738425</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2765,11 +2765,9 @@
       <c r="B24" s="5">
         <v>46079.83530122685</v>
       </c>
-      <c r="C24" s="5">
-        <v>46114.765597731486</v>
-      </c>
+      <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46114.765615625</v>
+        <v>46191.80108803241</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2831,10 +2829,10 @@
         <v>46079.87430951389</v>
       </c>
       <c r="C25" s="8">
-        <v>46114.515038530095</v>
+        <v>46191.80111393519</v>
       </c>
       <c r="D25" s="8">
-        <v>46114.51506849537</v>
+        <v>46191.801115636576</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>102</v>
@@ -2896,10 +2894,10 @@
         <v>46080.51039956018</v>
       </c>
       <c r="C26" s="5">
-        <v>46114.515089340275</v>
+        <v>46191.801125949074</v>
       </c>
       <c r="D26" s="5">
-        <v>46158.995789374996</v>
+        <v>46191.80112726852</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2962,7 +2960,7 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46158.992551006944</v>
+        <v>46191.801205324075</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -3798,11 +3796,9 @@
       <c r="B41" s="8">
         <v>46079.835302418986</v>
       </c>
-      <c r="C41" s="8">
-        <v>46114.765703530094</v>
-      </c>
+      <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46147.193391990746</v>
+        <v>46191.801202013885</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3867,7 +3863,7 @@
         <v>46114.765637812496</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.765639097226</v>
+        <v>46191.80109314815</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -4054,7 +4050,7 @@
         <v>46114.7660537037</v>
       </c>
       <c r="D45" s="8">
-        <v>46114.766054872685</v>
+        <v>46191.80111972222</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4479,11 +4475,9 @@
       <c r="B52" s="5">
         <v>46079.835301053245</v>
       </c>
-      <c r="C52" s="5">
-        <v>46191.79630699074</v>
-      </c>
+      <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46191.79631972223</v>
+        <v>46191.80128876158</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4534,11 +4528,9 @@
       <c r="B53" s="8">
         <v>46079.835301342595</v>
       </c>
-      <c r="C53" s="8">
-        <v>46191.79629</v>
-      </c>
+      <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46191.79630796296</v>
+        <v>46191.80125251158</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>195</v>
@@ -4599,11 +4591,9 @@
       <c r="B54" s="5">
         <v>46079.83530162037</v>
       </c>
-      <c r="C54" s="5">
-        <v>46191.79562175926</v>
-      </c>
+      <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46191.7963069213</v>
+        <v>46191.80126277778</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4719,7 +4709,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46191.795639421296</v>
+        <v>46191.80126917824</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="292">
   <si>
     <t>50001518 - EQ. CHAPARRAL</t>
   </si>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46191.801205324075</v>
+        <v>46191.87501525463</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2995,7 +2995,9 @@
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
+      <c r="T27" s="12" t="s">
+        <v>85</v>
+      </c>
       <c r="U27" s="9"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3005,9 +3007,11 @@
       <c r="B28" s="5">
         <v>46079.83530186342</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46191.874819687495</v>
+      </c>
       <c r="D28" s="5">
-        <v>46169.848285960645</v>
+        <v>46191.874831574074</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -3052,10 +3056,10 @@
         <v>46211</v>
       </c>
       <c r="S28" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="T28" s="11" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="T28" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U28" s="10" t="s">
         <v>59</v>
@@ -3129,9 +3133,11 @@
       <c r="B30" s="5">
         <v>46079.83530236111</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="5">
+        <v>46191.87480532407</v>
+      </c>
       <c r="D30" s="5">
-        <v>46169.84838902778</v>
+        <v>46191.87480704861</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3188,9 +3194,11 @@
       <c r="B31" s="8">
         <v>46079.83530269676</v>
       </c>
-      <c r="C31" s="9"/>
+      <c r="C31" s="8">
+        <v>46191.874711435186</v>
+      </c>
       <c r="D31" s="8">
-        <v>46190.18467553241</v>
+        <v>46191.8747227662</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3235,10 +3243,10 @@
         <v>46197</v>
       </c>
       <c r="S31" s="9">
-        <v>0</v>
-      </c>
-      <c r="T31" s="11" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="T31" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U31" s="12" t="s">
         <v>123</v>
@@ -3312,9 +3320,11 @@
       <c r="B33" s="8">
         <v>46079.83530319444</v>
       </c>
-      <c r="C33" s="9"/>
+      <c r="C33" s="8">
+        <v>46191.8746965162</v>
+      </c>
       <c r="D33" s="8">
-        <v>46182.67923179398</v>
+        <v>46191.874698125</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3371,9 +3381,11 @@
       <c r="B34" s="5">
         <v>46079.835301238425</v>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="5">
+        <v>46191.87458894676</v>
+      </c>
       <c r="D34" s="5">
-        <v>46169.84832984954</v>
+        <v>46191.874603414355</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3418,10 +3430,10 @@
         <v>46090</v>
       </c>
       <c r="S34" s="6">
-        <v>0.66</v>
-      </c>
-      <c r="T34" s="10" t="s">
-        <v>31</v>
+        <v>1</v>
+      </c>
+      <c r="T34" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="U34" s="11" t="s">
         <v>32</v>
@@ -3495,9 +3507,11 @@
       <c r="B36" s="5">
         <v>46079.83530179398</v>
       </c>
-      <c r="C36" s="6"/>
+      <c r="C36" s="5">
+        <v>46191.87457479167</v>
+      </c>
       <c r="D36" s="5">
-        <v>46169.84846550926</v>
+        <v>46191.87457655092</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3615,9 +3629,11 @@
       <c r="B38" s="5">
         <v>46079.83530342593</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46191.8749955324</v>
+      </c>
       <c r="D38" s="5">
-        <v>46169.848343715275</v>
+        <v>46191.875013136574</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3662,10 +3678,10 @@
         <v>46148</v>
       </c>
       <c r="S38" s="6">
-        <v>0</v>
-      </c>
-      <c r="T38" s="12" t="s">
-        <v>85</v>
+        <v>1</v>
+      </c>
+      <c r="T38" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U38" s="11" t="s">
         <v>32</v>
@@ -3678,9 +3694,11 @@
       <c r="B39" s="8">
         <v>46079.83530366898</v>
       </c>
-      <c r="C39" s="9"/>
+      <c r="C39" s="8">
+        <v>46191.87447350695</v>
+      </c>
       <c r="D39" s="8">
-        <v>46169.84852925926</v>
+        <v>46191.87447540509</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3737,9 +3755,11 @@
       <c r="B40" s="5">
         <v>46079.83530085648</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46191.87497929398</v>
+      </c>
       <c r="D40" s="5">
-        <v>46169.848559375</v>
+        <v>46191.87498288194</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3796,9 +3816,11 @@
       <c r="B41" s="8">
         <v>46079.835302418986</v>
       </c>
-      <c r="C41" s="9"/>
+      <c r="C41" s="8">
+        <v>46191.874874120374</v>
+      </c>
       <c r="D41" s="8">
-        <v>46191.801202013885</v>
+        <v>46191.874875995374</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -4951,7 +4973,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46090.80458715278</v>
+        <v>46191.874823923616</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4998,8 +5020,8 @@
       <c r="S60" s="6">
         <v>0</v>
       </c>
-      <c r="T60" s="11" t="s">
-        <v>58</v>
+      <c r="T60" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="U60" s="10" t="s">
         <v>59</v>
@@ -5014,7 +5036,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46090.804584259255</v>
+        <v>46191.87471502315</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>56</v>
@@ -5061,8 +5083,8 @@
       <c r="S61" s="9">
         <v>0</v>
       </c>
-      <c r="T61" s="11" t="s">
-        <v>58</v>
+      <c r="T61" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="U61" s="10" t="s">
         <v>59</v>
@@ -5140,7 +5162,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46158.992457141205</v>
+        <v>46191.87499096065</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5203,7 +5225,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46114.817406041664</v>
+        <v>46191.874584930556</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46185.204906643514</v>
+        <v>46192.16832519676</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46191.87471502315</v>
+        <v>46192.20217834491</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>56</v>
@@ -5086,8 +5086,8 @@
       <c r="T61" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="U61" s="10" t="s">
-        <v>59</v>
+      <c r="U61" s="12" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46192.16832519676</v>
+        <v>46193.205434930554</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -4907,8 +4907,8 @@
       <c r="T58" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="U58" s="12" t="s">
-        <v>123</v>
+      <c r="U58" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -4007,7 +4007,7 @@
         <v>46114.76610813657</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.76611935185</v>
+        <v>46196.20244436343</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4057,8 +4057,8 @@
       <c r="T44" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U44" s="10" t="s">
-        <v>59</v>
+      <c r="U44" s="12" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -2767,7 +2767,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46191.80108803241</v>
+        <v>46196.639933819446</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -1523,13 +1523,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.83530122685</v>
+        <v>46079.668634560185</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.71525421296</v>
+        <v>46092.54858754629</v>
       </c>
       <c r="D4" s="5">
-        <v>46128.59644841435</v>
+        <v>46128.42978174768</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1572,13 +1572,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.835301493054</v>
+        <v>46079.66863482639</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.715221805556</v>
+        <v>46092.548555138885</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.715255312505</v>
+        <v>46092.548588645834</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1637,13 +1637,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.83530173611</v>
+        <v>46079.66863506944</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.71522243056</v>
+        <v>46092.54855576389</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.71525466435</v>
+        <v>46092.548587997684</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1702,13 +1702,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.835301956016</v>
+        <v>46079.66863528935</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71522290509</v>
+        <v>46092.54855623843</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.71525525463</v>
+        <v>46092.54858858796</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1767,13 +1767,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.835302175925</v>
+        <v>46079.66863550926</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.715223391206</v>
+        <v>46092.548556724534</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.602382129626</v>
+        <v>46128.43571546296</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1832,13 +1832,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.835302384265</v>
+        <v>46079.66863571759</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71522413194</v>
+        <v>46092.54855746528</v>
       </c>
       <c r="D9" s="8">
-        <v>46128.596533055555</v>
+        <v>46128.42986638889</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1897,11 +1897,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.835302604166</v>
+        <v>46079.6686359375</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46142.66126674769</v>
+        <v>46142.494600081016</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1944,13 +1944,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.835302858795</v>
+        <v>46079.66863619213</v>
       </c>
       <c r="C11" s="8">
-        <v>46142.661258946755</v>
+        <v>46142.4945922801</v>
       </c>
       <c r="D11" s="8">
-        <v>46142.661260625</v>
+        <v>46142.494593958334</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -2009,11 +2009,11 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.83530313657</v>
+        <v>46079.66863646991</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46133.57711384259</v>
+        <v>46133.41044717593</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2072,13 +2072,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46079.83530335648</v>
+        <v>46079.668636689814</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51490326389</v>
+        <v>46114.34823659722</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.51491809028</v>
+        <v>46114.34825142361</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2125,13 +2125,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46079.83530126157</v>
+        <v>46079.668634594906</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.51435532408</v>
+        <v>46114.347688657406</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.5143725</v>
+        <v>46114.34770583334</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2190,13 +2190,13 @@
         <v>66</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.83530193287</v>
+        <v>46079.66863526621</v>
       </c>
       <c r="C15" s="8">
-        <v>46111.792812430554</v>
+        <v>46111.62614576389</v>
       </c>
       <c r="D15" s="8">
-        <v>46111.79282915509</v>
+        <v>46111.62616248842</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>67</v>
@@ -2255,13 +2255,13 @@
         <v>69</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.83530225694</v>
+        <v>46079.66863559028</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.51445959491</v>
+        <v>46114.34779292824</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.51447722223</v>
+        <v>46114.347810555555</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>70</v>
@@ -2320,13 +2320,13 @@
         <v>72</v>
       </c>
       <c r="B17" s="8">
-        <v>46080.51025131944</v>
+        <v>46080.34358465278</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.51481871528</v>
+        <v>46114.34815204861</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.51483395833</v>
+        <v>46114.34816729167</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>73</v>
@@ -2385,13 +2385,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.83530255787</v>
+        <v>46079.668635891205</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.51488369213</v>
+        <v>46114.348217025465</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.51490420139</v>
+        <v>46114.34823753472</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2450,13 +2450,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.83530284722</v>
+        <v>46079.668636180555</v>
       </c>
       <c r="C19" s="8">
-        <v>46128.431861122684</v>
+        <v>46128.26519445602</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.801118738425</v>
+        <v>46191.634452071754</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2503,13 +2503,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.83530313657</v>
+        <v>46079.66863646991</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.54399693287</v>
+        <v>46097.3773302662</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.79283396991</v>
+        <v>46111.62616730324</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2568,13 +2568,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.8353034375</v>
+        <v>46079.66863677083</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.514944780094</v>
+        <v>46114.34827811342</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.514961354165</v>
+        <v>46114.3482946875</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2633,13 +2633,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.83530375</v>
+        <v>46079.668637083334</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.51496503472</v>
+        <v>46114.34829836806</v>
       </c>
       <c r="D22" s="5">
-        <v>46142.66126559028</v>
+        <v>46142.494598923615</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2698,13 +2698,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.835304050925</v>
+        <v>46079.66863738426</v>
       </c>
       <c r="C23" s="8">
-        <v>46128.43184210648</v>
+        <v>46128.26517543981</v>
       </c>
       <c r="D23" s="8">
-        <v>46129.00161702547</v>
+        <v>46128.834950358796</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2763,11 +2763,11 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.83530122685</v>
+        <v>46079.668634560185</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46196.639933819446</v>
+        <v>46196.473267152774</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2826,13 +2826,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.87430951389</v>
+        <v>46079.70764284722</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.80111393519</v>
+        <v>46191.634447268516</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.801115636576</v>
+        <v>46191.63444896991</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>102</v>
@@ -2891,13 +2891,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46080.51039956018</v>
+        <v>46080.34373289352</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.801125949074</v>
+        <v>46191.6344592824</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.80112726852</v>
+        <v>46191.634460601854</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2956,11 +2956,11 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.83530158565</v>
+        <v>46079.668634918984</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46191.87501525463</v>
+        <v>46191.70834858796</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -3005,13 +3005,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.83530186342</v>
+        <v>46079.66863519676</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.874819687495</v>
+        <v>46191.70815302084</v>
       </c>
       <c r="D28" s="5">
-        <v>46191.874831574074</v>
+        <v>46191.70816490741</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -3070,13 +3070,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.83530212963</v>
+        <v>46079.668635462964</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.544059004635</v>
+        <v>46097.37739233796</v>
       </c>
       <c r="D29" s="8">
-        <v>46169.848412384265</v>
+        <v>46169.68174571759</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3131,13 +3131,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.83530236111</v>
+        <v>46079.66863569444</v>
       </c>
       <c r="C30" s="5">
-        <v>46191.87480532407</v>
+        <v>46191.70813865741</v>
       </c>
       <c r="D30" s="5">
-        <v>46191.87480704861</v>
+        <v>46191.70814038195</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3192,13 +3192,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.83530269676</v>
+        <v>46079.668636030096</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.874711435186</v>
+        <v>46191.708044768515</v>
       </c>
       <c r="D31" s="8">
-        <v>46191.8747227662</v>
+        <v>46191.70805609954</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3257,13 +3257,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.83530295139</v>
+        <v>46079.668636284725</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.67922460648</v>
+        <v>46182.512557939815</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.6792266088</v>
+        <v>46182.51255994213</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3318,13 +3318,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.83530319444</v>
+        <v>46079.66863652778</v>
       </c>
       <c r="C33" s="8">
-        <v>46191.8746965162</v>
+        <v>46191.70802984954</v>
       </c>
       <c r="D33" s="8">
-        <v>46191.874698125</v>
+        <v>46191.70803145833</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3379,13 +3379,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.835301238425</v>
+        <v>46079.66863457176</v>
       </c>
       <c r="C34" s="5">
-        <v>46191.87458894676</v>
+        <v>46191.7079222801</v>
       </c>
       <c r="D34" s="5">
-        <v>46191.874603414355</v>
+        <v>46191.70793674768</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3444,13 +3444,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.835301493054</v>
+        <v>46079.66863482639</v>
       </c>
       <c r="C35" s="8">
-        <v>46114.76627853009</v>
+        <v>46114.59961186342</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.84848269676</v>
+        <v>46169.68181603009</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3505,13 +3505,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.83530179398</v>
+        <v>46079.66863512732</v>
       </c>
       <c r="C36" s="5">
-        <v>46191.87457479167</v>
+        <v>46191.707908125</v>
       </c>
       <c r="D36" s="5">
-        <v>46191.87457655092</v>
+        <v>46191.70790988426</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3566,13 +3566,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.83530215277</v>
+        <v>46079.668635486116</v>
       </c>
       <c r="C37" s="8">
-        <v>46114.81738291666</v>
+        <v>46114.65071625</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.84849621527</v>
+        <v>46169.681829548615</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3627,13 +3627,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46079.83530342593</v>
+        <v>46079.66863675926</v>
       </c>
       <c r="C38" s="5">
-        <v>46191.8749955324</v>
+        <v>46191.708328865745</v>
       </c>
       <c r="D38" s="5">
-        <v>46191.875013136574</v>
+        <v>46191.70834646991</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3692,13 +3692,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46079.83530366898</v>
+        <v>46079.668637002316</v>
       </c>
       <c r="C39" s="8">
-        <v>46191.87447350695</v>
+        <v>46191.70780684028</v>
       </c>
       <c r="D39" s="8">
-        <v>46191.87447540509</v>
+        <v>46191.70780873843</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3753,13 +3753,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.83530085648</v>
+        <v>46079.66863418982</v>
       </c>
       <c r="C40" s="5">
-        <v>46191.87497929398</v>
+        <v>46191.708312627314</v>
       </c>
       <c r="D40" s="5">
-        <v>46191.87498288194</v>
+        <v>46191.70831621528</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3814,13 +3814,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.835302418986</v>
+        <v>46079.668635752314</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.874874120374</v>
+        <v>46191.7082074537</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.874875995374</v>
+        <v>46191.7082093287</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3879,13 +3879,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.83530269676</v>
+        <v>46079.668636030096</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.765637812496</v>
+        <v>46114.59897114584</v>
       </c>
       <c r="D42" s="5">
-        <v>46191.80109314815</v>
+        <v>46191.63442648148</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3940,13 +3940,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.835302962965</v>
+        <v>46079.668636296294</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.76568907408</v>
+        <v>46114.599022407405</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.765690740736</v>
+        <v>46114.59902407408</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4001,13 +4001,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.87449113426</v>
+        <v>46079.707824467594</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.76610813657</v>
+        <v>46114.59944146991</v>
       </c>
       <c r="D44" s="5">
-        <v>46196.20244436343</v>
+        <v>46196.03577769676</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4066,13 +4066,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.87456693287</v>
+        <v>46079.70790026621</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.7660537037</v>
+        <v>46114.59938703704</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.80111972222</v>
+        <v>46191.63445305555</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4127,13 +4127,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.8746696875</v>
+        <v>46079.70800302083</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.7660946875</v>
+        <v>46114.59942802083</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.766096481486</v>
+        <v>46114.599429814814</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4188,11 +4188,11 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.835303252315</v>
+        <v>46079.668636585644</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46127.68782663194</v>
+        <v>46127.52115996528</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4237,13 +4237,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.8353035301</v>
+        <v>46079.668636863425</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.7954665162</v>
+        <v>46114.62879984954</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.79548327546</v>
+        <v>46114.6288166088</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4302,13 +4302,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.83530068287</v>
+        <v>46079.668634016205</v>
       </c>
       <c r="C49" s="8">
-        <v>46127.68775965278</v>
+        <v>46127.521092986106</v>
       </c>
       <c r="D49" s="8">
-        <v>46156.20046739583</v>
+        <v>46156.03380072917</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4367,13 +4367,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46087.628862847225</v>
+        <v>46087.46219618055</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.68781304398</v>
+        <v>46127.521146377316</v>
       </c>
       <c r="D50" s="5">
-        <v>46158.99592378472</v>
+        <v>46158.82925711806</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4432,11 +4432,11 @@
         <v>187</v>
       </c>
       <c r="B51" s="8">
-        <v>46087.62890292824</v>
+        <v>46087.46223626158</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46127.69021349537</v>
+        <v>46127.5235468287</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>188</v>
@@ -4495,11 +4495,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.835301053245</v>
+        <v>46079.66863438657</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46191.80128876158</v>
+        <v>46191.634622094905</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4548,11 +4548,11 @@
         <v>194</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.835301342595</v>
+        <v>46079.66863467592</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46191.80125251158</v>
+        <v>46191.634585844906</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>195</v>
@@ -4611,11 +4611,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.83530162037</v>
+        <v>46079.668634953705</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46191.80126277778</v>
+        <v>46191.63459611111</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4674,11 +4674,11 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.835301886575</v>
+        <v>46079.6686352199</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46080.57920532407</v>
+        <v>46080.41253865741</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4727,11 +4727,11 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.835302164356</v>
+        <v>46079.668635497685</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46191.80126917824</v>
+        <v>46191.63460251158</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4790,11 +4790,11 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.835302418986</v>
+        <v>46079.668635752314</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.1671537963</v>
+        <v>46191.000487129626</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>212</v>
@@ -4853,11 +4853,11 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.835302673615</v>
+        <v>46079.66863600694</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46193.205434930554</v>
+        <v>46193.03876826389</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -4916,11 +4916,11 @@
         <v>218</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.83530291667</v>
+        <v>46079.668636250004</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46158.99585525463</v>
+        <v>46158.82918858796</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>192</v>
@@ -4969,11 +4969,11 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.83530225694</v>
+        <v>46079.66863559028</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46191.874823923616</v>
+        <v>46191.708157256944</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -5032,11 +5032,11 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.835301851854</v>
+        <v>46079.66863518518</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46192.20217834491</v>
+        <v>46192.035511678245</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>56</v>
@@ -5095,11 +5095,11 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.87589787037</v>
+        <v>46079.7092312037</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46114.766112094905</v>
+        <v>46114.59944542824</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5158,11 +5158,11 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.83530319444</v>
+        <v>46079.66863652778</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46191.87499096065</v>
+        <v>46191.708324293984</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5221,11 +5221,11 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.83530262731</v>
+        <v>46079.66863596065</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46191.874584930556</v>
+        <v>46191.707918263884</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5284,11 +5284,11 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.835302962965</v>
+        <v>46079.668636296294</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46158.99592380787</v>
+        <v>46158.8292571412</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5337,11 +5337,11 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46079.83530328704</v>
+        <v>46079.66863662037</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46158.99592369213</v>
+        <v>46158.82925702546</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>217</v>
@@ -5400,11 +5400,11 @@
         <v>239</v>
       </c>
       <c r="B67" s="8">
-        <v>46079.83530362268</v>
+        <v>46079.66863695602</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46127.6878281713</v>
+        <v>46127.52116150463</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>240</v>
@@ -5463,11 +5463,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46079.83530398148</v>
+        <v>46079.66863731481</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46127.6878287963</v>
+        <v>46127.52116212963</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5526,11 +5526,11 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46079.835304293985</v>
+        <v>46079.668637627314</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46127.68782931713</v>
+        <v>46127.52116265046</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>248</v>
@@ -5589,11 +5589,11 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46080.49271868056</v>
+        <v>46080.32605201389</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46127.687829814815</v>
+        <v>46127.52116314815</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>251</v>
@@ -5652,11 +5652,11 @@
         <v>253</v>
       </c>
       <c r="B71" s="8">
-        <v>46079.83530460648</v>
+        <v>46079.668637939816</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46158.99592372685</v>
+        <v>46158.829257060184</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>189</v>
@@ -5715,11 +5715,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46079.83530493056</v>
+        <v>46079.66863826389</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46090.804674259256</v>
+        <v>46090.63800759259</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>257</v>
@@ -5778,11 +5778,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46079.83530144676</v>
+        <v>46079.66863478009</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46090.67671023148</v>
+        <v>46090.51004356482</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5825,11 +5825,11 @@
         <v>262</v>
       </c>
       <c r="B74" s="5">
-        <v>46079.83530181713</v>
+        <v>46079.66863515046</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46090.80473224537</v>
+        <v>46090.63806557871</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>263</v>
@@ -5886,11 +5886,11 @@
         <v>265</v>
       </c>
       <c r="B75" s="8">
-        <v>46079.8353024074</v>
+        <v>46079.668635740745</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46097.64290024305</v>
+        <v>46097.47623357639</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>57</v>
@@ -5949,11 +5949,11 @@
         <v>268</v>
       </c>
       <c r="B76" s="5">
-        <v>46079.83530269676</v>
+        <v>46079.668636030096</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.80487153935</v>
+        <v>46090.63820487268</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>269</v>
@@ -6012,11 +6012,11 @@
         <v>271</v>
       </c>
       <c r="B77" s="8">
-        <v>46079.83530306713</v>
+        <v>46079.66863640046</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46090.80495936342</v>
+        <v>46090.63829269676</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>272</v>
@@ -6075,11 +6075,11 @@
         <v>274</v>
       </c>
       <c r="B78" s="5">
-        <v>46079.83530333333</v>
+        <v>46079.66863666667</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46090.67667782407</v>
+        <v>46090.51001115741</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>275</v>
@@ -6122,11 +6122,11 @@
         <v>277</v>
       </c>
       <c r="B79" s="8">
-        <v>46079.83530363426</v>
+        <v>46079.66863696759</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.805033425924</v>
+        <v>46090.63836675926</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>278</v>
@@ -6185,11 +6185,11 @@
         <v>281</v>
       </c>
       <c r="B80" s="5">
-        <v>46079.83530395833</v>
+        <v>46079.66863729167</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.51489402778</v>
+        <v>46114.348227361115</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>282</v>
@@ -6248,11 +6248,11 @@
         <v>284</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.6740474074</v>
+        <v>46090.507380740746</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.6782175</v>
+        <v>46090.51155083333</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>285</v>
@@ -6301,11 +6301,11 @@
         <v>287</v>
       </c>
       <c r="B82" s="5">
-        <v>46090.674231365745</v>
+        <v>46090.50756469907</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46090.80510871528</v>
+        <v>46090.638442048614</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>288</v>
@@ -6364,11 +6364,11 @@
         <v>290</v>
       </c>
       <c r="B83" s="8">
-        <v>46090.67444209491</v>
+        <v>46090.50777542824</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46090.80510556713</v>
+        <v>46090.63843890047</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>291</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -1523,13 +1523,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.668634560185</v>
+        <v>46079.83530122685</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.54858754629</v>
+        <v>46092.71525421296</v>
       </c>
       <c r="D4" s="5">
-        <v>46128.42978174768</v>
+        <v>46128.59644841435</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1572,13 +1572,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.66863482639</v>
+        <v>46079.835301493054</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.548555138885</v>
+        <v>46092.715221805556</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.548588645834</v>
+        <v>46092.715255312505</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1637,13 +1637,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.66863506944</v>
+        <v>46079.83530173611</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.54855576389</v>
+        <v>46092.71522243056</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.548587997684</v>
+        <v>46092.71525466435</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1702,13 +1702,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.66863528935</v>
+        <v>46079.835301956016</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.54855623843</v>
+        <v>46092.71522290509</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.54858858796</v>
+        <v>46092.71525525463</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1767,13 +1767,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.66863550926</v>
+        <v>46079.835302175925</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.548556724534</v>
+        <v>46092.715223391206</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.43571546296</v>
+        <v>46128.602382129626</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1832,13 +1832,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.66863571759</v>
+        <v>46079.835302384265</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.54855746528</v>
+        <v>46092.71522413194</v>
       </c>
       <c r="D9" s="8">
-        <v>46128.42986638889</v>
+        <v>46128.596533055555</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1897,11 +1897,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.6686359375</v>
+        <v>46079.835302604166</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46142.494600081016</v>
+        <v>46142.66126674769</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1944,13 +1944,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.66863619213</v>
+        <v>46079.835302858795</v>
       </c>
       <c r="C11" s="8">
-        <v>46142.4945922801</v>
+        <v>46142.661258946755</v>
       </c>
       <c r="D11" s="8">
-        <v>46142.494593958334</v>
+        <v>46142.661260625</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -2009,11 +2009,11 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.66863646991</v>
+        <v>46079.83530313657</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46133.41044717593</v>
+        <v>46133.57711384259</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2072,13 +2072,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46079.668636689814</v>
+        <v>46079.83530335648</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.34823659722</v>
+        <v>46114.51490326389</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.34825142361</v>
+        <v>46114.51491809028</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2125,13 +2125,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46079.668634594906</v>
+        <v>46079.83530126157</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.347688657406</v>
+        <v>46114.51435532408</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.34770583334</v>
+        <v>46114.5143725</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2190,13 +2190,13 @@
         <v>66</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.66863526621</v>
+        <v>46079.83530193287</v>
       </c>
       <c r="C15" s="8">
-        <v>46111.62614576389</v>
+        <v>46111.792812430554</v>
       </c>
       <c r="D15" s="8">
-        <v>46111.62616248842</v>
+        <v>46111.79282915509</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>67</v>
@@ -2255,13 +2255,13 @@
         <v>69</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.66863559028</v>
+        <v>46079.83530225694</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.34779292824</v>
+        <v>46114.51445959491</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.347810555555</v>
+        <v>46114.51447722223</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>70</v>
@@ -2320,13 +2320,13 @@
         <v>72</v>
       </c>
       <c r="B17" s="8">
-        <v>46080.34358465278</v>
+        <v>46080.51025131944</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34815204861</v>
+        <v>46114.51481871528</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.34816729167</v>
+        <v>46114.51483395833</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>73</v>
@@ -2385,13 +2385,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.668635891205</v>
+        <v>46079.83530255787</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.348217025465</v>
+        <v>46114.51488369213</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.34823753472</v>
+        <v>46114.51490420139</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2450,13 +2450,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.668636180555</v>
+        <v>46079.83530284722</v>
       </c>
       <c r="C19" s="8">
-        <v>46128.26519445602</v>
+        <v>46128.431861122684</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.634452071754</v>
+        <v>46191.801118738425</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2503,13 +2503,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.66863646991</v>
+        <v>46079.83530313657</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3773302662</v>
+        <v>46097.54399693287</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.62616730324</v>
+        <v>46111.79283396991</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2568,13 +2568,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.66863677083</v>
+        <v>46079.8353034375</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.34827811342</v>
+        <v>46114.514944780094</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.3482946875</v>
+        <v>46114.514961354165</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2633,13 +2633,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.668637083334</v>
+        <v>46079.83530375</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.34829836806</v>
+        <v>46114.51496503472</v>
       </c>
       <c r="D22" s="5">
-        <v>46142.494598923615</v>
+        <v>46142.66126559028</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2698,13 +2698,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.66863738426</v>
+        <v>46079.835304050925</v>
       </c>
       <c r="C23" s="8">
-        <v>46128.26517543981</v>
+        <v>46128.43184210648</v>
       </c>
       <c r="D23" s="8">
-        <v>46128.834950358796</v>
+        <v>46129.00161702547</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2763,11 +2763,11 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.668634560185</v>
+        <v>46079.83530122685</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46196.473267152774</v>
+        <v>46196.639933819446</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2826,13 +2826,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.70764284722</v>
+        <v>46079.87430951389</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.634447268516</v>
+        <v>46191.80111393519</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.63444896991</v>
+        <v>46191.801115636576</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>102</v>
@@ -2891,13 +2891,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46080.34373289352</v>
+        <v>46080.51039956018</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.6344592824</v>
+        <v>46191.801125949074</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.634460601854</v>
+        <v>46191.80112726852</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2956,11 +2956,11 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.668634918984</v>
+        <v>46079.83530158565</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46191.70834858796</v>
+        <v>46191.87501525463</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -3005,13 +3005,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.66863519676</v>
+        <v>46079.83530186342</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.70815302084</v>
+        <v>46191.874819687495</v>
       </c>
       <c r="D28" s="5">
-        <v>46191.70816490741</v>
+        <v>46191.874831574074</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -3070,13 +3070,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.668635462964</v>
+        <v>46079.83530212963</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.37739233796</v>
+        <v>46097.544059004635</v>
       </c>
       <c r="D29" s="8">
-        <v>46169.68174571759</v>
+        <v>46169.848412384265</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3131,13 +3131,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.66863569444</v>
+        <v>46079.83530236111</v>
       </c>
       <c r="C30" s="5">
-        <v>46191.70813865741</v>
+        <v>46191.87480532407</v>
       </c>
       <c r="D30" s="5">
-        <v>46191.70814038195</v>
+        <v>46191.87480704861</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3192,13 +3192,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.668636030096</v>
+        <v>46079.83530269676</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.708044768515</v>
+        <v>46191.874711435186</v>
       </c>
       <c r="D31" s="8">
-        <v>46191.70805609954</v>
+        <v>46191.8747227662</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3257,13 +3257,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.668636284725</v>
+        <v>46079.83530295139</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.512557939815</v>
+        <v>46182.67922460648</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.51255994213</v>
+        <v>46182.6792266088</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3318,13 +3318,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.66863652778</v>
+        <v>46079.83530319444</v>
       </c>
       <c r="C33" s="8">
-        <v>46191.70802984954</v>
+        <v>46191.8746965162</v>
       </c>
       <c r="D33" s="8">
-        <v>46191.70803145833</v>
+        <v>46191.874698125</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3379,13 +3379,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.66863457176</v>
+        <v>46079.835301238425</v>
       </c>
       <c r="C34" s="5">
-        <v>46191.7079222801</v>
+        <v>46191.87458894676</v>
       </c>
       <c r="D34" s="5">
-        <v>46191.70793674768</v>
+        <v>46191.874603414355</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3444,13 +3444,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.66863482639</v>
+        <v>46079.835301493054</v>
       </c>
       <c r="C35" s="8">
-        <v>46114.59961186342</v>
+        <v>46114.76627853009</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.68181603009</v>
+        <v>46169.84848269676</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3505,13 +3505,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.66863512732</v>
+        <v>46079.83530179398</v>
       </c>
       <c r="C36" s="5">
-        <v>46191.707908125</v>
+        <v>46191.87457479167</v>
       </c>
       <c r="D36" s="5">
-        <v>46191.70790988426</v>
+        <v>46191.87457655092</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3566,13 +3566,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.668635486116</v>
+        <v>46079.83530215277</v>
       </c>
       <c r="C37" s="8">
-        <v>46114.65071625</v>
+        <v>46114.81738291666</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.681829548615</v>
+        <v>46169.84849621527</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3627,13 +3627,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46079.66863675926</v>
+        <v>46079.83530342593</v>
       </c>
       <c r="C38" s="5">
-        <v>46191.708328865745</v>
+        <v>46191.8749955324</v>
       </c>
       <c r="D38" s="5">
-        <v>46191.70834646991</v>
+        <v>46191.875013136574</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3692,13 +3692,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46079.668637002316</v>
+        <v>46079.83530366898</v>
       </c>
       <c r="C39" s="8">
-        <v>46191.70780684028</v>
+        <v>46191.87447350695</v>
       </c>
       <c r="D39" s="8">
-        <v>46191.70780873843</v>
+        <v>46191.87447540509</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3753,13 +3753,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.66863418982</v>
+        <v>46079.83530085648</v>
       </c>
       <c r="C40" s="5">
-        <v>46191.708312627314</v>
+        <v>46191.87497929398</v>
       </c>
       <c r="D40" s="5">
-        <v>46191.70831621528</v>
+        <v>46191.87498288194</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3814,13 +3814,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.668635752314</v>
+        <v>46079.835302418986</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.7082074537</v>
+        <v>46191.874874120374</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.7082093287</v>
+        <v>46191.874875995374</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3879,13 +3879,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.668636030096</v>
+        <v>46079.83530269676</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.59897114584</v>
+        <v>46114.765637812496</v>
       </c>
       <c r="D42" s="5">
-        <v>46191.63442648148</v>
+        <v>46191.80109314815</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3940,13 +3940,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.668636296294</v>
+        <v>46079.835302962965</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.599022407405</v>
+        <v>46114.76568907408</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.59902407408</v>
+        <v>46114.765690740736</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4001,13 +4001,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.707824467594</v>
+        <v>46079.87449113426</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.59944146991</v>
+        <v>46114.76610813657</v>
       </c>
       <c r="D44" s="5">
-        <v>46196.03577769676</v>
+        <v>46196.20244436343</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4066,13 +4066,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.70790026621</v>
+        <v>46079.87456693287</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.59938703704</v>
+        <v>46114.7660537037</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.63445305555</v>
+        <v>46191.80111972222</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4127,13 +4127,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.70800302083</v>
+        <v>46079.8746696875</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.59942802083</v>
+        <v>46114.7660946875</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.599429814814</v>
+        <v>46114.766096481486</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4188,11 +4188,11 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.668636585644</v>
+        <v>46079.835303252315</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46127.52115996528</v>
+        <v>46127.68782663194</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4237,13 +4237,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.668636863425</v>
+        <v>46079.8353035301</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.62879984954</v>
+        <v>46114.7954665162</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.6288166088</v>
+        <v>46114.79548327546</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4302,13 +4302,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.668634016205</v>
+        <v>46079.83530068287</v>
       </c>
       <c r="C49" s="8">
-        <v>46127.521092986106</v>
+        <v>46127.68775965278</v>
       </c>
       <c r="D49" s="8">
-        <v>46156.03380072917</v>
+        <v>46156.20046739583</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4367,13 +4367,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46087.46219618055</v>
+        <v>46087.628862847225</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.521146377316</v>
+        <v>46127.68781304398</v>
       </c>
       <c r="D50" s="5">
-        <v>46158.82925711806</v>
+        <v>46158.99592378472</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4432,11 +4432,11 @@
         <v>187</v>
       </c>
       <c r="B51" s="8">
-        <v>46087.46223626158</v>
+        <v>46087.62890292824</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46127.5235468287</v>
+        <v>46127.69021349537</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>188</v>
@@ -4495,11 +4495,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.66863438657</v>
+        <v>46079.835301053245</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46191.634622094905</v>
+        <v>46191.80128876158</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4548,11 +4548,11 @@
         <v>194</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.66863467592</v>
+        <v>46079.835301342595</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46191.634585844906</v>
+        <v>46191.80125251158</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>195</v>
@@ -4611,11 +4611,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.668634953705</v>
+        <v>46079.83530162037</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46191.63459611111</v>
+        <v>46191.80126277778</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4674,11 +4674,11 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.6686352199</v>
+        <v>46079.835301886575</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46080.41253865741</v>
+        <v>46080.57920532407</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4727,11 +4727,11 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.668635497685</v>
+        <v>46079.835302164356</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46191.63460251158</v>
+        <v>46191.80126917824</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4790,11 +4790,11 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.668635752314</v>
+        <v>46079.835302418986</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.000487129626</v>
+        <v>46191.1671537963</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>212</v>
@@ -4853,11 +4853,11 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.66863600694</v>
+        <v>46079.835302673615</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46193.03876826389</v>
+        <v>46193.205434930554</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -4916,11 +4916,11 @@
         <v>218</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.668636250004</v>
+        <v>46079.83530291667</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46158.82918858796</v>
+        <v>46158.99585525463</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>192</v>
@@ -4969,11 +4969,11 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.66863559028</v>
+        <v>46079.83530225694</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46191.708157256944</v>
+        <v>46191.874823923616</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -5032,11 +5032,11 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.66863518518</v>
+        <v>46079.835301851854</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46192.035511678245</v>
+        <v>46192.20217834491</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>56</v>
@@ -5095,11 +5095,11 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.7092312037</v>
+        <v>46079.87589787037</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46114.59944542824</v>
+        <v>46114.766112094905</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5158,11 +5158,11 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.66863652778</v>
+        <v>46079.83530319444</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46191.708324293984</v>
+        <v>46191.87499096065</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5221,11 +5221,11 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.66863596065</v>
+        <v>46079.83530262731</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46191.707918263884</v>
+        <v>46191.874584930556</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5284,11 +5284,11 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.668636296294</v>
+        <v>46079.835302962965</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46158.8292571412</v>
+        <v>46158.99592380787</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5337,11 +5337,11 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46079.66863662037</v>
+        <v>46079.83530328704</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46158.82925702546</v>
+        <v>46158.99592369213</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>217</v>
@@ -5400,11 +5400,11 @@
         <v>239</v>
       </c>
       <c r="B67" s="8">
-        <v>46079.66863695602</v>
+        <v>46079.83530362268</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46127.52116150463</v>
+        <v>46127.6878281713</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>240</v>
@@ -5463,11 +5463,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46079.66863731481</v>
+        <v>46079.83530398148</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46127.52116212963</v>
+        <v>46127.6878287963</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5526,11 +5526,11 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46079.668637627314</v>
+        <v>46079.835304293985</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46127.52116265046</v>
+        <v>46127.68782931713</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>248</v>
@@ -5589,11 +5589,11 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46080.32605201389</v>
+        <v>46080.49271868056</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46127.52116314815</v>
+        <v>46127.687829814815</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>251</v>
@@ -5652,11 +5652,11 @@
         <v>253</v>
       </c>
       <c r="B71" s="8">
-        <v>46079.668637939816</v>
+        <v>46079.83530460648</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46158.829257060184</v>
+        <v>46158.99592372685</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>189</v>
@@ -5715,11 +5715,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46079.66863826389</v>
+        <v>46079.83530493056</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46090.63800759259</v>
+        <v>46090.804674259256</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>257</v>
@@ -5778,11 +5778,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46079.66863478009</v>
+        <v>46079.83530144676</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46090.51004356482</v>
+        <v>46090.67671023148</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5825,11 +5825,11 @@
         <v>262</v>
       </c>
       <c r="B74" s="5">
-        <v>46079.66863515046</v>
+        <v>46079.83530181713</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46090.63806557871</v>
+        <v>46090.80473224537</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>263</v>
@@ -5886,11 +5886,11 @@
         <v>265</v>
       </c>
       <c r="B75" s="8">
-        <v>46079.668635740745</v>
+        <v>46079.8353024074</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46097.47623357639</v>
+        <v>46097.64290024305</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>57</v>
@@ -5949,11 +5949,11 @@
         <v>268</v>
       </c>
       <c r="B76" s="5">
-        <v>46079.668636030096</v>
+        <v>46079.83530269676</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.63820487268</v>
+        <v>46090.80487153935</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>269</v>
@@ -6012,11 +6012,11 @@
         <v>271</v>
       </c>
       <c r="B77" s="8">
-        <v>46079.66863640046</v>
+        <v>46079.83530306713</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46090.63829269676</v>
+        <v>46090.80495936342</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>272</v>
@@ -6075,11 +6075,11 @@
         <v>274</v>
       </c>
       <c r="B78" s="5">
-        <v>46079.66863666667</v>
+        <v>46079.83530333333</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46090.51001115741</v>
+        <v>46090.67667782407</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>275</v>
@@ -6122,11 +6122,11 @@
         <v>277</v>
       </c>
       <c r="B79" s="8">
-        <v>46079.66863696759</v>
+        <v>46079.83530363426</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.63836675926</v>
+        <v>46090.805033425924</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>278</v>
@@ -6185,11 +6185,11 @@
         <v>281</v>
       </c>
       <c r="B80" s="5">
-        <v>46079.66863729167</v>
+        <v>46079.83530395833</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.348227361115</v>
+        <v>46114.51489402778</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>282</v>
@@ -6248,11 +6248,11 @@
         <v>284</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.507380740746</v>
+        <v>46090.6740474074</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.51155083333</v>
+        <v>46090.6782175</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>285</v>
@@ -6301,11 +6301,11 @@
         <v>287</v>
       </c>
       <c r="B82" s="5">
-        <v>46090.50756469907</v>
+        <v>46090.674231365745</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46090.638442048614</v>
+        <v>46090.80510871528</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>288</v>
@@ -6364,11 +6364,11 @@
         <v>290</v>
       </c>
       <c r="B83" s="8">
-        <v>46090.50777542824</v>
+        <v>46090.67444209491</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46090.63843890047</v>
+        <v>46090.80510556713</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>291</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -392,130 +392,130 @@
     <t>Generación OC Tableros  ot 4265 - ot 4266,Fabricación Tablero  ot 4265 - ot 4266</t>
   </si>
   <si>
+    <t>1213459189153331</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros  ot 4265 - ot 4266</t>
+  </si>
+  <si>
+    <t>Fabricación Tablero  ot 4265 - ot 4266,Tablero ot 4265 - ot 4266</t>
+  </si>
+  <si>
+    <t>1213459189153332</t>
+  </si>
+  <si>
+    <t>Fabricación Tablero  ot 4265 - ot 4266</t>
+  </si>
+  <si>
+    <t>Tablero ot 4265 - ot 4266,Recepcion Tableros</t>
+  </si>
+  <si>
+    <t>1213459189153336</t>
+  </si>
+  <si>
+    <t>Motor ot 4264</t>
+  </si>
+  <si>
+    <t>Generación OC motor ot 4264,Fabricación motor ot 4264,Planos motor proveedor ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189207060</t>
+  </si>
+  <si>
+    <t>Generación OC motor ot 4264</t>
+  </si>
+  <si>
+    <t>Fabricación motor ot 4264,Motor ot 4264,Planos motor proveedor ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189207061</t>
+  </si>
+  <si>
+    <t>Fabricación motor ot 4264</t>
+  </si>
+  <si>
+    <t>Motor ot 4264,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1213459189207062</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor ot 4264</t>
+  </si>
+  <si>
+    <t>Motor ot 4264,Ingenieria y diseño:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1213459189153333</t>
+  </si>
+  <si>
+    <t>rodete ot 4264</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete ot 4264,Fabricación Rodete ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189153334</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete ot 4264</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete ot 4264,rodete ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189153335</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete ot 4264</t>
+  </si>
+  <si>
+    <t>rodete ot 4264,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1213459189207063</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento:</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales,Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
+    <t>1213459189207064</t>
+  </si>
+  <si>
+    <t>Generación OC materiales</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales,Materiales a codigo // compras locales aprovisionamientomiento:</t>
+  </si>
+  <si>
+    <t>1213459189207065</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento:,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213458788103037</t>
+  </si>
+  <si>
+    <t>Sensores</t>
+  </si>
+  <si>
+    <t>Generación OC Sensores,Fabricacion Sensores</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213459189153331</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros  ot 4265 - ot 4266</t>
-  </si>
-  <si>
-    <t>Fabricación Tablero  ot 4265 - ot 4266,Tablero ot 4265 - ot 4266</t>
-  </si>
-  <si>
-    <t>1213459189153332</t>
-  </si>
-  <si>
-    <t>Fabricación Tablero  ot 4265 - ot 4266</t>
-  </si>
-  <si>
-    <t>Tablero ot 4265 - ot 4266,Recepcion Tableros</t>
-  </si>
-  <si>
-    <t>1213459189153336</t>
-  </si>
-  <si>
-    <t>Motor ot 4264</t>
-  </si>
-  <si>
-    <t>Generación OC motor ot 4264,Fabricación motor ot 4264,Planos motor proveedor ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189207060</t>
-  </si>
-  <si>
-    <t>Generación OC motor ot 4264</t>
-  </si>
-  <si>
-    <t>Fabricación motor ot 4264,Motor ot 4264,Planos motor proveedor ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189207061</t>
-  </si>
-  <si>
-    <t>Fabricación motor ot 4264</t>
-  </si>
-  <si>
-    <t>Motor ot 4264,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1213459189207062</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor ot 4264</t>
-  </si>
-  <si>
-    <t>Motor ot 4264,Ingenieria y diseño:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1213459189153333</t>
-  </si>
-  <si>
-    <t>rodete ot 4264</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete ot 4264,Fabricación Rodete ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189153334</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete ot 4264</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete ot 4264,rodete ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189153335</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete ot 4264</t>
-  </si>
-  <si>
-    <t>rodete ot 4264,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1213459189207063</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento:</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales,Fabricacion a codigo y compras locales</t>
-  </si>
-  <si>
-    <t>1213459189207064</t>
-  </si>
-  <si>
-    <t>Generación OC materiales</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales,Materiales a codigo // compras locales aprovisionamientomiento:</t>
-  </si>
-  <si>
-    <t>1213459189207065</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento:,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213458788103037</t>
-  </si>
-  <si>
-    <t>Sensores</t>
-  </si>
-  <si>
-    <t>Generación OC Sensores,Fabricacion Sensores</t>
   </si>
   <si>
     <t>1213458788103039</t>
@@ -3198,7 +3198,7 @@
         <v>46191.874711435186</v>
       </c>
       <c r="D31" s="8">
-        <v>46191.8747227662</v>
+        <v>46198.19648104167</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3248,13 +3248,13 @@
       <c r="T31" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U31" s="12" t="s">
-        <v>123</v>
+      <c r="U31" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46079.83530295139</v>
@@ -3266,7 +3266,7 @@
         <v>46182.6792266088</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3299,7 +3299,7 @@
         <v>90</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3315,7 +3315,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46079.83530319444</v>
@@ -3327,7 +3327,7 @@
         <v>46191.874698125</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3357,10 +3357,10 @@
         <v>121</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46079.835301238425</v>
@@ -3388,7 +3388,7 @@
         <v>46191.874603414355</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3418,7 +3418,7 @@
         <v>107</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>107</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46079.835301493054</v>
@@ -3453,7 +3453,7 @@
         <v>46169.84848269676</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3480,13 +3480,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>87</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46079.83530179398</v>
@@ -3514,7 +3514,7 @@
         <v>46191.87457655092</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3541,13 +3541,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3563,7 +3563,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46079.83530215277</v>
@@ -3575,7 +3575,7 @@
         <v>46169.84849621527</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -3602,13 +3602,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3624,7 +3624,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46079.83530342593</v>
@@ -3636,7 +3636,7 @@
         <v>46191.875013136574</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3666,7 +3666,7 @@
         <v>107</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>107</v>
@@ -3689,7 +3689,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46079.83530366898</v>
@@ -3701,7 +3701,7 @@
         <v>46191.87447540509</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
@@ -3728,13 +3728,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>93</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3750,7 +3750,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46079.83530085648</v>
@@ -3762,7 +3762,7 @@
         <v>46191.87498288194</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -3789,13 +3789,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3811,7 +3811,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>46079.835302418986</v>
@@ -3823,16 +3823,16 @@
         <v>46191.874875995374</v>
       </c>
       <c r="E41" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="9" t="s">
+      <c r="H41" s="9" t="s">
         <v>153</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>154</v>
       </c>
       <c r="I41" s="8">
         <v>46097</v>
@@ -3853,7 +3853,7 @@
         <v>107</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>107</v>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46079.83530269676</v>
@@ -3888,16 +3888,16 @@
         <v>46191.80109314815</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I42" s="5">
         <v>46097</v>
@@ -3915,13 +3915,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3937,7 +3937,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46079.835302962965</v>
@@ -3949,16 +3949,16 @@
         <v>46114.765690740736</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>153</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>154</v>
       </c>
       <c r="I43" s="8">
         <v>46115</v>
@@ -3976,13 +3976,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3998,7 +3998,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46079.87449113426</v>
@@ -4010,16 +4010,16 @@
         <v>46196.20244436343</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I44" s="5">
         <v>46097</v>
@@ -4040,7 +4040,7 @@
         <v>107</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>107</v>
@@ -4058,7 +4058,7 @@
         <v>31</v>
       </c>
       <c r="U44" s="12" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4081,10 +4081,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>153</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>154</v>
       </c>
       <c r="I45" s="8">
         <v>46097</v>
@@ -4102,7 +4102,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>102</v>
@@ -4142,10 +4142,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I46" s="5">
         <v>46126</v>
@@ -4163,7 +4163,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>166</v>
@@ -4585,7 +4585,7 @@
         <v>192</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>198</v>
@@ -5069,7 +5069,7 @@
         <v>192</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>224</v>
@@ -5087,7 +5087,7 @@
         <v>85</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46114.766112094905</v>
+        <v>46198.16904811343</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5149,8 +5149,8 @@
       <c r="T62" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="U62" s="10" t="s">
-        <v>59</v>
+      <c r="U62" s="12" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5195,7 +5195,7 @@
         <v>192</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>230</v>
@@ -5258,7 +5258,7 @@
         <v>192</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>233</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -1523,13 +1523,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.83530122685</v>
+        <v>46079.668634560185</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.71525421296</v>
+        <v>46092.54858754629</v>
       </c>
       <c r="D4" s="5">
-        <v>46128.59644841435</v>
+        <v>46128.42978174768</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1572,13 +1572,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.835301493054</v>
+        <v>46079.66863482639</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.715221805556</v>
+        <v>46092.548555138885</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.715255312505</v>
+        <v>46092.548588645834</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1637,13 +1637,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.83530173611</v>
+        <v>46079.66863506944</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.71522243056</v>
+        <v>46092.54855576389</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.71525466435</v>
+        <v>46092.548587997684</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1702,13 +1702,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.835301956016</v>
+        <v>46079.66863528935</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71522290509</v>
+        <v>46092.54855623843</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.71525525463</v>
+        <v>46092.54858858796</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1767,13 +1767,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.835302175925</v>
+        <v>46079.66863550926</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.715223391206</v>
+        <v>46092.548556724534</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.602382129626</v>
+        <v>46128.43571546296</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1832,13 +1832,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.835302384265</v>
+        <v>46079.66863571759</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71522413194</v>
+        <v>46092.54855746528</v>
       </c>
       <c r="D9" s="8">
-        <v>46128.596533055555</v>
+        <v>46128.42986638889</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1897,11 +1897,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.835302604166</v>
+        <v>46079.6686359375</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46142.66126674769</v>
+        <v>46142.494600081016</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1944,13 +1944,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.835302858795</v>
+        <v>46079.66863619213</v>
       </c>
       <c r="C11" s="8">
-        <v>46142.661258946755</v>
+        <v>46142.4945922801</v>
       </c>
       <c r="D11" s="8">
-        <v>46142.661260625</v>
+        <v>46142.494593958334</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -2009,11 +2009,11 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.83530313657</v>
+        <v>46079.66863646991</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46133.57711384259</v>
+        <v>46133.41044717593</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2072,13 +2072,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46079.83530335648</v>
+        <v>46079.668636689814</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51490326389</v>
+        <v>46114.34823659722</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.51491809028</v>
+        <v>46114.34825142361</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2125,13 +2125,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46079.83530126157</v>
+        <v>46079.668634594906</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.51435532408</v>
+        <v>46114.347688657406</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.5143725</v>
+        <v>46114.34770583334</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2190,13 +2190,13 @@
         <v>66</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.83530193287</v>
+        <v>46079.66863526621</v>
       </c>
       <c r="C15" s="8">
-        <v>46111.792812430554</v>
+        <v>46111.62614576389</v>
       </c>
       <c r="D15" s="8">
-        <v>46111.79282915509</v>
+        <v>46111.62616248842</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>67</v>
@@ -2255,13 +2255,13 @@
         <v>69</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.83530225694</v>
+        <v>46079.66863559028</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.51445959491</v>
+        <v>46114.34779292824</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.51447722223</v>
+        <v>46114.347810555555</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>70</v>
@@ -2320,13 +2320,13 @@
         <v>72</v>
       </c>
       <c r="B17" s="8">
-        <v>46080.51025131944</v>
+        <v>46080.34358465278</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.51481871528</v>
+        <v>46114.34815204861</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.51483395833</v>
+        <v>46114.34816729167</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>73</v>
@@ -2385,13 +2385,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.83530255787</v>
+        <v>46079.668635891205</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.51488369213</v>
+        <v>46114.348217025465</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.51490420139</v>
+        <v>46114.34823753472</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2450,13 +2450,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.83530284722</v>
+        <v>46079.668636180555</v>
       </c>
       <c r="C19" s="8">
-        <v>46128.431861122684</v>
+        <v>46128.26519445602</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.801118738425</v>
+        <v>46191.634452071754</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2503,13 +2503,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.83530313657</v>
+        <v>46079.66863646991</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.54399693287</v>
+        <v>46097.3773302662</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.79283396991</v>
+        <v>46111.62616730324</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2568,13 +2568,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.8353034375</v>
+        <v>46079.66863677083</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.514944780094</v>
+        <v>46114.34827811342</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.514961354165</v>
+        <v>46114.3482946875</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2633,13 +2633,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.83530375</v>
+        <v>46079.668637083334</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.51496503472</v>
+        <v>46114.34829836806</v>
       </c>
       <c r="D22" s="5">
-        <v>46142.66126559028</v>
+        <v>46142.494598923615</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2698,13 +2698,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.835304050925</v>
+        <v>46079.66863738426</v>
       </c>
       <c r="C23" s="8">
-        <v>46128.43184210648</v>
+        <v>46128.26517543981</v>
       </c>
       <c r="D23" s="8">
-        <v>46129.00161702547</v>
+        <v>46128.834950358796</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2763,11 +2763,11 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.83530122685</v>
+        <v>46079.668634560185</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46196.639933819446</v>
+        <v>46196.473267152774</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2826,13 +2826,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.87430951389</v>
+        <v>46079.70764284722</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.80111393519</v>
+        <v>46191.634447268516</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.801115636576</v>
+        <v>46191.63444896991</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>102</v>
@@ -2891,13 +2891,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46080.51039956018</v>
+        <v>46080.34373289352</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.801125949074</v>
+        <v>46191.6344592824</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.80112726852</v>
+        <v>46191.634460601854</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2956,11 +2956,11 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.83530158565</v>
+        <v>46079.668634918984</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46191.87501525463</v>
+        <v>46191.70834858796</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -3005,13 +3005,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.83530186342</v>
+        <v>46079.66863519676</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.874819687495</v>
+        <v>46191.70815302084</v>
       </c>
       <c r="D28" s="5">
-        <v>46191.874831574074</v>
+        <v>46191.70816490741</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -3070,13 +3070,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.83530212963</v>
+        <v>46079.668635462964</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.544059004635</v>
+        <v>46097.37739233796</v>
       </c>
       <c r="D29" s="8">
-        <v>46169.848412384265</v>
+        <v>46169.68174571759</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3131,13 +3131,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.83530236111</v>
+        <v>46079.66863569444</v>
       </c>
       <c r="C30" s="5">
-        <v>46191.87480532407</v>
+        <v>46191.70813865741</v>
       </c>
       <c r="D30" s="5">
-        <v>46191.87480704861</v>
+        <v>46191.70814038195</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3192,13 +3192,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.83530269676</v>
+        <v>46079.668636030096</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.874711435186</v>
+        <v>46191.708044768515</v>
       </c>
       <c r="D31" s="8">
-        <v>46198.19648104167</v>
+        <v>46198.029814375</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3257,13 +3257,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.83530295139</v>
+        <v>46079.668636284725</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.67922460648</v>
+        <v>46182.512557939815</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.6792266088</v>
+        <v>46182.51255994213</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3318,13 +3318,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.83530319444</v>
+        <v>46079.66863652778</v>
       </c>
       <c r="C33" s="8">
-        <v>46191.8746965162</v>
+        <v>46191.70802984954</v>
       </c>
       <c r="D33" s="8">
-        <v>46191.874698125</v>
+        <v>46191.70803145833</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3379,13 +3379,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.835301238425</v>
+        <v>46079.66863457176</v>
       </c>
       <c r="C34" s="5">
-        <v>46191.87458894676</v>
+        <v>46191.7079222801</v>
       </c>
       <c r="D34" s="5">
-        <v>46191.874603414355</v>
+        <v>46191.70793674768</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3444,13 +3444,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.835301493054</v>
+        <v>46079.66863482639</v>
       </c>
       <c r="C35" s="8">
-        <v>46114.76627853009</v>
+        <v>46114.59961186342</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.84848269676</v>
+        <v>46169.68181603009</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3505,13 +3505,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.83530179398</v>
+        <v>46079.66863512732</v>
       </c>
       <c r="C36" s="5">
-        <v>46191.87457479167</v>
+        <v>46191.707908125</v>
       </c>
       <c r="D36" s="5">
-        <v>46191.87457655092</v>
+        <v>46191.70790988426</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3566,13 +3566,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.83530215277</v>
+        <v>46079.668635486116</v>
       </c>
       <c r="C37" s="8">
-        <v>46114.81738291666</v>
+        <v>46114.65071625</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.84849621527</v>
+        <v>46169.681829548615</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3627,13 +3627,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46079.83530342593</v>
+        <v>46079.66863675926</v>
       </c>
       <c r="C38" s="5">
-        <v>46191.8749955324</v>
+        <v>46191.708328865745</v>
       </c>
       <c r="D38" s="5">
-        <v>46191.875013136574</v>
+        <v>46191.70834646991</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3692,13 +3692,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46079.83530366898</v>
+        <v>46079.668637002316</v>
       </c>
       <c r="C39" s="8">
-        <v>46191.87447350695</v>
+        <v>46191.70780684028</v>
       </c>
       <c r="D39" s="8">
-        <v>46191.87447540509</v>
+        <v>46191.70780873843</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3753,13 +3753,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.83530085648</v>
+        <v>46079.66863418982</v>
       </c>
       <c r="C40" s="5">
-        <v>46191.87497929398</v>
+        <v>46191.708312627314</v>
       </c>
       <c r="D40" s="5">
-        <v>46191.87498288194</v>
+        <v>46191.70831621528</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3814,13 +3814,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.835302418986</v>
+        <v>46079.668635752314</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.874874120374</v>
+        <v>46191.7082074537</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.874875995374</v>
+        <v>46191.7082093287</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3879,13 +3879,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.83530269676</v>
+        <v>46079.668636030096</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.765637812496</v>
+        <v>46114.59897114584</v>
       </c>
       <c r="D42" s="5">
-        <v>46191.80109314815</v>
+        <v>46191.63442648148</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3940,13 +3940,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.835302962965</v>
+        <v>46079.668636296294</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.76568907408</v>
+        <v>46114.599022407405</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.765690740736</v>
+        <v>46114.59902407408</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -4001,13 +4001,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.87449113426</v>
+        <v>46079.707824467594</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.76610813657</v>
+        <v>46114.59944146991</v>
       </c>
       <c r="D44" s="5">
-        <v>46196.20244436343</v>
+        <v>46196.03577769676</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4066,13 +4066,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.87456693287</v>
+        <v>46079.70790026621</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.7660537037</v>
+        <v>46114.59938703704</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.80111972222</v>
+        <v>46191.63445305555</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4127,13 +4127,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.8746696875</v>
+        <v>46079.70800302083</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.7660946875</v>
+        <v>46114.59942802083</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.766096481486</v>
+        <v>46114.599429814814</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4188,11 +4188,11 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.835303252315</v>
+        <v>46079.668636585644</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46127.68782663194</v>
+        <v>46127.52115996528</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4237,13 +4237,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.8353035301</v>
+        <v>46079.668636863425</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.7954665162</v>
+        <v>46114.62879984954</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.79548327546</v>
+        <v>46114.6288166088</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4302,13 +4302,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.83530068287</v>
+        <v>46079.668634016205</v>
       </c>
       <c r="C49" s="8">
-        <v>46127.68775965278</v>
+        <v>46127.521092986106</v>
       </c>
       <c r="D49" s="8">
-        <v>46156.20046739583</v>
+        <v>46156.03380072917</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4367,13 +4367,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46087.628862847225</v>
+        <v>46087.46219618055</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.68781304398</v>
+        <v>46127.521146377316</v>
       </c>
       <c r="D50" s="5">
-        <v>46158.99592378472</v>
+        <v>46158.82925711806</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4432,11 +4432,11 @@
         <v>187</v>
       </c>
       <c r="B51" s="8">
-        <v>46087.62890292824</v>
+        <v>46087.46223626158</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46127.69021349537</v>
+        <v>46127.5235468287</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>188</v>
@@ -4495,11 +4495,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.835301053245</v>
+        <v>46079.66863438657</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46191.80128876158</v>
+        <v>46191.634622094905</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4548,11 +4548,11 @@
         <v>194</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.835301342595</v>
+        <v>46079.66863467592</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46191.80125251158</v>
+        <v>46191.634585844906</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>195</v>
@@ -4611,11 +4611,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.83530162037</v>
+        <v>46079.668634953705</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46191.80126277778</v>
+        <v>46191.63459611111</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4674,11 +4674,11 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.835301886575</v>
+        <v>46079.6686352199</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46080.57920532407</v>
+        <v>46080.41253865741</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4727,11 +4727,11 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.835302164356</v>
+        <v>46079.668635497685</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46191.80126917824</v>
+        <v>46191.63460251158</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4790,11 +4790,11 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.835302418986</v>
+        <v>46079.668635752314</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.1671537963</v>
+        <v>46191.000487129626</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>212</v>
@@ -4853,11 +4853,11 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.835302673615</v>
+        <v>46079.66863600694</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46193.205434930554</v>
+        <v>46193.03876826389</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -4916,11 +4916,11 @@
         <v>218</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.83530291667</v>
+        <v>46079.668636250004</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46158.99585525463</v>
+        <v>46158.82918858796</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>192</v>
@@ -4969,11 +4969,11 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.83530225694</v>
+        <v>46079.66863559028</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46191.874823923616</v>
+        <v>46191.708157256944</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -5032,11 +5032,11 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.835301851854</v>
+        <v>46079.66863518518</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46192.20217834491</v>
+        <v>46192.035511678245</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>56</v>
@@ -5095,11 +5095,11 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.87589787037</v>
+        <v>46079.7092312037</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.16904811343</v>
+        <v>46198.00238144676</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5158,11 +5158,11 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.83530319444</v>
+        <v>46079.66863652778</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46191.87499096065</v>
+        <v>46191.708324293984</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5221,11 +5221,11 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.83530262731</v>
+        <v>46079.66863596065</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46191.874584930556</v>
+        <v>46191.707918263884</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5284,11 +5284,11 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.835302962965</v>
+        <v>46079.668636296294</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46158.99592380787</v>
+        <v>46158.8292571412</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5337,11 +5337,11 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46079.83530328704</v>
+        <v>46079.66863662037</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46158.99592369213</v>
+        <v>46158.82925702546</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>217</v>
@@ -5400,11 +5400,11 @@
         <v>239</v>
       </c>
       <c r="B67" s="8">
-        <v>46079.83530362268</v>
+        <v>46079.66863695602</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46127.6878281713</v>
+        <v>46127.52116150463</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>240</v>
@@ -5463,11 +5463,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46079.83530398148</v>
+        <v>46079.66863731481</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46127.6878287963</v>
+        <v>46127.52116212963</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5526,11 +5526,11 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46079.835304293985</v>
+        <v>46079.668637627314</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46127.68782931713</v>
+        <v>46127.52116265046</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>248</v>
@@ -5589,11 +5589,11 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46080.49271868056</v>
+        <v>46080.32605201389</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46127.687829814815</v>
+        <v>46127.52116314815</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>251</v>
@@ -5652,11 +5652,11 @@
         <v>253</v>
       </c>
       <c r="B71" s="8">
-        <v>46079.83530460648</v>
+        <v>46079.668637939816</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46158.99592372685</v>
+        <v>46158.829257060184</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>189</v>
@@ -5715,11 +5715,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46079.83530493056</v>
+        <v>46079.66863826389</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46090.804674259256</v>
+        <v>46090.63800759259</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>257</v>
@@ -5778,11 +5778,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46079.83530144676</v>
+        <v>46079.66863478009</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46090.67671023148</v>
+        <v>46090.51004356482</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5825,11 +5825,11 @@
         <v>262</v>
       </c>
       <c r="B74" s="5">
-        <v>46079.83530181713</v>
+        <v>46079.66863515046</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46090.80473224537</v>
+        <v>46090.63806557871</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>263</v>
@@ -5886,11 +5886,11 @@
         <v>265</v>
       </c>
       <c r="B75" s="8">
-        <v>46079.8353024074</v>
+        <v>46079.668635740745</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46097.64290024305</v>
+        <v>46097.47623357639</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>57</v>
@@ -5949,11 +5949,11 @@
         <v>268</v>
       </c>
       <c r="B76" s="5">
-        <v>46079.83530269676</v>
+        <v>46079.668636030096</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.80487153935</v>
+        <v>46090.63820487268</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>269</v>
@@ -6012,11 +6012,11 @@
         <v>271</v>
       </c>
       <c r="B77" s="8">
-        <v>46079.83530306713</v>
+        <v>46079.66863640046</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46090.80495936342</v>
+        <v>46090.63829269676</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>272</v>
@@ -6075,11 +6075,11 @@
         <v>274</v>
       </c>
       <c r="B78" s="5">
-        <v>46079.83530333333</v>
+        <v>46079.66863666667</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46090.67667782407</v>
+        <v>46090.51001115741</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>275</v>
@@ -6122,11 +6122,11 @@
         <v>277</v>
       </c>
       <c r="B79" s="8">
-        <v>46079.83530363426</v>
+        <v>46079.66863696759</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.805033425924</v>
+        <v>46090.63836675926</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>278</v>
@@ -6185,11 +6185,11 @@
         <v>281</v>
       </c>
       <c r="B80" s="5">
-        <v>46079.83530395833</v>
+        <v>46079.66863729167</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.51489402778</v>
+        <v>46114.348227361115</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>282</v>
@@ -6248,11 +6248,11 @@
         <v>284</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.6740474074</v>
+        <v>46090.507380740746</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.6782175</v>
+        <v>46090.51155083333</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>285</v>
@@ -6301,11 +6301,11 @@
         <v>287</v>
       </c>
       <c r="B82" s="5">
-        <v>46090.674231365745</v>
+        <v>46090.50756469907</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46090.80510871528</v>
+        <v>46090.638442048614</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>288</v>
@@ -6364,11 +6364,11 @@
         <v>290</v>
       </c>
       <c r="B83" s="8">
-        <v>46090.67444209491</v>
+        <v>46090.50777542824</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46090.80510556713</v>
+        <v>46090.63843890047</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>291</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -1523,13 +1523,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.668634560185</v>
+        <v>46079.83530122685</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.54858754629</v>
+        <v>46092.71525421296</v>
       </c>
       <c r="D4" s="5">
-        <v>46128.42978174768</v>
+        <v>46128.59644841435</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1572,13 +1572,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.66863482639</v>
+        <v>46079.835301493054</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.548555138885</v>
+        <v>46092.715221805556</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.548588645834</v>
+        <v>46092.715255312505</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1637,13 +1637,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.66863506944</v>
+        <v>46079.83530173611</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.54855576389</v>
+        <v>46092.71522243056</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.548587997684</v>
+        <v>46092.71525466435</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1702,13 +1702,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.66863528935</v>
+        <v>46079.835301956016</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.54855623843</v>
+        <v>46092.71522290509</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.54858858796</v>
+        <v>46092.71525525463</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1767,13 +1767,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.66863550926</v>
+        <v>46079.835302175925</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.548556724534</v>
+        <v>46092.715223391206</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.43571546296</v>
+        <v>46128.602382129626</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1832,13 +1832,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.66863571759</v>
+        <v>46079.835302384265</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.54855746528</v>
+        <v>46092.71522413194</v>
       </c>
       <c r="D9" s="8">
-        <v>46128.42986638889</v>
+        <v>46128.596533055555</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1897,11 +1897,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.6686359375</v>
+        <v>46079.835302604166</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46142.494600081016</v>
+        <v>46142.66126674769</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1944,13 +1944,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.66863619213</v>
+        <v>46079.835302858795</v>
       </c>
       <c r="C11" s="8">
-        <v>46142.4945922801</v>
+        <v>46142.661258946755</v>
       </c>
       <c r="D11" s="8">
-        <v>46142.494593958334</v>
+        <v>46142.661260625</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -2009,11 +2009,11 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.66863646991</v>
+        <v>46079.83530313657</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46133.41044717593</v>
+        <v>46133.57711384259</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2072,13 +2072,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46079.668636689814</v>
+        <v>46079.83530335648</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.34823659722</v>
+        <v>46114.51490326389</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.34825142361</v>
+        <v>46114.51491809028</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2125,13 +2125,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46079.668634594906</v>
+        <v>46079.83530126157</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.347688657406</v>
+        <v>46114.51435532408</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.34770583334</v>
+        <v>46114.5143725</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2190,13 +2190,13 @@
         <v>66</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.66863526621</v>
+        <v>46079.83530193287</v>
       </c>
       <c r="C15" s="8">
-        <v>46111.62614576389</v>
+        <v>46111.792812430554</v>
       </c>
       <c r="D15" s="8">
-        <v>46111.62616248842</v>
+        <v>46111.79282915509</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>67</v>
@@ -2255,13 +2255,13 @@
         <v>69</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.66863559028</v>
+        <v>46079.83530225694</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.34779292824</v>
+        <v>46114.51445959491</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.347810555555</v>
+        <v>46114.51447722223</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>70</v>
@@ -2320,13 +2320,13 @@
         <v>72</v>
       </c>
       <c r="B17" s="8">
-        <v>46080.34358465278</v>
+        <v>46080.51025131944</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34815204861</v>
+        <v>46114.51481871528</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.34816729167</v>
+        <v>46114.51483395833</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>73</v>
@@ -2385,13 +2385,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.668635891205</v>
+        <v>46079.83530255787</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.348217025465</v>
+        <v>46114.51488369213</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.34823753472</v>
+        <v>46114.51490420139</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2450,13 +2450,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.668636180555</v>
+        <v>46079.83530284722</v>
       </c>
       <c r="C19" s="8">
-        <v>46128.26519445602</v>
+        <v>46128.431861122684</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.634452071754</v>
+        <v>46191.801118738425</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2503,13 +2503,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.66863646991</v>
+        <v>46079.83530313657</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3773302662</v>
+        <v>46097.54399693287</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.62616730324</v>
+        <v>46111.79283396991</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2568,13 +2568,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.66863677083</v>
+        <v>46079.8353034375</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.34827811342</v>
+        <v>46114.514944780094</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.3482946875</v>
+        <v>46114.514961354165</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2633,13 +2633,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.668637083334</v>
+        <v>46079.83530375</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.34829836806</v>
+        <v>46114.51496503472</v>
       </c>
       <c r="D22" s="5">
-        <v>46142.494598923615</v>
+        <v>46142.66126559028</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2698,13 +2698,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.66863738426</v>
+        <v>46079.835304050925</v>
       </c>
       <c r="C23" s="8">
-        <v>46128.26517543981</v>
+        <v>46128.43184210648</v>
       </c>
       <c r="D23" s="8">
-        <v>46128.834950358796</v>
+        <v>46129.00161702547</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2763,11 +2763,11 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.668634560185</v>
+        <v>46079.83530122685</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46196.473267152774</v>
+        <v>46196.639933819446</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2826,13 +2826,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.70764284722</v>
+        <v>46079.87430951389</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.634447268516</v>
+        <v>46191.80111393519</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.63444896991</v>
+        <v>46191.801115636576</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>102</v>
@@ -2891,13 +2891,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46080.34373289352</v>
+        <v>46080.51039956018</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.6344592824</v>
+        <v>46191.801125949074</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.634460601854</v>
+        <v>46191.80112726852</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2956,11 +2956,11 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.668634918984</v>
+        <v>46079.83530158565</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46191.70834858796</v>
+        <v>46191.87501525463</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -3005,13 +3005,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.66863519676</v>
+        <v>46079.83530186342</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.70815302084</v>
+        <v>46191.874819687495</v>
       </c>
       <c r="D28" s="5">
-        <v>46191.70816490741</v>
+        <v>46191.874831574074</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -3070,13 +3070,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.668635462964</v>
+        <v>46079.83530212963</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.37739233796</v>
+        <v>46097.544059004635</v>
       </c>
       <c r="D29" s="8">
-        <v>46169.68174571759</v>
+        <v>46169.848412384265</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3131,13 +3131,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.66863569444</v>
+        <v>46079.83530236111</v>
       </c>
       <c r="C30" s="5">
-        <v>46191.70813865741</v>
+        <v>46191.87480532407</v>
       </c>
       <c r="D30" s="5">
-        <v>46191.70814038195</v>
+        <v>46191.87480704861</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3192,13 +3192,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.668636030096</v>
+        <v>46079.83530269676</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.708044768515</v>
+        <v>46191.874711435186</v>
       </c>
       <c r="D31" s="8">
-        <v>46198.029814375</v>
+        <v>46198.19648104167</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3257,13 +3257,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.668636284725</v>
+        <v>46079.83530295139</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.512557939815</v>
+        <v>46182.67922460648</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.51255994213</v>
+        <v>46182.6792266088</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3318,13 +3318,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.66863652778</v>
+        <v>46079.83530319444</v>
       </c>
       <c r="C33" s="8">
-        <v>46191.70802984954</v>
+        <v>46191.8746965162</v>
       </c>
       <c r="D33" s="8">
-        <v>46191.70803145833</v>
+        <v>46191.874698125</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3379,13 +3379,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.66863457176</v>
+        <v>46079.835301238425</v>
       </c>
       <c r="C34" s="5">
-        <v>46191.7079222801</v>
+        <v>46191.87458894676</v>
       </c>
       <c r="D34" s="5">
-        <v>46191.70793674768</v>
+        <v>46191.874603414355</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3444,13 +3444,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.66863482639</v>
+        <v>46079.835301493054</v>
       </c>
       <c r="C35" s="8">
-        <v>46114.59961186342</v>
+        <v>46114.76627853009</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.68181603009</v>
+        <v>46169.84848269676</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3505,13 +3505,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.66863512732</v>
+        <v>46079.83530179398</v>
       </c>
       <c r="C36" s="5">
-        <v>46191.707908125</v>
+        <v>46191.87457479167</v>
       </c>
       <c r="D36" s="5">
-        <v>46191.70790988426</v>
+        <v>46191.87457655092</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3566,13 +3566,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.668635486116</v>
+        <v>46079.83530215277</v>
       </c>
       <c r="C37" s="8">
-        <v>46114.65071625</v>
+        <v>46114.81738291666</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.681829548615</v>
+        <v>46169.84849621527</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3627,13 +3627,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46079.66863675926</v>
+        <v>46079.83530342593</v>
       </c>
       <c r="C38" s="5">
-        <v>46191.708328865745</v>
+        <v>46191.8749955324</v>
       </c>
       <c r="D38" s="5">
-        <v>46191.70834646991</v>
+        <v>46191.875013136574</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3692,13 +3692,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46079.668637002316</v>
+        <v>46079.83530366898</v>
       </c>
       <c r="C39" s="8">
-        <v>46191.70780684028</v>
+        <v>46191.87447350695</v>
       </c>
       <c r="D39" s="8">
-        <v>46191.70780873843</v>
+        <v>46191.87447540509</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3753,13 +3753,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.66863418982</v>
+        <v>46079.83530085648</v>
       </c>
       <c r="C40" s="5">
-        <v>46191.708312627314</v>
+        <v>46191.87497929398</v>
       </c>
       <c r="D40" s="5">
-        <v>46191.70831621528</v>
+        <v>46191.87498288194</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3814,13 +3814,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.668635752314</v>
+        <v>46079.835302418986</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.7082074537</v>
+        <v>46191.874874120374</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.7082093287</v>
+        <v>46191.874875995374</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3879,13 +3879,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.668636030096</v>
+        <v>46079.83530269676</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.59897114584</v>
+        <v>46114.765637812496</v>
       </c>
       <c r="D42" s="5">
-        <v>46191.63442648148</v>
+        <v>46191.80109314815</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3940,13 +3940,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.668636296294</v>
+        <v>46079.835302962965</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.599022407405</v>
+        <v>46114.76568907408</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.59902407408</v>
+        <v>46114.765690740736</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -4001,13 +4001,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.707824467594</v>
+        <v>46079.87449113426</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.59944146991</v>
+        <v>46114.76610813657</v>
       </c>
       <c r="D44" s="5">
-        <v>46196.03577769676</v>
+        <v>46196.20244436343</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4066,13 +4066,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.70790026621</v>
+        <v>46079.87456693287</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.59938703704</v>
+        <v>46114.7660537037</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.63445305555</v>
+        <v>46191.80111972222</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4127,13 +4127,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.70800302083</v>
+        <v>46079.8746696875</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.59942802083</v>
+        <v>46114.7660946875</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.599429814814</v>
+        <v>46114.766096481486</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4188,11 +4188,11 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.668636585644</v>
+        <v>46079.835303252315</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46127.52115996528</v>
+        <v>46127.68782663194</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4237,13 +4237,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.668636863425</v>
+        <v>46079.8353035301</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.62879984954</v>
+        <v>46114.7954665162</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.6288166088</v>
+        <v>46114.79548327546</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4302,13 +4302,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.668634016205</v>
+        <v>46079.83530068287</v>
       </c>
       <c r="C49" s="8">
-        <v>46127.521092986106</v>
+        <v>46127.68775965278</v>
       </c>
       <c r="D49" s="8">
-        <v>46156.03380072917</v>
+        <v>46156.20046739583</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4367,13 +4367,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46087.46219618055</v>
+        <v>46087.628862847225</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.521146377316</v>
+        <v>46127.68781304398</v>
       </c>
       <c r="D50" s="5">
-        <v>46158.82925711806</v>
+        <v>46158.99592378472</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4432,11 +4432,11 @@
         <v>187</v>
       </c>
       <c r="B51" s="8">
-        <v>46087.46223626158</v>
+        <v>46087.62890292824</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46127.5235468287</v>
+        <v>46127.69021349537</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>188</v>
@@ -4495,11 +4495,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.66863438657</v>
+        <v>46079.835301053245</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46191.634622094905</v>
+        <v>46191.80128876158</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4548,11 +4548,11 @@
         <v>194</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.66863467592</v>
+        <v>46079.835301342595</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46191.634585844906</v>
+        <v>46191.80125251158</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>195</v>
@@ -4611,11 +4611,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.668634953705</v>
+        <v>46079.83530162037</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46191.63459611111</v>
+        <v>46191.80126277778</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4674,11 +4674,11 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.6686352199</v>
+        <v>46079.835301886575</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46080.41253865741</v>
+        <v>46080.57920532407</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4727,11 +4727,11 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.668635497685</v>
+        <v>46079.835302164356</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46191.63460251158</v>
+        <v>46191.80126917824</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4790,11 +4790,11 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.668635752314</v>
+        <v>46079.835302418986</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.000487129626</v>
+        <v>46191.1671537963</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>212</v>
@@ -4853,11 +4853,11 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.66863600694</v>
+        <v>46079.835302673615</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46193.03876826389</v>
+        <v>46193.205434930554</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -4916,11 +4916,11 @@
         <v>218</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.668636250004</v>
+        <v>46079.83530291667</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46158.82918858796</v>
+        <v>46158.99585525463</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>192</v>
@@ -4969,11 +4969,11 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.66863559028</v>
+        <v>46079.83530225694</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46191.708157256944</v>
+        <v>46191.874823923616</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -5032,11 +5032,11 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.66863518518</v>
+        <v>46079.835301851854</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46192.035511678245</v>
+        <v>46192.20217834491</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>56</v>
@@ -5095,11 +5095,11 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.7092312037</v>
+        <v>46079.87589787037</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.00238144676</v>
+        <v>46198.16904811343</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5158,11 +5158,11 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.66863652778</v>
+        <v>46079.83530319444</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46191.708324293984</v>
+        <v>46191.87499096065</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5221,11 +5221,11 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.66863596065</v>
+        <v>46079.83530262731</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46191.707918263884</v>
+        <v>46191.874584930556</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5284,11 +5284,11 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.668636296294</v>
+        <v>46079.835302962965</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46158.8292571412</v>
+        <v>46158.99592380787</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5337,11 +5337,11 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46079.66863662037</v>
+        <v>46079.83530328704</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46158.82925702546</v>
+        <v>46158.99592369213</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>217</v>
@@ -5400,11 +5400,11 @@
         <v>239</v>
       </c>
       <c r="B67" s="8">
-        <v>46079.66863695602</v>
+        <v>46079.83530362268</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46127.52116150463</v>
+        <v>46127.6878281713</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>240</v>
@@ -5463,11 +5463,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46079.66863731481</v>
+        <v>46079.83530398148</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46127.52116212963</v>
+        <v>46127.6878287963</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5526,11 +5526,11 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46079.668637627314</v>
+        <v>46079.835304293985</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46127.52116265046</v>
+        <v>46127.68782931713</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>248</v>
@@ -5589,11 +5589,11 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46080.32605201389</v>
+        <v>46080.49271868056</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46127.52116314815</v>
+        <v>46127.687829814815</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>251</v>
@@ -5652,11 +5652,11 @@
         <v>253</v>
       </c>
       <c r="B71" s="8">
-        <v>46079.668637939816</v>
+        <v>46079.83530460648</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46158.829257060184</v>
+        <v>46158.99592372685</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>189</v>
@@ -5715,11 +5715,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46079.66863826389</v>
+        <v>46079.83530493056</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46090.63800759259</v>
+        <v>46090.804674259256</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>257</v>
@@ -5778,11 +5778,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46079.66863478009</v>
+        <v>46079.83530144676</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46090.51004356482</v>
+        <v>46090.67671023148</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5825,11 +5825,11 @@
         <v>262</v>
       </c>
       <c r="B74" s="5">
-        <v>46079.66863515046</v>
+        <v>46079.83530181713</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46090.63806557871</v>
+        <v>46090.80473224537</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>263</v>
@@ -5886,11 +5886,11 @@
         <v>265</v>
       </c>
       <c r="B75" s="8">
-        <v>46079.668635740745</v>
+        <v>46079.8353024074</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46097.47623357639</v>
+        <v>46097.64290024305</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>57</v>
@@ -5949,11 +5949,11 @@
         <v>268</v>
       </c>
       <c r="B76" s="5">
-        <v>46079.668636030096</v>
+        <v>46079.83530269676</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.63820487268</v>
+        <v>46090.80487153935</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>269</v>
@@ -6012,11 +6012,11 @@
         <v>271</v>
       </c>
       <c r="B77" s="8">
-        <v>46079.66863640046</v>
+        <v>46079.83530306713</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46090.63829269676</v>
+        <v>46090.80495936342</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>272</v>
@@ -6075,11 +6075,11 @@
         <v>274</v>
       </c>
       <c r="B78" s="5">
-        <v>46079.66863666667</v>
+        <v>46079.83530333333</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46090.51001115741</v>
+        <v>46090.67667782407</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>275</v>
@@ -6122,11 +6122,11 @@
         <v>277</v>
       </c>
       <c r="B79" s="8">
-        <v>46079.66863696759</v>
+        <v>46079.83530363426</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.63836675926</v>
+        <v>46090.805033425924</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>278</v>
@@ -6185,11 +6185,11 @@
         <v>281</v>
       </c>
       <c r="B80" s="5">
-        <v>46079.66863729167</v>
+        <v>46079.83530395833</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.348227361115</v>
+        <v>46114.51489402778</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>282</v>
@@ -6248,11 +6248,11 @@
         <v>284</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.507380740746</v>
+        <v>46090.6740474074</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.51155083333</v>
+        <v>46090.6782175</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>285</v>
@@ -6301,11 +6301,11 @@
         <v>287</v>
       </c>
       <c r="B82" s="5">
-        <v>46090.50756469907</v>
+        <v>46090.674231365745</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46090.638442048614</v>
+        <v>46090.80510871528</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>288</v>
@@ -6364,11 +6364,11 @@
         <v>290</v>
       </c>
       <c r="B83" s="8">
-        <v>46090.50777542824</v>
+        <v>46090.67444209491</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46090.63843890047</v>
+        <v>46090.80510556713</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>291</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -200,171 +200,174 @@
     <t>Tarea sin iniciar</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1213459189153314</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Damper,Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete,Analisis de costeo</t>
+  </si>
+  <si>
+    <t>1213459189153315</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
+  </si>
+  <si>
+    <t>1213459189153317</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
+  </si>
+  <si>
+    <t>1213459189153318</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta compras a codigo // aprovisionamiento,Propuesta Sensores,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1213458011369803</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Damper</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Propuesta Damper,Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>1213459189153319</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Damper,Ingenieria Basica Motor,Ingenieria Detalle,Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Costos</t>
+  </si>
+  <si>
+    <t>1213459189153320</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta motor,propuesta alabes,propuesta nucleo rodete,propuesta tableros,propuesta compras a codigo // aprovisionamiento,Propuesta Sensores</t>
+  </si>
+  <si>
+    <t>1213459189153321</t>
+  </si>
+  <si>
+    <t>propuesta alabes</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe ot 4264</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1213459189153322</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC motor ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189153323</t>
+  </si>
+  <si>
+    <t>propuesta tableros</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Tableros  ot 4265 - ot 4266</t>
+  </si>
+  <si>
+    <t>1213459189153324</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189153325</t>
+  </si>
+  <si>
+    <t>propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales</t>
+  </si>
+  <si>
+    <t>1213458788103036</t>
+  </si>
+  <si>
+    <t>Propuesta Sensores</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Sensores</t>
+  </si>
+  <si>
+    <t>1213458011369804</t>
+  </si>
+  <si>
+    <t>Propuesta Damper</t>
+  </si>
+  <si>
+    <t>1213459189153326</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Sensores,Materiales a codigo // compras locales aprovisionamientomiento:,rodete ot 4264,Tablero ot 4265 - ot 4266,Motor ot 4264,Alabe  ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189153327</t>
+  </si>
+  <si>
+    <t>Alabe  ot 4264</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe ot 4264,Fabricación Alabe ot 4264</t>
+  </si>
+  <si>
     <t>Baja</t>
   </si>
   <si>
-    <t>1213459189153314</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Damper,Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213459189153315</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
-  </si>
-  <si>
-    <t>1213459189153317</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
-  </si>
-  <si>
-    <t>1213459189153318</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta compras a codigo // aprovisionamiento,Propuesta Sensores,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1213458011369803</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Damper</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Propuesta Damper,Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>1213459189153319</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Damper,Ingenieria Basica Motor,Ingenieria Detalle,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>1213459189153320</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta motor,propuesta alabes,propuesta nucleo rodete,propuesta tableros,propuesta compras a codigo // aprovisionamiento,Propuesta Sensores</t>
-  </si>
-  <si>
-    <t>1213459189153321</t>
-  </si>
-  <si>
-    <t>propuesta alabes</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe ot 4264</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213459189153322</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC motor ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189153323</t>
-  </si>
-  <si>
-    <t>propuesta tableros</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Tableros  ot 4265 - ot 4266</t>
-  </si>
-  <si>
-    <t>1213459189153324</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189153325</t>
-  </si>
-  <si>
-    <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales</t>
-  </si>
-  <si>
-    <t>1213458788103036</t>
-  </si>
-  <si>
-    <t>Propuesta Sensores</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Sensores</t>
-  </si>
-  <si>
-    <t>1213458011369804</t>
-  </si>
-  <si>
-    <t>Propuesta Damper</t>
-  </si>
-  <si>
-    <t>1213459189153326</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Sensores,Materiales a codigo // compras locales aprovisionamientomiento:,rodete ot 4264,Tablero ot 4265 - ot 4266,Motor ot 4264,Alabe  ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189153327</t>
-  </si>
-  <si>
-    <t>Alabe  ot 4264</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe ot 4264,Fabricación Alabe ot 4264</t>
-  </si>
-  <si>
     <t>1213459189153328</t>
   </si>
   <si>
@@ -513,9 +516,6 @@
   </si>
   <si>
     <t>Generación OC Sensores,Fabricacion Sensores</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213458788103039</t>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46133.57711384259</v>
+        <v>46199.18484332176</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2063,7 +2063,7 @@
       <c r="T12" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="U12" s="10" t="s">
+      <c r="U12" s="12" t="s">
         <v>59</v>
       </c>
     </row>
@@ -3062,12 +3062,12 @@
         <v>31</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="8">
         <v>46079.83530212963</v>
@@ -3079,7 +3079,7 @@
         <v>46169.848412384265</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3112,7 +3112,7 @@
         <v>83</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3123,12 +3123,12 @@
         <v>58</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46079.83530236111</v>
@@ -3140,7 +3140,7 @@
         <v>46191.87480704861</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3170,10 +3170,10 @@
         <v>110</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3184,12 +3184,12 @@
         <v>58</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="8">
         <v>46079.83530269676</v>
@@ -3201,7 +3201,7 @@
         <v>46198.19648104167</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3231,7 +3231,7 @@
         <v>107</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>107</v>
@@ -3254,7 +3254,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46079.83530295139</v>
@@ -3266,7 +3266,7 @@
         <v>46182.6792266088</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3293,13 +3293,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>90</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3310,12 +3310,12 @@
         <v>58</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46079.83530319444</v>
@@ -3327,7 +3327,7 @@
         <v>46191.874698125</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3354,13 +3354,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3371,12 +3371,12 @@
         <v>58</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46079.835301238425</v>
@@ -3388,7 +3388,7 @@
         <v>46191.874603414355</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3418,7 +3418,7 @@
         <v>107</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>107</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B35" s="8">
         <v>46079.835301493054</v>
@@ -3453,7 +3453,7 @@
         <v>46169.84848269676</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3480,13 +3480,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>87</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3497,12 +3497,12 @@
         <v>58</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46079.83530179398</v>
@@ -3514,7 +3514,7 @@
         <v>46191.87457655092</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3541,13 +3541,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3558,12 +3558,12 @@
         <v>58</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="8">
         <v>46079.83530215277</v>
@@ -3575,7 +3575,7 @@
         <v>46169.84849621527</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -3602,13 +3602,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3619,12 +3619,12 @@
         <v>58</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46079.83530342593</v>
@@ -3636,7 +3636,7 @@
         <v>46191.875013136574</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3666,7 +3666,7 @@
         <v>107</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>107</v>
@@ -3689,7 +3689,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>46079.83530366898</v>
@@ -3701,7 +3701,7 @@
         <v>46191.87447540509</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
@@ -3728,13 +3728,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>93</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3745,12 +3745,12 @@
         <v>58</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46079.83530085648</v>
@@ -3762,7 +3762,7 @@
         <v>46191.87498288194</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -3789,13 +3789,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3806,12 +3806,12 @@
         <v>58</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46079.835302418986</v>
@@ -3823,16 +3823,16 @@
         <v>46191.874875995374</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I41" s="8">
         <v>46097</v>
@@ -3853,7 +3853,7 @@
         <v>107</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>107</v>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46079.83530269676</v>
@@ -3888,16 +3888,16 @@
         <v>46191.80109314815</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I42" s="5">
         <v>46097</v>
@@ -3915,13 +3915,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3932,12 +3932,12 @@
         <v>58</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46079.835302962965</v>
@@ -3949,16 +3949,16 @@
         <v>46114.765690740736</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I43" s="8">
         <v>46115</v>
@@ -3976,13 +3976,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3993,12 +3993,12 @@
         <v>58</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46079.87449113426</v>
@@ -4010,16 +4010,16 @@
         <v>46196.20244436343</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I44" s="5">
         <v>46097</v>
@@ -4040,7 +4040,7 @@
         <v>107</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>107</v>
@@ -4058,7 +4058,7 @@
         <v>31</v>
       </c>
       <c r="U44" s="12" t="s">
-        <v>164</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4081,10 +4081,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I45" s="8">
         <v>46097</v>
@@ -4102,7 +4102,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>102</v>
@@ -4119,7 +4119,7 @@
         <v>58</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4142,10 +4142,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I46" s="5">
         <v>46126</v>
@@ -4163,7 +4163,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>166</v>
@@ -4180,7 +4180,7 @@
         <v>58</v>
       </c>
       <c r="U46" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4487,7 +4487,7 @@
         <v>58</v>
       </c>
       <c r="U51" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4540,7 +4540,7 @@
         <v>31</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4585,7 +4585,7 @@
         <v>192</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>198</v>
@@ -4719,7 +4719,7 @@
         <v>58</v>
       </c>
       <c r="U55" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4961,7 +4961,7 @@
         <v>58</v>
       </c>
       <c r="U59" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5006,7 +5006,7 @@
         <v>192</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>222</v>
@@ -5024,7 +5024,7 @@
         <v>85</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46192.20217834491</v>
+        <v>46199.25029855324</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>56</v>
@@ -5069,7 +5069,7 @@
         <v>192</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>224</v>
@@ -5087,7 +5087,7 @@
         <v>85</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>164</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5150,7 +5150,7 @@
         <v>85</v>
       </c>
       <c r="U62" s="12" t="s">
-        <v>164</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5195,7 +5195,7 @@
         <v>192</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>230</v>
@@ -5258,7 +5258,7 @@
         <v>192</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>233</v>
@@ -5276,7 +5276,7 @@
         <v>85</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5329,7 +5329,7 @@
         <v>58</v>
       </c>
       <c r="U65" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5392,7 +5392,7 @@
         <v>58</v>
       </c>
       <c r="U66" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5455,7 +5455,7 @@
         <v>58</v>
       </c>
       <c r="U67" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5518,7 +5518,7 @@
         <v>58</v>
       </c>
       <c r="U68" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5581,7 +5581,7 @@
         <v>58</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5644,7 +5644,7 @@
         <v>58</v>
       </c>
       <c r="U70" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5707,7 +5707,7 @@
         <v>58</v>
       </c>
       <c r="U71" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5770,7 +5770,7 @@
         <v>58</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5878,7 +5878,7 @@
         <v>58</v>
       </c>
       <c r="U74" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5941,7 +5941,7 @@
         <v>58</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6004,7 +6004,7 @@
         <v>58</v>
       </c>
       <c r="U76" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6067,7 +6067,7 @@
         <v>58</v>
       </c>
       <c r="U77" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6177,7 +6177,7 @@
         <v>58</v>
       </c>
       <c r="U79" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6240,7 +6240,7 @@
         <v>58</v>
       </c>
       <c r="U80" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6293,7 +6293,7 @@
         <v>58</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6356,7 +6356,7 @@
         <v>58</v>
       </c>
       <c r="U82" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6419,7 +6419,7 @@
         <v>58</v>
       </c>
       <c r="U83" s="10" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -5036,7 +5036,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46199.25029855324</v>
+        <v>46200.20831664352</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>56</v>
@@ -5086,8 +5086,8 @@
       <c r="T61" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="U61" s="12" t="s">
-        <v>59</v>
+      <c r="U61" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -365,16 +365,16 @@
     <t>Generación OC Alabe ot 4264,Fabricación Alabe ot 4264</t>
   </si>
   <si>
+    <t>1213459189153328</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe ot 4264</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe ot 4264,Alabe  ot 4264</t>
+  </si>
+  <si>
     <t>Baja</t>
-  </si>
-  <si>
-    <t>1213459189153328</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe ot 4264</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe ot 4264,Alabe  ot 4264</t>
   </si>
   <si>
     <t>1213459189153329</t>
@@ -3011,7 +3011,7 @@
         <v>46191.874819687495</v>
       </c>
       <c r="D28" s="5">
-        <v>46191.874831574074</v>
+        <v>46204.193195381944</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -3061,13 +3061,13 @@
       <c r="T28" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U28" s="10" t="s">
-        <v>114</v>
+      <c r="U28" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46079.83530212963</v>
@@ -3079,7 +3079,7 @@
         <v>46169.848412384265</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3112,7 +3112,7 @@
         <v>83</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3123,7 +3123,7 @@
         <v>58</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3170,7 +3170,7 @@
         <v>110</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>120</v>
@@ -3184,7 +3184,7 @@
         <v>58</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3310,7 +3310,7 @@
         <v>58</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3371,7 +3371,7 @@
         <v>58</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3497,7 +3497,7 @@
         <v>58</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3558,7 +3558,7 @@
         <v>58</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3619,7 +3619,7 @@
         <v>58</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -3745,7 +3745,7 @@
         <v>58</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -3806,7 +3806,7 @@
         <v>58</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -3932,7 +3932,7 @@
         <v>58</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -3993,7 +3993,7 @@
         <v>58</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4007,7 +4007,7 @@
         <v>46114.76610813657</v>
       </c>
       <c r="D44" s="5">
-        <v>46196.20244436343</v>
+        <v>46204.18561212963</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4057,8 +4057,8 @@
       <c r="T44" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U44" s="12" t="s">
-        <v>59</v>
+      <c r="U44" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4119,7 +4119,7 @@
         <v>58</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4180,7 +4180,7 @@
         <v>58</v>
       </c>
       <c r="U46" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4487,7 +4487,7 @@
         <v>58</v>
       </c>
       <c r="U51" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4540,7 +4540,7 @@
         <v>31</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4719,7 +4719,7 @@
         <v>58</v>
       </c>
       <c r="U55" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4961,7 +4961,7 @@
         <v>58</v>
       </c>
       <c r="U59" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5024,7 +5024,7 @@
         <v>85</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5276,7 +5276,7 @@
         <v>85</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5329,7 +5329,7 @@
         <v>58</v>
       </c>
       <c r="U65" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5392,7 +5392,7 @@
         <v>58</v>
       </c>
       <c r="U66" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5455,7 +5455,7 @@
         <v>58</v>
       </c>
       <c r="U67" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5518,7 +5518,7 @@
         <v>58</v>
       </c>
       <c r="U68" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5581,7 +5581,7 @@
         <v>58</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5644,7 +5644,7 @@
         <v>58</v>
       </c>
       <c r="U70" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5707,7 +5707,7 @@
         <v>58</v>
       </c>
       <c r="U71" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5770,7 +5770,7 @@
         <v>58</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5878,7 +5878,7 @@
         <v>58</v>
       </c>
       <c r="U74" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5941,7 +5941,7 @@
         <v>58</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6004,7 +6004,7 @@
         <v>58</v>
       </c>
       <c r="U76" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6067,7 +6067,7 @@
         <v>58</v>
       </c>
       <c r="U77" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6177,7 +6177,7 @@
         <v>58</v>
       </c>
       <c r="U79" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6240,7 +6240,7 @@
         <v>58</v>
       </c>
       <c r="U80" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6293,7 +6293,7 @@
         <v>58</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6356,7 +6356,7 @@
         <v>58</v>
       </c>
       <c r="U82" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6419,7 +6419,7 @@
         <v>58</v>
       </c>
       <c r="U83" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -269,6 +269,9 @@
     <t>propuesta motor,propuesta alabes,propuesta nucleo rodete,propuesta tableros,propuesta compras a codigo // aprovisionamiento,Propuesta Sensores</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1213459189153321</t>
   </si>
   <si>
@@ -276,9 +279,6 @@
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Alabe ot 4264</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213459189153322</t>
@@ -2456,7 +2456,7 @@
         <v>46128.431861122684</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.801118738425</v>
+        <v>46204.90569222222</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2493,14 +2493,14 @@
       <c r="S19" s="9">
         <v>1</v>
       </c>
-      <c r="T19" s="10" t="s">
-        <v>31</v>
+      <c r="T19" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="U19" s="9"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" s="5">
         <v>46079.83530313657</v>
@@ -2512,7 +2512,7 @@
         <v>46111.79283396991</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2545,7 +2545,7 @@
         <v>67</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="5">
         <v>46093</v>
@@ -2557,7 +2557,7 @@
         <v>1</v>
       </c>
       <c r="T20" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="U20" s="11" t="s">
         <v>32</v>
@@ -2765,9 +2765,11 @@
       <c r="B24" s="5">
         <v>46079.83530122685</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="5">
+        <v>46204.90566989583</v>
+      </c>
       <c r="D24" s="5">
-        <v>46196.639933819446</v>
+        <v>46204.90567366898</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2996,7 +2998,7 @@
       <c r="R27" s="9"/>
       <c r="S27" s="9"/>
       <c r="T27" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="U27" s="9"/>
     </row>
@@ -3109,7 +3111,7 @@
         <v>110</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>116</v>
@@ -3433,7 +3435,7 @@
         <v>1</v>
       </c>
       <c r="T34" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="U34" s="11" t="s">
         <v>32</v>
@@ -3885,7 +3887,7 @@
         <v>46114.765637812496</v>
       </c>
       <c r="D42" s="5">
-        <v>46191.80109314815</v>
+        <v>46204.90568498842</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -4663,7 +4665,7 @@
         <v>1</v>
       </c>
       <c r="T54" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="U54" s="11" t="s">
         <v>32</v>
@@ -4779,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="T56" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="U56" s="11" t="s">
         <v>32</v>
@@ -5021,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="T60" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="U60" s="10" t="s">
         <v>117</v>
@@ -5084,7 +5086,7 @@
         <v>0</v>
       </c>
       <c r="T61" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="U61" s="11" t="s">
         <v>32</v>
@@ -5147,7 +5149,7 @@
         <v>0</v>
       </c>
       <c r="T62" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="U62" s="12" t="s">
         <v>59</v>
@@ -5210,7 +5212,7 @@
         <v>0</v>
       </c>
       <c r="T63" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="U63" s="11" t="s">
         <v>32</v>
@@ -5273,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="T64" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="U64" s="10" t="s">
         <v>117</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -1523,13 +1523,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.83530122685</v>
+        <v>46079.668634560185</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.71525421296</v>
+        <v>46092.54858754629</v>
       </c>
       <c r="D4" s="5">
-        <v>46128.59644841435</v>
+        <v>46128.42978174768</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1572,13 +1572,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.835301493054</v>
+        <v>46079.66863482639</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.715221805556</v>
+        <v>46092.548555138885</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.715255312505</v>
+        <v>46092.548588645834</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1637,13 +1637,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.83530173611</v>
+        <v>46079.66863506944</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.71522243056</v>
+        <v>46092.54855576389</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.71525466435</v>
+        <v>46092.548587997684</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1702,13 +1702,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.835301956016</v>
+        <v>46079.66863528935</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71522290509</v>
+        <v>46092.54855623843</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.71525525463</v>
+        <v>46092.54858858796</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1767,13 +1767,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.835302175925</v>
+        <v>46079.66863550926</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.715223391206</v>
+        <v>46092.548556724534</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.602382129626</v>
+        <v>46128.43571546296</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1832,13 +1832,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.835302384265</v>
+        <v>46079.66863571759</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71522413194</v>
+        <v>46092.54855746528</v>
       </c>
       <c r="D9" s="8">
-        <v>46128.596533055555</v>
+        <v>46128.42986638889</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1897,11 +1897,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.835302604166</v>
+        <v>46079.6686359375</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46142.66126674769</v>
+        <v>46142.494600081016</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1944,13 +1944,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.835302858795</v>
+        <v>46079.66863619213</v>
       </c>
       <c r="C11" s="8">
-        <v>46142.661258946755</v>
+        <v>46142.4945922801</v>
       </c>
       <c r="D11" s="8">
-        <v>46142.661260625</v>
+        <v>46142.494593958334</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -2009,11 +2009,11 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.83530313657</v>
+        <v>46079.66863646991</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46199.18484332176</v>
+        <v>46199.018176655096</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2072,13 +2072,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46079.83530335648</v>
+        <v>46079.668636689814</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51490326389</v>
+        <v>46114.34823659722</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.51491809028</v>
+        <v>46114.34825142361</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2125,13 +2125,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46079.83530126157</v>
+        <v>46079.668634594906</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.51435532408</v>
+        <v>46114.347688657406</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.5143725</v>
+        <v>46114.34770583334</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2190,13 +2190,13 @@
         <v>66</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.83530193287</v>
+        <v>46079.66863526621</v>
       </c>
       <c r="C15" s="8">
-        <v>46111.792812430554</v>
+        <v>46111.62614576389</v>
       </c>
       <c r="D15" s="8">
-        <v>46111.79282915509</v>
+        <v>46111.62616248842</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>67</v>
@@ -2255,13 +2255,13 @@
         <v>69</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.83530225694</v>
+        <v>46079.66863559028</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.51445959491</v>
+        <v>46114.34779292824</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.51447722223</v>
+        <v>46114.347810555555</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>70</v>
@@ -2320,13 +2320,13 @@
         <v>72</v>
       </c>
       <c r="B17" s="8">
-        <v>46080.51025131944</v>
+        <v>46080.34358465278</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.51481871528</v>
+        <v>46114.34815204861</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.51483395833</v>
+        <v>46114.34816729167</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>73</v>
@@ -2385,13 +2385,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.83530255787</v>
+        <v>46079.668635891205</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.51488369213</v>
+        <v>46114.348217025465</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.51490420139</v>
+        <v>46114.34823753472</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2450,13 +2450,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.83530284722</v>
+        <v>46079.668636180555</v>
       </c>
       <c r="C19" s="8">
-        <v>46128.431861122684</v>
+        <v>46128.26519445602</v>
       </c>
       <c r="D19" s="8">
-        <v>46204.90569222222</v>
+        <v>46204.73902555555</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2503,13 +2503,13 @@
         <v>83</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.83530313657</v>
+        <v>46079.66863646991</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.54399693287</v>
+        <v>46097.3773302662</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.79283396991</v>
+        <v>46111.62616730324</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>84</v>
@@ -2568,13 +2568,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.8353034375</v>
+        <v>46079.66863677083</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.514944780094</v>
+        <v>46114.34827811342</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.514961354165</v>
+        <v>46114.3482946875</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2633,13 +2633,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.83530375</v>
+        <v>46079.668637083334</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.51496503472</v>
+        <v>46114.34829836806</v>
       </c>
       <c r="D22" s="5">
-        <v>46142.66126559028</v>
+        <v>46142.494598923615</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2698,13 +2698,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.835304050925</v>
+        <v>46079.66863738426</v>
       </c>
       <c r="C23" s="8">
-        <v>46128.43184210648</v>
+        <v>46128.26517543981</v>
       </c>
       <c r="D23" s="8">
-        <v>46129.00161702547</v>
+        <v>46128.834950358796</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2763,13 +2763,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.83530122685</v>
+        <v>46079.668634560185</v>
       </c>
       <c r="C24" s="5">
-        <v>46204.90566989583</v>
+        <v>46204.739003229166</v>
       </c>
       <c r="D24" s="5">
-        <v>46204.90567366898</v>
+        <v>46204.73900700231</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2828,13 +2828,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.87430951389</v>
+        <v>46079.70764284722</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.80111393519</v>
+        <v>46191.634447268516</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.801115636576</v>
+        <v>46191.63444896991</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>102</v>
@@ -2893,13 +2893,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46080.51039956018</v>
+        <v>46080.34373289352</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.801125949074</v>
+        <v>46191.6344592824</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.80112726852</v>
+        <v>46191.634460601854</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2958,11 +2958,11 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.83530158565</v>
+        <v>46079.668634918984</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46191.87501525463</v>
+        <v>46191.70834858796</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -3007,13 +3007,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.83530186342</v>
+        <v>46079.66863519676</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.874819687495</v>
+        <v>46191.70815302084</v>
       </c>
       <c r="D28" s="5">
-        <v>46204.193195381944</v>
+        <v>46204.02652871527</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -3072,13 +3072,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.83530212963</v>
+        <v>46079.668635462964</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.544059004635</v>
+        <v>46097.37739233796</v>
       </c>
       <c r="D29" s="8">
-        <v>46169.848412384265</v>
+        <v>46169.68174571759</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3133,13 +3133,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.83530236111</v>
+        <v>46079.66863569444</v>
       </c>
       <c r="C30" s="5">
-        <v>46191.87480532407</v>
+        <v>46191.70813865741</v>
       </c>
       <c r="D30" s="5">
-        <v>46191.87480704861</v>
+        <v>46191.70814038195</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3194,13 +3194,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.83530269676</v>
+        <v>46079.668636030096</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.874711435186</v>
+        <v>46191.708044768515</v>
       </c>
       <c r="D31" s="8">
-        <v>46198.19648104167</v>
+        <v>46198.029814375</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3259,13 +3259,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.83530295139</v>
+        <v>46079.668636284725</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.67922460648</v>
+        <v>46182.512557939815</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.6792266088</v>
+        <v>46182.51255994213</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3320,13 +3320,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.83530319444</v>
+        <v>46079.66863652778</v>
       </c>
       <c r="C33" s="8">
-        <v>46191.8746965162</v>
+        <v>46191.70802984954</v>
       </c>
       <c r="D33" s="8">
-        <v>46191.874698125</v>
+        <v>46191.70803145833</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3381,13 +3381,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.835301238425</v>
+        <v>46079.66863457176</v>
       </c>
       <c r="C34" s="5">
-        <v>46191.87458894676</v>
+        <v>46191.7079222801</v>
       </c>
       <c r="D34" s="5">
-        <v>46191.874603414355</v>
+        <v>46191.70793674768</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3446,13 +3446,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.835301493054</v>
+        <v>46079.66863482639</v>
       </c>
       <c r="C35" s="8">
-        <v>46114.76627853009</v>
+        <v>46114.59961186342</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.84848269676</v>
+        <v>46169.68181603009</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3507,13 +3507,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.83530179398</v>
+        <v>46079.66863512732</v>
       </c>
       <c r="C36" s="5">
-        <v>46191.87457479167</v>
+        <v>46191.707908125</v>
       </c>
       <c r="D36" s="5">
-        <v>46191.87457655092</v>
+        <v>46191.70790988426</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3568,13 +3568,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.83530215277</v>
+        <v>46079.668635486116</v>
       </c>
       <c r="C37" s="8">
-        <v>46114.81738291666</v>
+        <v>46114.65071625</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.84849621527</v>
+        <v>46169.681829548615</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3629,13 +3629,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46079.83530342593</v>
+        <v>46079.66863675926</v>
       </c>
       <c r="C38" s="5">
-        <v>46191.8749955324</v>
+        <v>46191.708328865745</v>
       </c>
       <c r="D38" s="5">
-        <v>46191.875013136574</v>
+        <v>46191.70834646991</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3694,13 +3694,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46079.83530366898</v>
+        <v>46079.668637002316</v>
       </c>
       <c r="C39" s="8">
-        <v>46191.87447350695</v>
+        <v>46191.70780684028</v>
       </c>
       <c r="D39" s="8">
-        <v>46191.87447540509</v>
+        <v>46191.70780873843</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3755,13 +3755,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.83530085648</v>
+        <v>46079.66863418982</v>
       </c>
       <c r="C40" s="5">
-        <v>46191.87497929398</v>
+        <v>46191.708312627314</v>
       </c>
       <c r="D40" s="5">
-        <v>46191.87498288194</v>
+        <v>46191.70831621528</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3816,13 +3816,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.835302418986</v>
+        <v>46079.668635752314</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.874874120374</v>
+        <v>46191.7082074537</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.874875995374</v>
+        <v>46191.7082093287</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3881,13 +3881,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.83530269676</v>
+        <v>46079.668636030096</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.765637812496</v>
+        <v>46114.59897114584</v>
       </c>
       <c r="D42" s="5">
-        <v>46204.90568498842</v>
+        <v>46204.73901832176</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3942,13 +3942,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.835302962965</v>
+        <v>46079.668636296294</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.76568907408</v>
+        <v>46114.599022407405</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.765690740736</v>
+        <v>46114.59902407408</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4003,13 +4003,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.87449113426</v>
+        <v>46079.707824467594</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.76610813657</v>
+        <v>46114.59944146991</v>
       </c>
       <c r="D44" s="5">
-        <v>46204.18561212963</v>
+        <v>46204.01894546296</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4068,13 +4068,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.87456693287</v>
+        <v>46079.70790026621</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.7660537037</v>
+        <v>46114.59938703704</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.80111972222</v>
+        <v>46191.63445305555</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4129,13 +4129,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.8746696875</v>
+        <v>46079.70800302083</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.7660946875</v>
+        <v>46114.59942802083</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.766096481486</v>
+        <v>46114.599429814814</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4190,11 +4190,11 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.835303252315</v>
+        <v>46079.668636585644</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46127.68782663194</v>
+        <v>46127.52115996528</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4239,13 +4239,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.8353035301</v>
+        <v>46079.668636863425</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.7954665162</v>
+        <v>46114.62879984954</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.79548327546</v>
+        <v>46114.6288166088</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4304,13 +4304,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.83530068287</v>
+        <v>46079.668634016205</v>
       </c>
       <c r="C49" s="8">
-        <v>46127.68775965278</v>
+        <v>46127.521092986106</v>
       </c>
       <c r="D49" s="8">
-        <v>46156.20046739583</v>
+        <v>46156.03380072917</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4369,13 +4369,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46087.628862847225</v>
+        <v>46087.46219618055</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.68781304398</v>
+        <v>46127.521146377316</v>
       </c>
       <c r="D50" s="5">
-        <v>46158.99592378472</v>
+        <v>46158.82925711806</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4434,11 +4434,11 @@
         <v>187</v>
       </c>
       <c r="B51" s="8">
-        <v>46087.62890292824</v>
+        <v>46087.46223626158</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46127.69021349537</v>
+        <v>46127.5235468287</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>188</v>
@@ -4497,11 +4497,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.835301053245</v>
+        <v>46079.66863438657</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46191.80128876158</v>
+        <v>46191.634622094905</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4550,11 +4550,11 @@
         <v>194</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.835301342595</v>
+        <v>46079.66863467592</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46191.80125251158</v>
+        <v>46191.634585844906</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>195</v>
@@ -4613,11 +4613,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.83530162037</v>
+        <v>46079.668634953705</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46191.80126277778</v>
+        <v>46191.63459611111</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4676,11 +4676,11 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.835301886575</v>
+        <v>46079.6686352199</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46080.57920532407</v>
+        <v>46080.41253865741</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4729,11 +4729,11 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.835302164356</v>
+        <v>46079.668635497685</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46191.80126917824</v>
+        <v>46191.63460251158</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4792,11 +4792,11 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.835302418986</v>
+        <v>46079.668635752314</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.1671537963</v>
+        <v>46191.000487129626</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>212</v>
@@ -4855,11 +4855,11 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.835302673615</v>
+        <v>46079.66863600694</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46193.205434930554</v>
+        <v>46193.03876826389</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -4918,11 +4918,11 @@
         <v>218</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.83530291667</v>
+        <v>46079.668636250004</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46158.99585525463</v>
+        <v>46158.82918858796</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>192</v>
@@ -4971,11 +4971,11 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.83530225694</v>
+        <v>46079.66863559028</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46191.874823923616</v>
+        <v>46191.708157256944</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -5034,11 +5034,11 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.835301851854</v>
+        <v>46079.66863518518</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46200.20831664352</v>
+        <v>46200.04164997685</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>56</v>
@@ -5097,11 +5097,11 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.87589787037</v>
+        <v>46079.7092312037</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.16904811343</v>
+        <v>46205.08364280092</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5160,11 +5160,11 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.83530319444</v>
+        <v>46079.66863652778</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46191.87499096065</v>
+        <v>46191.708324293984</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5223,11 +5223,11 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.83530262731</v>
+        <v>46079.66863596065</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46191.874584930556</v>
+        <v>46191.707918263884</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5286,11 +5286,11 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.835302962965</v>
+        <v>46079.668636296294</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46158.99592380787</v>
+        <v>46158.8292571412</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5339,11 +5339,11 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46079.83530328704</v>
+        <v>46079.66863662037</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46158.99592369213</v>
+        <v>46205.02663775463</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>217</v>
@@ -5393,8 +5393,8 @@
       <c r="T66" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="U66" s="10" t="s">
-        <v>117</v>
+      <c r="U66" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5402,11 +5402,11 @@
         <v>239</v>
       </c>
       <c r="B67" s="8">
-        <v>46079.83530362268</v>
+        <v>46079.66863695602</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46127.6878281713</v>
+        <v>46127.52116150463</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>240</v>
@@ -5465,11 +5465,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46079.83530398148</v>
+        <v>46079.66863731481</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46127.6878287963</v>
+        <v>46127.52116212963</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5528,11 +5528,11 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46079.835304293985</v>
+        <v>46079.668637627314</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46127.68782931713</v>
+        <v>46127.52116265046</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>248</v>
@@ -5591,11 +5591,11 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46080.49271868056</v>
+        <v>46080.32605201389</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46127.687829814815</v>
+        <v>46127.52116314815</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>251</v>
@@ -5654,11 +5654,11 @@
         <v>253</v>
       </c>
       <c r="B71" s="8">
-        <v>46079.83530460648</v>
+        <v>46079.668637939816</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46158.99592372685</v>
+        <v>46158.829257060184</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>189</v>
@@ -5717,11 +5717,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46079.83530493056</v>
+        <v>46079.66863826389</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46090.804674259256</v>
+        <v>46090.63800759259</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>257</v>
@@ -5780,11 +5780,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46079.83530144676</v>
+        <v>46079.66863478009</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46090.67671023148</v>
+        <v>46090.51004356482</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5827,11 +5827,11 @@
         <v>262</v>
       </c>
       <c r="B74" s="5">
-        <v>46079.83530181713</v>
+        <v>46079.66863515046</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46090.80473224537</v>
+        <v>46090.63806557871</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>263</v>
@@ -5888,11 +5888,11 @@
         <v>265</v>
       </c>
       <c r="B75" s="8">
-        <v>46079.8353024074</v>
+        <v>46079.668635740745</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46097.64290024305</v>
+        <v>46097.47623357639</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>57</v>
@@ -5951,11 +5951,11 @@
         <v>268</v>
       </c>
       <c r="B76" s="5">
-        <v>46079.83530269676</v>
+        <v>46079.668636030096</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.80487153935</v>
+        <v>46090.63820487268</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>269</v>
@@ -6014,11 +6014,11 @@
         <v>271</v>
       </c>
       <c r="B77" s="8">
-        <v>46079.83530306713</v>
+        <v>46079.66863640046</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46090.80495936342</v>
+        <v>46090.63829269676</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>272</v>
@@ -6077,11 +6077,11 @@
         <v>274</v>
       </c>
       <c r="B78" s="5">
-        <v>46079.83530333333</v>
+        <v>46079.66863666667</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46090.67667782407</v>
+        <v>46090.51001115741</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>275</v>
@@ -6124,11 +6124,11 @@
         <v>277</v>
       </c>
       <c r="B79" s="8">
-        <v>46079.83530363426</v>
+        <v>46079.66863696759</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.805033425924</v>
+        <v>46090.63836675926</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>278</v>
@@ -6187,11 +6187,11 @@
         <v>281</v>
       </c>
       <c r="B80" s="5">
-        <v>46079.83530395833</v>
+        <v>46079.66863729167</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.51489402778</v>
+        <v>46114.348227361115</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>282</v>
@@ -6250,11 +6250,11 @@
         <v>284</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.6740474074</v>
+        <v>46090.507380740746</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.6782175</v>
+        <v>46090.51155083333</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>285</v>
@@ -6303,11 +6303,11 @@
         <v>287</v>
       </c>
       <c r="B82" s="5">
-        <v>46090.674231365745</v>
+        <v>46090.50756469907</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46090.80510871528</v>
+        <v>46090.638442048614</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>288</v>
@@ -6366,11 +6366,11 @@
         <v>290</v>
       </c>
       <c r="B83" s="8">
-        <v>46090.67444209491</v>
+        <v>46090.50777542824</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46090.80510556713</v>
+        <v>46090.63843890047</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>291</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -1523,13 +1523,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.668634560185</v>
+        <v>46079.83530122685</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.54858754629</v>
+        <v>46092.71525421296</v>
       </c>
       <c r="D4" s="5">
-        <v>46128.42978174768</v>
+        <v>46128.59644841435</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1572,13 +1572,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.66863482639</v>
+        <v>46079.835301493054</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.548555138885</v>
+        <v>46092.715221805556</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.548588645834</v>
+        <v>46092.715255312505</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1637,13 +1637,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.66863506944</v>
+        <v>46079.83530173611</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.54855576389</v>
+        <v>46092.71522243056</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.548587997684</v>
+        <v>46092.71525466435</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1702,13 +1702,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.66863528935</v>
+        <v>46079.835301956016</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.54855623843</v>
+        <v>46092.71522290509</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.54858858796</v>
+        <v>46092.71525525463</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1767,13 +1767,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.66863550926</v>
+        <v>46079.835302175925</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.548556724534</v>
+        <v>46092.715223391206</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.43571546296</v>
+        <v>46128.602382129626</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1832,13 +1832,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.66863571759</v>
+        <v>46079.835302384265</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.54855746528</v>
+        <v>46092.71522413194</v>
       </c>
       <c r="D9" s="8">
-        <v>46128.42986638889</v>
+        <v>46128.596533055555</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1897,11 +1897,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.6686359375</v>
+        <v>46079.835302604166</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46142.494600081016</v>
+        <v>46142.66126674769</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1944,13 +1944,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.66863619213</v>
+        <v>46079.835302858795</v>
       </c>
       <c r="C11" s="8">
-        <v>46142.4945922801</v>
+        <v>46142.661258946755</v>
       </c>
       <c r="D11" s="8">
-        <v>46142.494593958334</v>
+        <v>46142.661260625</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -2009,11 +2009,11 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.66863646991</v>
+        <v>46079.83530313657</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46199.018176655096</v>
+        <v>46199.18484332176</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2072,13 +2072,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46079.668636689814</v>
+        <v>46079.83530335648</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.34823659722</v>
+        <v>46114.51490326389</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.34825142361</v>
+        <v>46114.51491809028</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2125,13 +2125,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46079.668634594906</v>
+        <v>46079.83530126157</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.347688657406</v>
+        <v>46114.51435532408</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.34770583334</v>
+        <v>46114.5143725</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2190,13 +2190,13 @@
         <v>66</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.66863526621</v>
+        <v>46079.83530193287</v>
       </c>
       <c r="C15" s="8">
-        <v>46111.62614576389</v>
+        <v>46111.792812430554</v>
       </c>
       <c r="D15" s="8">
-        <v>46111.62616248842</v>
+        <v>46111.79282915509</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>67</v>
@@ -2255,13 +2255,13 @@
         <v>69</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.66863559028</v>
+        <v>46079.83530225694</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.34779292824</v>
+        <v>46114.51445959491</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.347810555555</v>
+        <v>46114.51447722223</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>70</v>
@@ -2320,13 +2320,13 @@
         <v>72</v>
       </c>
       <c r="B17" s="8">
-        <v>46080.34358465278</v>
+        <v>46080.51025131944</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34815204861</v>
+        <v>46114.51481871528</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.34816729167</v>
+        <v>46114.51483395833</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>73</v>
@@ -2385,13 +2385,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.668635891205</v>
+        <v>46079.83530255787</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.348217025465</v>
+        <v>46114.51488369213</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.34823753472</v>
+        <v>46114.51490420139</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2450,13 +2450,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.668636180555</v>
+        <v>46079.83530284722</v>
       </c>
       <c r="C19" s="8">
-        <v>46128.26519445602</v>
+        <v>46128.431861122684</v>
       </c>
       <c r="D19" s="8">
-        <v>46204.73902555555</v>
+        <v>46204.90569222222</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2503,13 +2503,13 @@
         <v>83</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.66863646991</v>
+        <v>46079.83530313657</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3773302662</v>
+        <v>46097.54399693287</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.62616730324</v>
+        <v>46111.79283396991</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>84</v>
@@ -2568,13 +2568,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.66863677083</v>
+        <v>46079.8353034375</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.34827811342</v>
+        <v>46114.514944780094</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.3482946875</v>
+        <v>46114.514961354165</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2633,13 +2633,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.668637083334</v>
+        <v>46079.83530375</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.34829836806</v>
+        <v>46114.51496503472</v>
       </c>
       <c r="D22" s="5">
-        <v>46142.494598923615</v>
+        <v>46142.66126559028</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2698,13 +2698,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.66863738426</v>
+        <v>46079.835304050925</v>
       </c>
       <c r="C23" s="8">
-        <v>46128.26517543981</v>
+        <v>46128.43184210648</v>
       </c>
       <c r="D23" s="8">
-        <v>46128.834950358796</v>
+        <v>46129.00161702547</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2763,13 +2763,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.668634560185</v>
+        <v>46079.83530122685</v>
       </c>
       <c r="C24" s="5">
-        <v>46204.739003229166</v>
+        <v>46204.90566989583</v>
       </c>
       <c r="D24" s="5">
-        <v>46204.73900700231</v>
+        <v>46204.90567366898</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2828,13 +2828,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.70764284722</v>
+        <v>46079.87430951389</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.634447268516</v>
+        <v>46191.80111393519</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.63444896991</v>
+        <v>46191.801115636576</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>102</v>
@@ -2893,13 +2893,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46080.34373289352</v>
+        <v>46080.51039956018</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.6344592824</v>
+        <v>46191.801125949074</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.634460601854</v>
+        <v>46191.80112726852</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2958,11 +2958,11 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.668634918984</v>
+        <v>46079.83530158565</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46191.70834858796</v>
+        <v>46191.87501525463</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -3007,13 +3007,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.66863519676</v>
+        <v>46079.83530186342</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.70815302084</v>
+        <v>46191.874819687495</v>
       </c>
       <c r="D28" s="5">
-        <v>46204.02652871527</v>
+        <v>46204.193195381944</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -3072,13 +3072,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.668635462964</v>
+        <v>46079.83530212963</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.37739233796</v>
+        <v>46097.544059004635</v>
       </c>
       <c r="D29" s="8">
-        <v>46169.68174571759</v>
+        <v>46169.848412384265</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3133,13 +3133,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.66863569444</v>
+        <v>46079.83530236111</v>
       </c>
       <c r="C30" s="5">
-        <v>46191.70813865741</v>
+        <v>46191.87480532407</v>
       </c>
       <c r="D30" s="5">
-        <v>46191.70814038195</v>
+        <v>46191.87480704861</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3194,13 +3194,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.668636030096</v>
+        <v>46079.83530269676</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.708044768515</v>
+        <v>46191.874711435186</v>
       </c>
       <c r="D31" s="8">
-        <v>46198.029814375</v>
+        <v>46198.19648104167</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3259,13 +3259,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.668636284725</v>
+        <v>46079.83530295139</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.512557939815</v>
+        <v>46182.67922460648</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.51255994213</v>
+        <v>46182.6792266088</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3320,13 +3320,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.66863652778</v>
+        <v>46079.83530319444</v>
       </c>
       <c r="C33" s="8">
-        <v>46191.70802984954</v>
+        <v>46191.8746965162</v>
       </c>
       <c r="D33" s="8">
-        <v>46191.70803145833</v>
+        <v>46191.874698125</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3381,13 +3381,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.66863457176</v>
+        <v>46079.835301238425</v>
       </c>
       <c r="C34" s="5">
-        <v>46191.7079222801</v>
+        <v>46191.87458894676</v>
       </c>
       <c r="D34" s="5">
-        <v>46191.70793674768</v>
+        <v>46191.874603414355</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3446,13 +3446,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.66863482639</v>
+        <v>46079.835301493054</v>
       </c>
       <c r="C35" s="8">
-        <v>46114.59961186342</v>
+        <v>46114.76627853009</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.68181603009</v>
+        <v>46169.84848269676</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3507,13 +3507,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.66863512732</v>
+        <v>46079.83530179398</v>
       </c>
       <c r="C36" s="5">
-        <v>46191.707908125</v>
+        <v>46191.87457479167</v>
       </c>
       <c r="D36" s="5">
-        <v>46191.70790988426</v>
+        <v>46191.87457655092</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3568,13 +3568,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.668635486116</v>
+        <v>46079.83530215277</v>
       </c>
       <c r="C37" s="8">
-        <v>46114.65071625</v>
+        <v>46114.81738291666</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.681829548615</v>
+        <v>46169.84849621527</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3629,13 +3629,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46079.66863675926</v>
+        <v>46079.83530342593</v>
       </c>
       <c r="C38" s="5">
-        <v>46191.708328865745</v>
+        <v>46191.8749955324</v>
       </c>
       <c r="D38" s="5">
-        <v>46191.70834646991</v>
+        <v>46191.875013136574</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3694,13 +3694,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46079.668637002316</v>
+        <v>46079.83530366898</v>
       </c>
       <c r="C39" s="8">
-        <v>46191.70780684028</v>
+        <v>46191.87447350695</v>
       </c>
       <c r="D39" s="8">
-        <v>46191.70780873843</v>
+        <v>46191.87447540509</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3755,13 +3755,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.66863418982</v>
+        <v>46079.83530085648</v>
       </c>
       <c r="C40" s="5">
-        <v>46191.708312627314</v>
+        <v>46191.87497929398</v>
       </c>
       <c r="D40" s="5">
-        <v>46191.70831621528</v>
+        <v>46191.87498288194</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3816,13 +3816,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.668635752314</v>
+        <v>46079.835302418986</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.7082074537</v>
+        <v>46191.874874120374</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.7082093287</v>
+        <v>46191.874875995374</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3881,13 +3881,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.668636030096</v>
+        <v>46079.83530269676</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.59897114584</v>
+        <v>46114.765637812496</v>
       </c>
       <c r="D42" s="5">
-        <v>46204.73901832176</v>
+        <v>46204.90568498842</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3942,13 +3942,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.668636296294</v>
+        <v>46079.835302962965</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.599022407405</v>
+        <v>46114.76568907408</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.59902407408</v>
+        <v>46114.765690740736</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4003,13 +4003,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.707824467594</v>
+        <v>46079.87449113426</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.59944146991</v>
+        <v>46114.76610813657</v>
       </c>
       <c r="D44" s="5">
-        <v>46204.01894546296</v>
+        <v>46204.18561212963</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4068,13 +4068,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.70790026621</v>
+        <v>46079.87456693287</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.59938703704</v>
+        <v>46114.7660537037</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.63445305555</v>
+        <v>46191.80111972222</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4129,13 +4129,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.70800302083</v>
+        <v>46079.8746696875</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.59942802083</v>
+        <v>46114.7660946875</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.599429814814</v>
+        <v>46114.766096481486</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4190,11 +4190,11 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.668636585644</v>
+        <v>46079.835303252315</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46127.52115996528</v>
+        <v>46127.68782663194</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4239,13 +4239,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.668636863425</v>
+        <v>46079.8353035301</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.62879984954</v>
+        <v>46114.7954665162</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.6288166088</v>
+        <v>46114.79548327546</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4304,13 +4304,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.668634016205</v>
+        <v>46079.83530068287</v>
       </c>
       <c r="C49" s="8">
-        <v>46127.521092986106</v>
+        <v>46127.68775965278</v>
       </c>
       <c r="D49" s="8">
-        <v>46156.03380072917</v>
+        <v>46156.20046739583</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4369,13 +4369,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46087.46219618055</v>
+        <v>46087.628862847225</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.521146377316</v>
+        <v>46127.68781304398</v>
       </c>
       <c r="D50" s="5">
-        <v>46158.82925711806</v>
+        <v>46158.99592378472</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4434,11 +4434,11 @@
         <v>187</v>
       </c>
       <c r="B51" s="8">
-        <v>46087.46223626158</v>
+        <v>46087.62890292824</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46127.5235468287</v>
+        <v>46127.69021349537</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>188</v>
@@ -4497,11 +4497,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.66863438657</v>
+        <v>46079.835301053245</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46191.634622094905</v>
+        <v>46191.80128876158</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4550,11 +4550,11 @@
         <v>194</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.66863467592</v>
+        <v>46079.835301342595</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46191.634585844906</v>
+        <v>46191.80125251158</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>195</v>
@@ -4613,11 +4613,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.668634953705</v>
+        <v>46079.83530162037</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46191.63459611111</v>
+        <v>46191.80126277778</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4676,11 +4676,11 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.6686352199</v>
+        <v>46079.835301886575</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46080.41253865741</v>
+        <v>46080.57920532407</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4729,11 +4729,11 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.668635497685</v>
+        <v>46079.835302164356</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46191.63460251158</v>
+        <v>46191.80126917824</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4792,11 +4792,11 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.668635752314</v>
+        <v>46079.835302418986</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.000487129626</v>
+        <v>46191.1671537963</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>212</v>
@@ -4855,11 +4855,11 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.66863600694</v>
+        <v>46079.835302673615</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46193.03876826389</v>
+        <v>46193.205434930554</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -4918,11 +4918,11 @@
         <v>218</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.668636250004</v>
+        <v>46079.83530291667</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46158.82918858796</v>
+        <v>46158.99585525463</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>192</v>
@@ -4971,11 +4971,11 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.66863559028</v>
+        <v>46079.83530225694</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46191.708157256944</v>
+        <v>46191.874823923616</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -5034,11 +5034,11 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.66863518518</v>
+        <v>46079.835301851854</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46200.04164997685</v>
+        <v>46200.20831664352</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>56</v>
@@ -5097,11 +5097,11 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.7092312037</v>
+        <v>46079.87589787037</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46205.08364280092</v>
+        <v>46205.25030946759</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5160,11 +5160,11 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.66863652778</v>
+        <v>46079.83530319444</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46191.708324293984</v>
+        <v>46191.87499096065</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5223,11 +5223,11 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.66863596065</v>
+        <v>46079.83530262731</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46191.707918263884</v>
+        <v>46191.874584930556</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5286,11 +5286,11 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.668636296294</v>
+        <v>46079.835302962965</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46158.8292571412</v>
+        <v>46158.99592380787</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5339,11 +5339,11 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46079.66863662037</v>
+        <v>46079.83530328704</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46205.02663775463</v>
+        <v>46205.19330442129</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>217</v>
@@ -5402,11 +5402,11 @@
         <v>239</v>
       </c>
       <c r="B67" s="8">
-        <v>46079.66863695602</v>
+        <v>46079.83530362268</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46127.52116150463</v>
+        <v>46127.6878281713</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>240</v>
@@ -5465,11 +5465,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46079.66863731481</v>
+        <v>46079.83530398148</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46127.52116212963</v>
+        <v>46127.6878287963</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5528,11 +5528,11 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46079.668637627314</v>
+        <v>46079.835304293985</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46127.52116265046</v>
+        <v>46127.68782931713</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>248</v>
@@ -5591,11 +5591,11 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46080.32605201389</v>
+        <v>46080.49271868056</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46127.52116314815</v>
+        <v>46127.687829814815</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>251</v>
@@ -5654,11 +5654,11 @@
         <v>253</v>
       </c>
       <c r="B71" s="8">
-        <v>46079.668637939816</v>
+        <v>46079.83530460648</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46158.829257060184</v>
+        <v>46158.99592372685</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>189</v>
@@ -5717,11 +5717,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46079.66863826389</v>
+        <v>46079.83530493056</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46090.63800759259</v>
+        <v>46090.804674259256</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>257</v>
@@ -5780,11 +5780,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46079.66863478009</v>
+        <v>46079.83530144676</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46090.51004356482</v>
+        <v>46090.67671023148</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5827,11 +5827,11 @@
         <v>262</v>
       </c>
       <c r="B74" s="5">
-        <v>46079.66863515046</v>
+        <v>46079.83530181713</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46090.63806557871</v>
+        <v>46090.80473224537</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>263</v>
@@ -5888,11 +5888,11 @@
         <v>265</v>
       </c>
       <c r="B75" s="8">
-        <v>46079.668635740745</v>
+        <v>46079.8353024074</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46097.47623357639</v>
+        <v>46097.64290024305</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>57</v>
@@ -5951,11 +5951,11 @@
         <v>268</v>
       </c>
       <c r="B76" s="5">
-        <v>46079.668636030096</v>
+        <v>46079.83530269676</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.63820487268</v>
+        <v>46090.80487153935</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>269</v>
@@ -6014,11 +6014,11 @@
         <v>271</v>
       </c>
       <c r="B77" s="8">
-        <v>46079.66863640046</v>
+        <v>46079.83530306713</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46090.63829269676</v>
+        <v>46090.80495936342</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>272</v>
@@ -6077,11 +6077,11 @@
         <v>274</v>
       </c>
       <c r="B78" s="5">
-        <v>46079.66863666667</v>
+        <v>46079.83530333333</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46090.51001115741</v>
+        <v>46090.67667782407</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>275</v>
@@ -6124,11 +6124,11 @@
         <v>277</v>
       </c>
       <c r="B79" s="8">
-        <v>46079.66863696759</v>
+        <v>46079.83530363426</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.63836675926</v>
+        <v>46090.805033425924</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>278</v>
@@ -6187,11 +6187,11 @@
         <v>281</v>
       </c>
       <c r="B80" s="5">
-        <v>46079.66863729167</v>
+        <v>46079.83530395833</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.348227361115</v>
+        <v>46114.51489402778</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>282</v>
@@ -6250,11 +6250,11 @@
         <v>284</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.507380740746</v>
+        <v>46090.6740474074</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.51155083333</v>
+        <v>46090.6782175</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>285</v>
@@ -6303,11 +6303,11 @@
         <v>287</v>
       </c>
       <c r="B82" s="5">
-        <v>46090.50756469907</v>
+        <v>46090.674231365745</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46090.638442048614</v>
+        <v>46090.80510871528</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>288</v>
@@ -6366,11 +6366,11 @@
         <v>290</v>
       </c>
       <c r="B83" s="8">
-        <v>46090.50777542824</v>
+        <v>46090.67444209491</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46090.63843890047</v>
+        <v>46090.80510556713</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>291</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -2013,7 +2013,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46199.18484332176</v>
+        <v>46206.25029707176</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46191.874823923616</v>
+        <v>46206.20063146991</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -5025,8 +5025,8 @@
       <c r="T60" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="U60" s="10" t="s">
-        <v>117</v>
+      <c r="U60" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46205.25030946759</v>
+        <v>46206.16743369213</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5151,8 +5151,8 @@
       <c r="T62" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="U62" s="12" t="s">
-        <v>59</v>
+      <c r="U62" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -200,169 +200,169 @@
     <t>Tarea sin iniciar</t>
   </si>
   <si>
+    <t>1213459189153314</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Damper,Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete,Analisis de costeo</t>
+  </si>
+  <si>
+    <t>1213459189153315</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
+  </si>
+  <si>
+    <t>1213459189153317</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
+  </si>
+  <si>
+    <t>1213459189153318</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta compras a codigo // aprovisionamiento,Propuesta Sensores,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1213458011369803</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Damper</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Propuesta Damper,Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>1213459189153319</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Damper,Ingenieria Basica Motor,Ingenieria Detalle,Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Costos</t>
+  </si>
+  <si>
+    <t>1213459189153320</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta motor,propuesta alabes,propuesta nucleo rodete,propuesta tableros,propuesta compras a codigo // aprovisionamiento,Propuesta Sensores</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1213459189153321</t>
+  </si>
+  <si>
+    <t>propuesta alabes</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189153322</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC motor ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189153323</t>
+  </si>
+  <si>
+    <t>propuesta tableros</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Tableros  ot 4265 - ot 4266</t>
+  </si>
+  <si>
+    <t>1213459189153324</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189153325</t>
+  </si>
+  <si>
+    <t>propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales</t>
+  </si>
+  <si>
+    <t>1213458788103036</t>
+  </si>
+  <si>
+    <t>Propuesta Sensores</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Sensores</t>
+  </si>
+  <si>
+    <t>1213458011369804</t>
+  </si>
+  <si>
+    <t>Propuesta Damper</t>
+  </si>
+  <si>
+    <t>1213459189153326</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Sensores,Materiales a codigo // compras locales aprovisionamientomiento:,rodete ot 4264,Tablero ot 4265 - ot 4266,Motor ot 4264,Alabe  ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189153327</t>
+  </si>
+  <si>
+    <t>Alabe  ot 4264</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe ot 4264,Fabricación Alabe ot 4264</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213459189153314</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Damper,Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213459189153315</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
-  </si>
-  <si>
-    <t>1213459189153317</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
-  </si>
-  <si>
-    <t>1213459189153318</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta compras a codigo // aprovisionamiento,Propuesta Sensores,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1213458011369803</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Damper</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Propuesta Damper,Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>1213459189153319</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Damper,Ingenieria Basica Motor,Ingenieria Detalle,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>1213459189153320</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta motor,propuesta alabes,propuesta nucleo rodete,propuesta tableros,propuesta compras a codigo // aprovisionamiento,Propuesta Sensores</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213459189153321</t>
-  </si>
-  <si>
-    <t>propuesta alabes</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189153322</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC motor ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189153323</t>
-  </si>
-  <si>
-    <t>propuesta tableros</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Tableros  ot 4265 - ot 4266</t>
-  </si>
-  <si>
-    <t>1213459189153324</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189153325</t>
-  </si>
-  <si>
-    <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales</t>
-  </si>
-  <si>
-    <t>1213458788103036</t>
-  </si>
-  <si>
-    <t>Propuesta Sensores</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Sensores</t>
-  </si>
-  <si>
-    <t>1213458011369804</t>
-  </si>
-  <si>
-    <t>Propuesta Damper</t>
-  </si>
-  <si>
-    <t>1213459189153326</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Sensores,Materiales a codigo // compras locales aprovisionamientomiento:,rodete ot 4264,Tablero ot 4265 - ot 4266,Motor ot 4264,Alabe  ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189153327</t>
-  </si>
-  <si>
-    <t>Alabe  ot 4264</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe ot 4264,Fabricación Alabe ot 4264</t>
   </si>
   <si>
     <t>1213459189153328</t>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46206.25029707176</v>
+        <v>46207.20142103009</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2063,13 +2063,13 @@
       <c r="T12" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="U12" s="12" t="s">
-        <v>59</v>
+      <c r="U12" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="8">
         <v>46079.83530335648</v>
@@ -2081,7 +2081,7 @@
         <v>46114.51491809028</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2105,7 +2105,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2122,7 +2122,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B14" s="5">
         <v>46079.83530126157</v>
@@ -2134,7 +2134,7 @@
         <v>46114.5143725</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2161,13 +2161,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q14" s="5">
         <v>46084</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B15" s="8">
         <v>46079.83530193287</v>
@@ -2199,7 +2199,7 @@
         <v>46111.79282915509</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2226,13 +2226,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>40</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q15" s="8">
         <v>46084</v>
@@ -2252,7 +2252,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B16" s="5">
         <v>46079.83530225694</v>
@@ -2264,7 +2264,7 @@
         <v>46114.51447722223</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2291,13 +2291,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="5">
         <v>46084</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B17" s="8">
         <v>46080.51025131944</v>
@@ -2329,7 +2329,7 @@
         <v>46114.51483395833</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
@@ -2356,13 +2356,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O17" s="9" t="s">
         <v>40</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q17" s="8">
         <v>46084</v>
@@ -2382,7 +2382,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="5">
         <v>46079.83530255787</v>
@@ -2394,7 +2394,7 @@
         <v>46114.51490420139</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2421,13 +2421,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="Q18" s="5">
         <v>46084</v>
@@ -2447,7 +2447,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" s="8">
         <v>46079.83530284722</v>
@@ -2459,7 +2459,7 @@
         <v>46204.90569222222</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>25</v>
@@ -2483,7 +2483,7 @@
         <v>26</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P19" s="9" t="s">
         <v>26</v>
@@ -2494,13 +2494,13 @@
         <v>1</v>
       </c>
       <c r="T19" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U19" s="9"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B20" s="5">
         <v>46079.83530313657</v>
@@ -2512,7 +2512,7 @@
         <v>46111.79283396991</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2539,13 +2539,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="5">
         <v>46093</v>
@@ -2557,7 +2557,7 @@
         <v>1</v>
       </c>
       <c r="T20" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U20" s="11" t="s">
         <v>32</v>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B21" s="8">
         <v>46079.8353034375</v>
@@ -2577,7 +2577,7 @@
         <v>46114.514961354165</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
@@ -2604,13 +2604,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q21" s="8">
         <v>46086</v>
@@ -2630,7 +2630,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5">
         <v>46079.83530375</v>
@@ -2642,7 +2642,7 @@
         <v>46142.66126559028</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2669,13 +2669,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>49</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q22" s="5">
         <v>46087</v>
@@ -2695,7 +2695,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B23" s="8">
         <v>46079.835304050925</v>
@@ -2707,16 +2707,16 @@
         <v>46129.00161702547</v>
       </c>
       <c r="E23" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>94</v>
-      </c>
       <c r="H23" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I23" s="8">
         <v>46093</v>
@@ -2734,13 +2734,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q23" s="8">
         <v>46093</v>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>46079.83530122685</v>
@@ -2772,16 +2772,16 @@
         <v>46204.90567366898</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I24" s="5">
         <v>46093</v>
@@ -2799,13 +2799,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="5">
         <v>46093</v>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B25" s="8">
         <v>46079.87430951389</v>
@@ -2837,7 +2837,7 @@
         <v>46191.801115636576</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -2864,13 +2864,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q25" s="8">
         <v>46093</v>
@@ -2890,7 +2890,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46080.51039956018</v>
@@ -2902,7 +2902,7 @@
         <v>46191.80112726852</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -2929,10 +2929,10 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>26</v>
@@ -2955,7 +2955,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B27" s="8">
         <v>46079.83530158565</v>
@@ -2965,7 +2965,7 @@
         <v>46191.87501525463</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>25</v>
@@ -2989,7 +2989,7 @@
         <v>26</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>26</v>
@@ -2998,13 +2998,13 @@
       <c r="R27" s="9"/>
       <c r="S27" s="9"/>
       <c r="T27" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U27" s="9"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B28" s="5">
         <v>46079.83530186342</v>
@@ -3016,16 +3016,16 @@
         <v>46204.193195381944</v>
       </c>
       <c r="E28" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="6" t="s">
+      <c r="H28" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="I28" s="5">
         <v>46097</v>
@@ -3043,13 +3043,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q28" s="5">
         <v>46097</v>
@@ -3064,7 +3064,7 @@
         <v>31</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3087,10 +3087,10 @@
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>112</v>
       </c>
       <c r="I29" s="8">
         <v>46097</v>
@@ -3108,10 +3108,10 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>116</v>
@@ -3148,10 +3148,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="I30" s="5">
         <v>46099</v>
@@ -3169,7 +3169,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>115</v>
@@ -3209,10 +3209,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>112</v>
       </c>
       <c r="I31" s="8">
         <v>46091</v>
@@ -3230,13 +3230,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>123</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q31" s="8">
         <v>46091</v>
@@ -3274,10 +3274,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="I32" s="5">
         <v>46091</v>
@@ -3298,7 +3298,7 @@
         <v>122</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>126</v>
@@ -3335,10 +3335,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>112</v>
       </c>
       <c r="I33" s="8">
         <v>46100</v>
@@ -3396,10 +3396,10 @@
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="I34" s="5">
         <v>46090</v>
@@ -3417,13 +3417,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>132</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q34" s="5">
         <v>46090</v>
@@ -3435,7 +3435,7 @@
         <v>1</v>
       </c>
       <c r="T34" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U34" s="11" t="s">
         <v>32</v>
@@ -3461,10 +3461,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>112</v>
       </c>
       <c r="I35" s="8">
         <v>46090</v>
@@ -3485,7 +3485,7 @@
         <v>131</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>135</v>
@@ -3522,10 +3522,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="I36" s="5">
         <v>46108</v>
@@ -3583,10 +3583,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>112</v>
       </c>
       <c r="I37" s="8">
         <v>46108</v>
@@ -3644,10 +3644,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="I38" s="5">
         <v>46097</v>
@@ -3665,13 +3665,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>144</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q38" s="5">
         <v>46097</v>
@@ -3709,10 +3709,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>112</v>
       </c>
       <c r="I39" s="8">
         <v>46097</v>
@@ -3733,7 +3733,7 @@
         <v>143</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>147</v>
@@ -3770,10 +3770,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="I40" s="5">
         <v>46099</v>
@@ -3852,13 +3852,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>155</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q41" s="8">
         <v>46097</v>
@@ -3920,7 +3920,7 @@
         <v>152</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>158</v>
@@ -4039,13 +4039,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>164</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q44" s="5">
         <v>46097</v>
@@ -4107,7 +4107,7 @@
         <v>163</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>167</v>
@@ -4278,7 +4278,7 @@
         <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>178</v>
@@ -4665,7 +4665,7 @@
         <v>1</v>
       </c>
       <c r="T54" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U54" s="11" t="s">
         <v>32</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="T56" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U56" s="11" t="s">
         <v>32</v>
@@ -5023,10 +5023,10 @@
         <v>0</v>
       </c>
       <c r="T60" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U60" s="12" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5086,7 +5086,7 @@
         <v>0</v>
       </c>
       <c r="T61" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U61" s="11" t="s">
         <v>32</v>
@@ -5149,7 +5149,7 @@
         <v>0</v>
       </c>
       <c r="T62" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U62" s="11" t="s">
         <v>32</v>
@@ -5212,7 +5212,7 @@
         <v>0</v>
       </c>
       <c r="T63" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U63" s="11" t="s">
         <v>32</v>
@@ -5275,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="T64" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U64" s="10" t="s">
         <v>117</v>
@@ -5352,10 +5352,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I66" s="5">
         <v>46195</v>
@@ -5394,7 +5394,7 @@
         <v>58</v>
       </c>
       <c r="U66" s="12" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5415,10 +5415,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I67" s="8">
         <v>46238</v>
@@ -5478,10 +5478,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I68" s="5">
         <v>46216</v>
@@ -5541,10 +5541,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I69" s="8">
         <v>46218</v>
@@ -5604,10 +5604,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5667,10 +5667,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I71" s="8">
         <v>46240</v>
@@ -5730,10 +5730,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I72" s="5">
         <v>46244</v>
@@ -5901,10 +5901,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I75" s="8">
         <v>46246</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -2960,9 +2960,11 @@
       <c r="B27" s="8">
         <v>46079.83530158565</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="8">
+        <v>46209.70945200232</v>
+      </c>
       <c r="D27" s="8">
-        <v>46191.87501525463</v>
+        <v>46209.709468483794</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>106</v>
@@ -2996,9 +2998,11 @@
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="12" t="s">
-        <v>81</v>
+      <c r="S27" s="9">
+        <v>1</v>
+      </c>
+      <c r="T27" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U27" s="9"/>
     </row>
@@ -4975,7 +4979,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46206.20063146991</v>
+        <v>46209.7099818287</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -2456,7 +2456,7 @@
         <v>46128.431861122684</v>
       </c>
       <c r="D19" s="8">
-        <v>46204.90569222222</v>
+        <v>46209.77994920139</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2766,10 +2766,10 @@
         <v>46079.83530122685</v>
       </c>
       <c r="C24" s="5">
-        <v>46204.90566989583</v>
+        <v>46209.77994163195</v>
       </c>
       <c r="D24" s="5">
-        <v>46204.90567366898</v>
+        <v>46209.779943333335</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -3891,7 +3891,7 @@
         <v>46114.765637812496</v>
       </c>
       <c r="D42" s="5">
-        <v>46204.90568498842</v>
+        <v>46209.779950625</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46191.80128876158</v>
+        <v>46209.78807094907</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4556,9 +4556,11 @@
       <c r="B53" s="8">
         <v>46079.835301342595</v>
       </c>
-      <c r="C53" s="9"/>
+      <c r="C53" s="8">
+        <v>46209.788062928244</v>
+      </c>
       <c r="D53" s="8">
-        <v>46191.80125251158</v>
+        <v>46209.78806449074</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>195</v>
@@ -4621,7 +4623,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46191.80126277778</v>
+        <v>46209.78806983796</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4737,7 +4739,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46191.80126917824</v>
+        <v>46209.79160884259</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4979,7 +4981,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46209.7099818287</v>
+        <v>46209.80479041667</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -5475,7 +5475,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46127.6878287963</v>
+        <v>46210.19251728009</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5525,8 +5525,8 @@
       <c r="T68" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="U68" s="10" t="s">
-        <v>117</v>
+      <c r="U68" s="12" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="294">
   <si>
     <t>50001518 - EQ. CHAPARRAL</t>
   </si>
@@ -813,6 +813,12 @@
   </si>
   <si>
     <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
   </si>
   <si>
     <t>Embalaje,Logistica:</t>
@@ -5837,7 +5843,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46090.80473224537</v>
+        <v>46210.61678060185</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>263</v>
@@ -5846,10 +5852,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>35</v>
+        <v>264</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>36</v>
+        <v>265</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5871,7 +5877,7 @@
         <v>257</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q74" s="5">
         <v>46245</v>
@@ -5891,7 +5897,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B75" s="8">
         <v>46079.8353024074</v>
@@ -5931,10 +5937,10 @@
         <v>260</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q75" s="8">
         <v>46246</v>
@@ -5954,7 +5960,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B76" s="5">
         <v>46079.83530269676</v>
@@ -5964,7 +5970,7 @@
         <v>46090.80487153935</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5997,7 +6003,7 @@
         <v>57</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q76" s="5">
         <v>46251</v>
@@ -6017,7 +6023,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B77" s="8">
         <v>46079.83530306713</v>
@@ -6027,7 +6033,7 @@
         <v>46090.80495936342</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6057,10 +6063,10 @@
         <v>260</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q77" s="8">
         <v>46252</v>
@@ -6080,7 +6086,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B78" s="5">
         <v>46079.83530333333</v>
@@ -6090,7 +6096,7 @@
         <v>46090.67667782407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6114,7 +6120,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6127,7 +6133,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B79" s="8">
         <v>46079.83530363426</v>
@@ -6137,16 +6143,16 @@
         <v>46090.805033425924</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I79" s="8">
         <v>46253</v>
@@ -6164,13 +6170,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q79" s="8">
         <v>46252</v>
@@ -6190,7 +6196,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B80" s="5">
         <v>46079.83530395833</v>
@@ -6200,16 +6206,16 @@
         <v>46114.51489402778</v>
       </c>
       <c r="E80" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>280</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6227,13 +6233,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q80" s="5">
         <v>46252</v>
@@ -6253,7 +6259,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B81" s="8">
         <v>46090.6740474074</v>
@@ -6263,7 +6269,7 @@
         <v>46090.6782175</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>25</v>
@@ -6287,7 +6293,7 @@
         <v>26</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>26</v>
@@ -6306,7 +6312,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B82" s="5">
         <v>46090.674231365745</v>
@@ -6316,7 +6322,7 @@
         <v>46090.80510871528</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6343,13 +6349,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q82" s="5">
         <v>46253</v>
@@ -6369,7 +6375,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B83" s="8">
         <v>46090.67444209491</v>
@@ -6379,7 +6385,7 @@
         <v>46090.80510556713</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6406,13 +6412,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q83" s="8">
         <v>46262</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -4987,7 +4987,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46209.80479041667</v>
+        <v>46210.71240582176</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -4987,7 +4987,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46210.71240582176</v>
+        <v>46210.807318935185</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -4987,7 +4987,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46210.807318935185</v>
+        <v>46210.81198283564</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -1529,13 +1529,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.83530122685</v>
+        <v>46079.668634560185</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.71525421296</v>
+        <v>46092.54858754629</v>
       </c>
       <c r="D4" s="5">
-        <v>46128.59644841435</v>
+        <v>46128.42978174768</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1578,13 +1578,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.835301493054</v>
+        <v>46079.66863482639</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.715221805556</v>
+        <v>46092.548555138885</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.715255312505</v>
+        <v>46092.548588645834</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1643,13 +1643,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.83530173611</v>
+        <v>46079.66863506944</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.71522243056</v>
+        <v>46092.54855576389</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.71525466435</v>
+        <v>46092.548587997684</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1708,13 +1708,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.835301956016</v>
+        <v>46079.66863528935</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71522290509</v>
+        <v>46092.54855623843</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.71525525463</v>
+        <v>46092.54858858796</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1773,13 +1773,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.835302175925</v>
+        <v>46079.66863550926</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.715223391206</v>
+        <v>46092.548556724534</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.602382129626</v>
+        <v>46128.43571546296</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1838,13 +1838,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.835302384265</v>
+        <v>46079.66863571759</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71522413194</v>
+        <v>46092.54855746528</v>
       </c>
       <c r="D9" s="8">
-        <v>46128.596533055555</v>
+        <v>46128.42986638889</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1903,11 +1903,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.835302604166</v>
+        <v>46079.6686359375</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46142.66126674769</v>
+        <v>46142.494600081016</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1950,13 +1950,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.835302858795</v>
+        <v>46079.66863619213</v>
       </c>
       <c r="C11" s="8">
-        <v>46142.661258946755</v>
+        <v>46142.4945922801</v>
       </c>
       <c r="D11" s="8">
-        <v>46142.661260625</v>
+        <v>46142.494593958334</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -2015,11 +2015,11 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.83530313657</v>
+        <v>46079.66863646991</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46207.20142103009</v>
+        <v>46207.03475436343</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2078,13 +2078,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46079.83530335648</v>
+        <v>46079.668636689814</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51490326389</v>
+        <v>46114.34823659722</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.51491809028</v>
+        <v>46114.34825142361</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2131,13 +2131,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46079.83530126157</v>
+        <v>46079.668634594906</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.51435532408</v>
+        <v>46114.347688657406</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.5143725</v>
+        <v>46114.34770583334</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2196,13 +2196,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.83530193287</v>
+        <v>46079.66863526621</v>
       </c>
       <c r="C15" s="8">
-        <v>46111.792812430554</v>
+        <v>46111.62614576389</v>
       </c>
       <c r="D15" s="8">
-        <v>46111.79282915509</v>
+        <v>46111.62616248842</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2261,13 +2261,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.83530225694</v>
+        <v>46079.66863559028</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.51445959491</v>
+        <v>46114.34779292824</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.51447722223</v>
+        <v>46114.347810555555</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2326,13 +2326,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46080.51025131944</v>
+        <v>46080.34358465278</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.51481871528</v>
+        <v>46114.34815204861</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.51483395833</v>
+        <v>46114.34816729167</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2391,13 +2391,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.83530255787</v>
+        <v>46079.668635891205</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.51488369213</v>
+        <v>46114.348217025465</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.51490420139</v>
+        <v>46114.34823753472</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2456,13 +2456,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.83530284722</v>
+        <v>46079.668636180555</v>
       </c>
       <c r="C19" s="8">
-        <v>46128.431861122684</v>
+        <v>46128.26519445602</v>
       </c>
       <c r="D19" s="8">
-        <v>46209.77994920139</v>
+        <v>46209.61328253472</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2509,13 +2509,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.83530313657</v>
+        <v>46079.66863646991</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.54399693287</v>
+        <v>46097.3773302662</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.79283396991</v>
+        <v>46111.62616730324</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2574,13 +2574,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.8353034375</v>
+        <v>46079.66863677083</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.514944780094</v>
+        <v>46114.34827811342</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.514961354165</v>
+        <v>46114.3482946875</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>86</v>
@@ -2639,13 +2639,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.83530375</v>
+        <v>46079.668637083334</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.51496503472</v>
+        <v>46114.34829836806</v>
       </c>
       <c r="D22" s="5">
-        <v>46142.66126559028</v>
+        <v>46142.494598923615</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2704,13 +2704,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.835304050925</v>
+        <v>46079.66863738426</v>
       </c>
       <c r="C23" s="8">
-        <v>46128.43184210648</v>
+        <v>46128.26517543981</v>
       </c>
       <c r="D23" s="8">
-        <v>46129.00161702547</v>
+        <v>46128.834950358796</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2769,13 +2769,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.83530122685</v>
+        <v>46079.668634560185</v>
       </c>
       <c r="C24" s="5">
-        <v>46209.77994163195</v>
+        <v>46209.613274965275</v>
       </c>
       <c r="D24" s="5">
-        <v>46209.779943333335</v>
+        <v>46209.61327666667</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2834,13 +2834,13 @@
         <v>100</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.87430951389</v>
+        <v>46079.70764284722</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.80111393519</v>
+        <v>46191.634447268516</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.801115636576</v>
+        <v>46191.63444896991</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>101</v>
@@ -2899,13 +2899,13 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46080.51039956018</v>
+        <v>46080.34373289352</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.801125949074</v>
+        <v>46191.6344592824</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.80112726852</v>
+        <v>46191.634460601854</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -2964,13 +2964,13 @@
         <v>105</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.83530158565</v>
+        <v>46079.668634918984</v>
       </c>
       <c r="C27" s="8">
-        <v>46209.70945200232</v>
+        <v>46209.54278533565</v>
       </c>
       <c r="D27" s="8">
-        <v>46209.709468483794</v>
+        <v>46209.54280181713</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>106</v>
@@ -3017,13 +3017,13 @@
         <v>108</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.83530186342</v>
+        <v>46079.66863519676</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.874819687495</v>
+        <v>46191.70815302084</v>
       </c>
       <c r="D28" s="5">
-        <v>46204.193195381944</v>
+        <v>46204.02652871527</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>109</v>
@@ -3082,13 +3082,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.83530212963</v>
+        <v>46079.668635462964</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.544059004635</v>
+        <v>46097.37739233796</v>
       </c>
       <c r="D29" s="8">
-        <v>46169.848412384265</v>
+        <v>46169.68174571759</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3143,13 +3143,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.83530236111</v>
+        <v>46079.66863569444</v>
       </c>
       <c r="C30" s="5">
-        <v>46191.87480532407</v>
+        <v>46191.70813865741</v>
       </c>
       <c r="D30" s="5">
-        <v>46191.87480704861</v>
+        <v>46191.70814038195</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3204,13 +3204,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.83530269676</v>
+        <v>46079.668636030096</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.874711435186</v>
+        <v>46191.708044768515</v>
       </c>
       <c r="D31" s="8">
-        <v>46198.19648104167</v>
+        <v>46198.029814375</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3269,13 +3269,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.83530295139</v>
+        <v>46079.668636284725</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.67922460648</v>
+        <v>46182.512557939815</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.6792266088</v>
+        <v>46182.51255994213</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3330,13 +3330,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.83530319444</v>
+        <v>46079.66863652778</v>
       </c>
       <c r="C33" s="8">
-        <v>46191.8746965162</v>
+        <v>46191.70802984954</v>
       </c>
       <c r="D33" s="8">
-        <v>46191.874698125</v>
+        <v>46191.70803145833</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3391,13 +3391,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.835301238425</v>
+        <v>46079.66863457176</v>
       </c>
       <c r="C34" s="5">
-        <v>46191.87458894676</v>
+        <v>46191.7079222801</v>
       </c>
       <c r="D34" s="5">
-        <v>46191.874603414355</v>
+        <v>46191.70793674768</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3456,13 +3456,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.835301493054</v>
+        <v>46079.66863482639</v>
       </c>
       <c r="C35" s="8">
-        <v>46114.76627853009</v>
+        <v>46114.59961186342</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.84848269676</v>
+        <v>46169.68181603009</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3517,13 +3517,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.83530179398</v>
+        <v>46079.66863512732</v>
       </c>
       <c r="C36" s="5">
-        <v>46191.87457479167</v>
+        <v>46191.707908125</v>
       </c>
       <c r="D36" s="5">
-        <v>46191.87457655092</v>
+        <v>46191.70790988426</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3578,13 +3578,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.83530215277</v>
+        <v>46079.668635486116</v>
       </c>
       <c r="C37" s="8">
-        <v>46114.81738291666</v>
+        <v>46114.65071625</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.84849621527</v>
+        <v>46169.681829548615</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3639,13 +3639,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46079.83530342593</v>
+        <v>46079.66863675926</v>
       </c>
       <c r="C38" s="5">
-        <v>46191.8749955324</v>
+        <v>46191.708328865745</v>
       </c>
       <c r="D38" s="5">
-        <v>46191.875013136574</v>
+        <v>46191.70834646991</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3704,13 +3704,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46079.83530366898</v>
+        <v>46079.668637002316</v>
       </c>
       <c r="C39" s="8">
-        <v>46191.87447350695</v>
+        <v>46191.70780684028</v>
       </c>
       <c r="D39" s="8">
-        <v>46191.87447540509</v>
+        <v>46191.70780873843</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3765,13 +3765,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.83530085648</v>
+        <v>46079.66863418982</v>
       </c>
       <c r="C40" s="5">
-        <v>46191.87497929398</v>
+        <v>46191.708312627314</v>
       </c>
       <c r="D40" s="5">
-        <v>46191.87498288194</v>
+        <v>46191.70831621528</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3826,13 +3826,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.835302418986</v>
+        <v>46079.668635752314</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.874874120374</v>
+        <v>46191.7082074537</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.874875995374</v>
+        <v>46191.7082093287</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3891,13 +3891,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.83530269676</v>
+        <v>46079.668636030096</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.765637812496</v>
+        <v>46114.59897114584</v>
       </c>
       <c r="D42" s="5">
-        <v>46209.779950625</v>
+        <v>46209.61328395833</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3952,13 +3952,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.835302962965</v>
+        <v>46079.668636296294</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.76568907408</v>
+        <v>46114.599022407405</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.765690740736</v>
+        <v>46114.59902407408</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4013,13 +4013,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.87449113426</v>
+        <v>46079.707824467594</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.76610813657</v>
+        <v>46114.59944146991</v>
       </c>
       <c r="D44" s="5">
-        <v>46204.18561212963</v>
+        <v>46204.01894546296</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4078,13 +4078,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.87456693287</v>
+        <v>46079.70790026621</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.7660537037</v>
+        <v>46114.59938703704</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.80111972222</v>
+        <v>46191.63445305555</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4139,13 +4139,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.8746696875</v>
+        <v>46079.70800302083</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.7660946875</v>
+        <v>46114.59942802083</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.766096481486</v>
+        <v>46114.599429814814</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4200,11 +4200,11 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.835303252315</v>
+        <v>46079.668636585644</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46127.68782663194</v>
+        <v>46127.52115996528</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4249,13 +4249,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.8353035301</v>
+        <v>46079.668636863425</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.7954665162</v>
+        <v>46114.62879984954</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.79548327546</v>
+        <v>46114.6288166088</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4314,13 +4314,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.83530068287</v>
+        <v>46079.668634016205</v>
       </c>
       <c r="C49" s="8">
-        <v>46127.68775965278</v>
+        <v>46127.521092986106</v>
       </c>
       <c r="D49" s="8">
-        <v>46156.20046739583</v>
+        <v>46156.03380072917</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4379,13 +4379,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46087.628862847225</v>
+        <v>46087.46219618055</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.68781304398</v>
+        <v>46127.521146377316</v>
       </c>
       <c r="D50" s="5">
-        <v>46158.99592378472</v>
+        <v>46158.82925711806</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4444,11 +4444,11 @@
         <v>187</v>
       </c>
       <c r="B51" s="8">
-        <v>46087.62890292824</v>
+        <v>46087.46223626158</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46127.69021349537</v>
+        <v>46127.5235468287</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>188</v>
@@ -4507,11 +4507,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.835301053245</v>
+        <v>46079.66863438657</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46209.78807094907</v>
+        <v>46209.62140428241</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4560,13 +4560,13 @@
         <v>194</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.835301342595</v>
+        <v>46079.66863467592</v>
       </c>
       <c r="C53" s="8">
-        <v>46209.788062928244</v>
+        <v>46209.62139626157</v>
       </c>
       <c r="D53" s="8">
-        <v>46209.78806449074</v>
+        <v>46209.62139782407</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>195</v>
@@ -4625,11 +4625,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.83530162037</v>
+        <v>46079.668634953705</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46209.78806983796</v>
+        <v>46209.621403171295</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4688,11 +4688,11 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.835301886575</v>
+        <v>46079.6686352199</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46080.57920532407</v>
+        <v>46080.41253865741</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4741,11 +4741,11 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.835302164356</v>
+        <v>46079.668635497685</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46209.79160884259</v>
+        <v>46209.62494217593</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4804,11 +4804,11 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.835302418986</v>
+        <v>46079.668635752314</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.1671537963</v>
+        <v>46191.000487129626</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>212</v>
@@ -4867,11 +4867,11 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.835302673615</v>
+        <v>46079.66863600694</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46193.205434930554</v>
+        <v>46193.03876826389</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -4930,11 +4930,11 @@
         <v>218</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.83530291667</v>
+        <v>46079.668636250004</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46158.99585525463</v>
+        <v>46158.82918858796</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>192</v>
@@ -4983,11 +4983,11 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.83530225694</v>
+        <v>46079.66863559028</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46210.81198283564</v>
+        <v>46210.645316168986</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -5046,11 +5046,11 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.835301851854</v>
+        <v>46079.66863518518</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46200.20831664352</v>
+        <v>46200.04164997685</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>56</v>
@@ -5109,11 +5109,11 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.87589787037</v>
+        <v>46079.7092312037</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46206.16743369213</v>
+        <v>46206.00076702546</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5172,11 +5172,11 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.83530319444</v>
+        <v>46079.66863652778</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46191.87499096065</v>
+        <v>46191.708324293984</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5235,11 +5235,11 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.83530262731</v>
+        <v>46079.66863596065</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46191.874584930556</v>
+        <v>46191.707918263884</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5298,11 +5298,11 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.835302962965</v>
+        <v>46079.668636296294</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46158.99592380787</v>
+        <v>46158.8292571412</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5351,11 +5351,11 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46079.83530328704</v>
+        <v>46079.66863662037</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46205.19330442129</v>
+        <v>46205.02663775463</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>217</v>
@@ -5414,11 +5414,11 @@
         <v>239</v>
       </c>
       <c r="B67" s="8">
-        <v>46079.83530362268</v>
+        <v>46079.66863695602</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46127.6878281713</v>
+        <v>46127.52116150463</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>240</v>
@@ -5477,11 +5477,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46079.83530398148</v>
+        <v>46079.66863731481</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46210.19251728009</v>
+        <v>46210.02585061343</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5540,11 +5540,11 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46079.835304293985</v>
+        <v>46079.668637627314</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46127.68782931713</v>
+        <v>46127.52116265046</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>248</v>
@@ -5603,11 +5603,11 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46080.49271868056</v>
+        <v>46080.32605201389</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46127.687829814815</v>
+        <v>46127.52116314815</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>251</v>
@@ -5666,11 +5666,11 @@
         <v>253</v>
       </c>
       <c r="B71" s="8">
-        <v>46079.83530460648</v>
+        <v>46079.668637939816</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46158.99592372685</v>
+        <v>46158.829257060184</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>189</v>
@@ -5729,11 +5729,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46079.83530493056</v>
+        <v>46079.66863826389</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46090.804674259256</v>
+        <v>46090.63800759259</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>257</v>
@@ -5792,11 +5792,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46079.83530144676</v>
+        <v>46079.66863478009</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46090.67671023148</v>
+        <v>46090.51004356482</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5839,11 +5839,11 @@
         <v>262</v>
       </c>
       <c r="B74" s="5">
-        <v>46079.83530181713</v>
+        <v>46079.66863515046</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46210.61678060185</v>
+        <v>46210.450113935185</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>263</v>
@@ -5900,11 +5900,11 @@
         <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46079.8353024074</v>
+        <v>46079.668635740745</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46097.64290024305</v>
+        <v>46097.47623357639</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>57</v>
@@ -5963,11 +5963,11 @@
         <v>270</v>
       </c>
       <c r="B76" s="5">
-        <v>46079.83530269676</v>
+        <v>46079.668636030096</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.80487153935</v>
+        <v>46090.63820487268</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>271</v>
@@ -6026,11 +6026,11 @@
         <v>273</v>
       </c>
       <c r="B77" s="8">
-        <v>46079.83530306713</v>
+        <v>46079.66863640046</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46090.80495936342</v>
+        <v>46090.63829269676</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>274</v>
@@ -6089,11 +6089,11 @@
         <v>276</v>
       </c>
       <c r="B78" s="5">
-        <v>46079.83530333333</v>
+        <v>46079.66863666667</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46090.67667782407</v>
+        <v>46090.51001115741</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>277</v>
@@ -6136,11 +6136,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46079.83530363426</v>
+        <v>46079.66863696759</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.805033425924</v>
+        <v>46090.63836675926</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6199,11 +6199,11 @@
         <v>283</v>
       </c>
       <c r="B80" s="5">
-        <v>46079.83530395833</v>
+        <v>46079.66863729167</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.51489402778</v>
+        <v>46114.348227361115</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>284</v>
@@ -6262,11 +6262,11 @@
         <v>286</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.6740474074</v>
+        <v>46090.507380740746</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.6782175</v>
+        <v>46090.51155083333</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>287</v>
@@ -6315,11 +6315,11 @@
         <v>289</v>
       </c>
       <c r="B82" s="5">
-        <v>46090.674231365745</v>
+        <v>46090.50756469907</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46090.80510871528</v>
+        <v>46090.638442048614</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>290</v>
@@ -6378,11 +6378,11 @@
         <v>292</v>
       </c>
       <c r="B83" s="8">
-        <v>46090.67444209491</v>
+        <v>46090.50777542824</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46090.80510556713</v>
+        <v>46090.63843890047</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>293</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -1529,13 +1529,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.668634560185</v>
+        <v>46079.83530122685</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.54858754629</v>
+        <v>46092.71525421296</v>
       </c>
       <c r="D4" s="5">
-        <v>46128.42978174768</v>
+        <v>46128.59644841435</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1578,13 +1578,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.66863482639</v>
+        <v>46079.835301493054</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.548555138885</v>
+        <v>46092.715221805556</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.548588645834</v>
+        <v>46092.715255312505</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1643,13 +1643,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.66863506944</v>
+        <v>46079.83530173611</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.54855576389</v>
+        <v>46092.71522243056</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.548587997684</v>
+        <v>46092.71525466435</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1708,13 +1708,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.66863528935</v>
+        <v>46079.835301956016</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.54855623843</v>
+        <v>46092.71522290509</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.54858858796</v>
+        <v>46092.71525525463</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1773,13 +1773,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.66863550926</v>
+        <v>46079.835302175925</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.548556724534</v>
+        <v>46092.715223391206</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.43571546296</v>
+        <v>46128.602382129626</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1838,13 +1838,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.66863571759</v>
+        <v>46079.835302384265</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.54855746528</v>
+        <v>46092.71522413194</v>
       </c>
       <c r="D9" s="8">
-        <v>46128.42986638889</v>
+        <v>46128.596533055555</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1903,11 +1903,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.6686359375</v>
+        <v>46079.835302604166</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46142.494600081016</v>
+        <v>46142.66126674769</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1950,13 +1950,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.66863619213</v>
+        <v>46079.835302858795</v>
       </c>
       <c r="C11" s="8">
-        <v>46142.4945922801</v>
+        <v>46142.661258946755</v>
       </c>
       <c r="D11" s="8">
-        <v>46142.494593958334</v>
+        <v>46142.661260625</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -2015,11 +2015,11 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.66863646991</v>
+        <v>46079.83530313657</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46207.03475436343</v>
+        <v>46207.20142103009</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2078,13 +2078,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46079.668636689814</v>
+        <v>46079.83530335648</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.34823659722</v>
+        <v>46114.51490326389</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.34825142361</v>
+        <v>46114.51491809028</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2131,13 +2131,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46079.668634594906</v>
+        <v>46079.83530126157</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.347688657406</v>
+        <v>46114.51435532408</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.34770583334</v>
+        <v>46114.5143725</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2196,13 +2196,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.66863526621</v>
+        <v>46079.83530193287</v>
       </c>
       <c r="C15" s="8">
-        <v>46111.62614576389</v>
+        <v>46111.792812430554</v>
       </c>
       <c r="D15" s="8">
-        <v>46111.62616248842</v>
+        <v>46111.79282915509</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2261,13 +2261,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.66863559028</v>
+        <v>46079.83530225694</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.34779292824</v>
+        <v>46114.51445959491</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.347810555555</v>
+        <v>46114.51447722223</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2326,13 +2326,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46080.34358465278</v>
+        <v>46080.51025131944</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34815204861</v>
+        <v>46114.51481871528</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.34816729167</v>
+        <v>46114.51483395833</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2391,13 +2391,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.668635891205</v>
+        <v>46079.83530255787</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.348217025465</v>
+        <v>46114.51488369213</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.34823753472</v>
+        <v>46114.51490420139</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2456,13 +2456,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.668636180555</v>
+        <v>46079.83530284722</v>
       </c>
       <c r="C19" s="8">
-        <v>46128.26519445602</v>
+        <v>46128.431861122684</v>
       </c>
       <c r="D19" s="8">
-        <v>46209.61328253472</v>
+        <v>46209.77994920139</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2509,13 +2509,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.66863646991</v>
+        <v>46079.83530313657</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3773302662</v>
+        <v>46097.54399693287</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.62616730324</v>
+        <v>46111.79283396991</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2574,13 +2574,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.66863677083</v>
+        <v>46079.8353034375</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.34827811342</v>
+        <v>46114.514944780094</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.3482946875</v>
+        <v>46114.514961354165</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>86</v>
@@ -2639,13 +2639,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.668637083334</v>
+        <v>46079.83530375</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.34829836806</v>
+        <v>46114.51496503472</v>
       </c>
       <c r="D22" s="5">
-        <v>46142.494598923615</v>
+        <v>46142.66126559028</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2704,13 +2704,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.66863738426</v>
+        <v>46079.835304050925</v>
       </c>
       <c r="C23" s="8">
-        <v>46128.26517543981</v>
+        <v>46128.43184210648</v>
       </c>
       <c r="D23" s="8">
-        <v>46128.834950358796</v>
+        <v>46129.00161702547</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2769,13 +2769,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.668634560185</v>
+        <v>46079.83530122685</v>
       </c>
       <c r="C24" s="5">
-        <v>46209.613274965275</v>
+        <v>46209.77994163195</v>
       </c>
       <c r="D24" s="5">
-        <v>46209.61327666667</v>
+        <v>46209.779943333335</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2834,13 +2834,13 @@
         <v>100</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.70764284722</v>
+        <v>46079.87430951389</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.634447268516</v>
+        <v>46191.80111393519</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.63444896991</v>
+        <v>46191.801115636576</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>101</v>
@@ -2899,13 +2899,13 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46080.34373289352</v>
+        <v>46080.51039956018</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.6344592824</v>
+        <v>46191.801125949074</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.634460601854</v>
+        <v>46191.80112726852</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -2964,13 +2964,13 @@
         <v>105</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.668634918984</v>
+        <v>46079.83530158565</v>
       </c>
       <c r="C27" s="8">
-        <v>46209.54278533565</v>
+        <v>46209.70945200232</v>
       </c>
       <c r="D27" s="8">
-        <v>46209.54280181713</v>
+        <v>46209.709468483794</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>106</v>
@@ -3017,13 +3017,13 @@
         <v>108</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.66863519676</v>
+        <v>46079.83530186342</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.70815302084</v>
+        <v>46191.874819687495</v>
       </c>
       <c r="D28" s="5">
-        <v>46204.02652871527</v>
+        <v>46204.193195381944</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>109</v>
@@ -3082,13 +3082,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.668635462964</v>
+        <v>46079.83530212963</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.37739233796</v>
+        <v>46097.544059004635</v>
       </c>
       <c r="D29" s="8">
-        <v>46169.68174571759</v>
+        <v>46169.848412384265</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3143,13 +3143,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.66863569444</v>
+        <v>46079.83530236111</v>
       </c>
       <c r="C30" s="5">
-        <v>46191.70813865741</v>
+        <v>46191.87480532407</v>
       </c>
       <c r="D30" s="5">
-        <v>46191.70814038195</v>
+        <v>46191.87480704861</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3204,13 +3204,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.668636030096</v>
+        <v>46079.83530269676</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.708044768515</v>
+        <v>46191.874711435186</v>
       </c>
       <c r="D31" s="8">
-        <v>46198.029814375</v>
+        <v>46198.19648104167</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3269,13 +3269,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.668636284725</v>
+        <v>46079.83530295139</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.512557939815</v>
+        <v>46182.67922460648</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.51255994213</v>
+        <v>46182.6792266088</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3330,13 +3330,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.66863652778</v>
+        <v>46079.83530319444</v>
       </c>
       <c r="C33" s="8">
-        <v>46191.70802984954</v>
+        <v>46191.8746965162</v>
       </c>
       <c r="D33" s="8">
-        <v>46191.70803145833</v>
+        <v>46191.874698125</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3391,13 +3391,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.66863457176</v>
+        <v>46079.835301238425</v>
       </c>
       <c r="C34" s="5">
-        <v>46191.7079222801</v>
+        <v>46191.87458894676</v>
       </c>
       <c r="D34" s="5">
-        <v>46191.70793674768</v>
+        <v>46191.874603414355</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3456,13 +3456,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.66863482639</v>
+        <v>46079.835301493054</v>
       </c>
       <c r="C35" s="8">
-        <v>46114.59961186342</v>
+        <v>46114.76627853009</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.68181603009</v>
+        <v>46169.84848269676</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3517,13 +3517,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.66863512732</v>
+        <v>46079.83530179398</v>
       </c>
       <c r="C36" s="5">
-        <v>46191.707908125</v>
+        <v>46191.87457479167</v>
       </c>
       <c r="D36" s="5">
-        <v>46191.70790988426</v>
+        <v>46191.87457655092</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3578,13 +3578,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.668635486116</v>
+        <v>46079.83530215277</v>
       </c>
       <c r="C37" s="8">
-        <v>46114.65071625</v>
+        <v>46114.81738291666</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.681829548615</v>
+        <v>46169.84849621527</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3639,13 +3639,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46079.66863675926</v>
+        <v>46079.83530342593</v>
       </c>
       <c r="C38" s="5">
-        <v>46191.708328865745</v>
+        <v>46191.8749955324</v>
       </c>
       <c r="D38" s="5">
-        <v>46191.70834646991</v>
+        <v>46191.875013136574</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3704,13 +3704,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46079.668637002316</v>
+        <v>46079.83530366898</v>
       </c>
       <c r="C39" s="8">
-        <v>46191.70780684028</v>
+        <v>46191.87447350695</v>
       </c>
       <c r="D39" s="8">
-        <v>46191.70780873843</v>
+        <v>46191.87447540509</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3765,13 +3765,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.66863418982</v>
+        <v>46079.83530085648</v>
       </c>
       <c r="C40" s="5">
-        <v>46191.708312627314</v>
+        <v>46191.87497929398</v>
       </c>
       <c r="D40" s="5">
-        <v>46191.70831621528</v>
+        <v>46191.87498288194</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3826,13 +3826,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.668635752314</v>
+        <v>46079.835302418986</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.7082074537</v>
+        <v>46191.874874120374</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.7082093287</v>
+        <v>46191.874875995374</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3891,13 +3891,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.668636030096</v>
+        <v>46079.83530269676</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.59897114584</v>
+        <v>46114.765637812496</v>
       </c>
       <c r="D42" s="5">
-        <v>46209.61328395833</v>
+        <v>46209.779950625</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3952,13 +3952,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.668636296294</v>
+        <v>46079.835302962965</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.599022407405</v>
+        <v>46114.76568907408</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.59902407408</v>
+        <v>46114.765690740736</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4013,13 +4013,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.707824467594</v>
+        <v>46079.87449113426</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.59944146991</v>
+        <v>46114.76610813657</v>
       </c>
       <c r="D44" s="5">
-        <v>46204.01894546296</v>
+        <v>46204.18561212963</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4078,13 +4078,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.70790026621</v>
+        <v>46079.87456693287</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.59938703704</v>
+        <v>46114.7660537037</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.63445305555</v>
+        <v>46191.80111972222</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4139,13 +4139,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.70800302083</v>
+        <v>46079.8746696875</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.59942802083</v>
+        <v>46114.7660946875</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.599429814814</v>
+        <v>46114.766096481486</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4200,11 +4200,11 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.668636585644</v>
+        <v>46079.835303252315</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46127.52115996528</v>
+        <v>46127.68782663194</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4249,13 +4249,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.668636863425</v>
+        <v>46079.8353035301</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.62879984954</v>
+        <v>46114.7954665162</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.6288166088</v>
+        <v>46114.79548327546</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4314,13 +4314,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.668634016205</v>
+        <v>46079.83530068287</v>
       </c>
       <c r="C49" s="8">
-        <v>46127.521092986106</v>
+        <v>46127.68775965278</v>
       </c>
       <c r="D49" s="8">
-        <v>46156.03380072917</v>
+        <v>46156.20046739583</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4379,13 +4379,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46087.46219618055</v>
+        <v>46087.628862847225</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.521146377316</v>
+        <v>46127.68781304398</v>
       </c>
       <c r="D50" s="5">
-        <v>46158.82925711806</v>
+        <v>46158.99592378472</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4444,11 +4444,11 @@
         <v>187</v>
       </c>
       <c r="B51" s="8">
-        <v>46087.46223626158</v>
+        <v>46087.62890292824</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46127.5235468287</v>
+        <v>46127.69021349537</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>188</v>
@@ -4507,11 +4507,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.66863438657</v>
+        <v>46079.835301053245</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46209.62140428241</v>
+        <v>46209.78807094907</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4560,13 +4560,13 @@
         <v>194</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.66863467592</v>
+        <v>46079.835301342595</v>
       </c>
       <c r="C53" s="8">
-        <v>46209.62139626157</v>
+        <v>46209.788062928244</v>
       </c>
       <c r="D53" s="8">
-        <v>46209.62139782407</v>
+        <v>46209.78806449074</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>195</v>
@@ -4625,11 +4625,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.668634953705</v>
+        <v>46079.83530162037</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46209.621403171295</v>
+        <v>46209.78806983796</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4688,11 +4688,11 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.6686352199</v>
+        <v>46079.835301886575</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46080.41253865741</v>
+        <v>46080.57920532407</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4741,11 +4741,11 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.668635497685</v>
+        <v>46079.835302164356</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46209.62494217593</v>
+        <v>46209.79160884259</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4804,11 +4804,11 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.668635752314</v>
+        <v>46079.835302418986</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.000487129626</v>
+        <v>46191.1671537963</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>212</v>
@@ -4867,11 +4867,11 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.66863600694</v>
+        <v>46079.835302673615</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46193.03876826389</v>
+        <v>46193.205434930554</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -4930,11 +4930,11 @@
         <v>218</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.668636250004</v>
+        <v>46079.83530291667</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46158.82918858796</v>
+        <v>46158.99585525463</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>192</v>
@@ -4983,11 +4983,11 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.66863559028</v>
+        <v>46079.83530225694</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46210.645316168986</v>
+        <v>46210.81198283564</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -5046,11 +5046,11 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.66863518518</v>
+        <v>46079.835301851854</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46200.04164997685</v>
+        <v>46200.20831664352</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>56</v>
@@ -5109,11 +5109,11 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.7092312037</v>
+        <v>46079.87589787037</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46206.00076702546</v>
+        <v>46206.16743369213</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5172,11 +5172,11 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.66863652778</v>
+        <v>46079.83530319444</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46191.708324293984</v>
+        <v>46191.87499096065</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5235,11 +5235,11 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.66863596065</v>
+        <v>46079.83530262731</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46191.707918263884</v>
+        <v>46191.874584930556</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5298,11 +5298,11 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.668636296294</v>
+        <v>46079.835302962965</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46158.8292571412</v>
+        <v>46158.99592380787</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5351,11 +5351,11 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46079.66863662037</v>
+        <v>46079.83530328704</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46205.02663775463</v>
+        <v>46205.19330442129</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>217</v>
@@ -5414,11 +5414,11 @@
         <v>239</v>
       </c>
       <c r="B67" s="8">
-        <v>46079.66863695602</v>
+        <v>46079.83530362268</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46127.52116150463</v>
+        <v>46127.6878281713</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>240</v>
@@ -5477,11 +5477,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46079.66863731481</v>
+        <v>46079.83530398148</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46210.02585061343</v>
+        <v>46210.19251728009</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5540,11 +5540,11 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46079.668637627314</v>
+        <v>46079.835304293985</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46127.52116265046</v>
+        <v>46127.68782931713</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>248</v>
@@ -5603,11 +5603,11 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46080.32605201389</v>
+        <v>46080.49271868056</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46127.52116314815</v>
+        <v>46127.687829814815</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>251</v>
@@ -5666,11 +5666,11 @@
         <v>253</v>
       </c>
       <c r="B71" s="8">
-        <v>46079.668637939816</v>
+        <v>46079.83530460648</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46158.829257060184</v>
+        <v>46158.99592372685</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>189</v>
@@ -5729,11 +5729,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46079.66863826389</v>
+        <v>46079.83530493056</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46090.63800759259</v>
+        <v>46090.804674259256</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>257</v>
@@ -5792,11 +5792,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46079.66863478009</v>
+        <v>46079.83530144676</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46090.51004356482</v>
+        <v>46090.67671023148</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5839,11 +5839,11 @@
         <v>262</v>
       </c>
       <c r="B74" s="5">
-        <v>46079.66863515046</v>
+        <v>46079.83530181713</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46210.450113935185</v>
+        <v>46210.61678060185</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>263</v>
@@ -5900,11 +5900,11 @@
         <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46079.668635740745</v>
+        <v>46079.8353024074</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46097.47623357639</v>
+        <v>46097.64290024305</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>57</v>
@@ -5963,11 +5963,11 @@
         <v>270</v>
       </c>
       <c r="B76" s="5">
-        <v>46079.668636030096</v>
+        <v>46079.83530269676</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.63820487268</v>
+        <v>46090.80487153935</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>271</v>
@@ -6026,11 +6026,11 @@
         <v>273</v>
       </c>
       <c r="B77" s="8">
-        <v>46079.66863640046</v>
+        <v>46079.83530306713</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46090.63829269676</v>
+        <v>46090.80495936342</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>274</v>
@@ -6089,11 +6089,11 @@
         <v>276</v>
       </c>
       <c r="B78" s="5">
-        <v>46079.66863666667</v>
+        <v>46079.83530333333</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46090.51001115741</v>
+        <v>46090.67667782407</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>277</v>
@@ -6136,11 +6136,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46079.66863696759</v>
+        <v>46079.83530363426</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.63836675926</v>
+        <v>46090.805033425924</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6199,11 +6199,11 @@
         <v>283</v>
       </c>
       <c r="B80" s="5">
-        <v>46079.66863729167</v>
+        <v>46079.83530395833</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.348227361115</v>
+        <v>46114.51489402778</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>284</v>
@@ -6262,11 +6262,11 @@
         <v>286</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.507380740746</v>
+        <v>46090.6740474074</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.51155083333</v>
+        <v>46090.6782175</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>287</v>
@@ -6315,11 +6315,11 @@
         <v>289</v>
       </c>
       <c r="B82" s="5">
-        <v>46090.50756469907</v>
+        <v>46090.674231365745</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46090.638442048614</v>
+        <v>46090.80510871528</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>290</v>
@@ -6378,11 +6378,11 @@
         <v>292</v>
       </c>
       <c r="B83" s="8">
-        <v>46090.50777542824</v>
+        <v>46090.67444209491</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46090.63843890047</v>
+        <v>46090.80510556713</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>293</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -362,334 +362,334 @@
     <t>Generación OC Alabe ot 4264,Fabricación Alabe ot 4264</t>
   </si>
   <si>
+    <t>1213459189153328</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe ot 4264</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe ot 4264,Alabe  ot 4264</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>1213459189153329</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe ot 4264</t>
+  </si>
+  <si>
+    <t>Alabe  ot 4264,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1213459189153330</t>
+  </si>
+  <si>
+    <t>Tablero ot 4265 - ot 4266</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros  ot 4265 - ot 4266,Fabricación Tablero  ot 4265 - ot 4266</t>
+  </si>
+  <si>
+    <t>1213459189153331</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros  ot 4265 - ot 4266</t>
+  </si>
+  <si>
+    <t>Fabricación Tablero  ot 4265 - ot 4266,Tablero ot 4265 - ot 4266</t>
+  </si>
+  <si>
+    <t>1213459189153332</t>
+  </si>
+  <si>
+    <t>Fabricación Tablero  ot 4265 - ot 4266</t>
+  </si>
+  <si>
+    <t>Tablero ot 4265 - ot 4266,Recepcion Tableros</t>
+  </si>
+  <si>
+    <t>1213459189153336</t>
+  </si>
+  <si>
+    <t>Motor ot 4264</t>
+  </si>
+  <si>
+    <t>Generación OC motor ot 4264,Fabricación motor ot 4264,Planos motor proveedor ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189207060</t>
+  </si>
+  <si>
+    <t>Generación OC motor ot 4264</t>
+  </si>
+  <si>
+    <t>Fabricación motor ot 4264,Motor ot 4264,Planos motor proveedor ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189207061</t>
+  </si>
+  <si>
+    <t>Fabricación motor ot 4264</t>
+  </si>
+  <si>
+    <t>Motor ot 4264,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1213459189207062</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor ot 4264</t>
+  </si>
+  <si>
+    <t>Motor ot 4264,Ingenieria y diseño:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1213459189153333</t>
+  </si>
+  <si>
+    <t>rodete ot 4264</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete ot 4264,Fabricación Rodete ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189153334</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete ot 4264</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete ot 4264,rodete ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189153335</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete ot 4264</t>
+  </si>
+  <si>
+    <t>rodete ot 4264,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1213459189207063</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento:</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales,Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
+    <t>1213459189207064</t>
+  </si>
+  <si>
+    <t>Generación OC materiales</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales,Materiales a codigo // compras locales aprovisionamientomiento:</t>
+  </si>
+  <si>
+    <t>1213459189207065</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento:,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213458788103037</t>
+  </si>
+  <si>
+    <t>Sensores</t>
+  </si>
+  <si>
+    <t>Generación OC Sensores,Fabricacion Sensores</t>
+  </si>
+  <si>
+    <t>1213458788103039</t>
+  </si>
+  <si>
+    <t>Generación OC Sensores</t>
+  </si>
+  <si>
+    <t>Fabricacion Sensores,Sensores</t>
+  </si>
+  <si>
+    <t>1213458788103040</t>
+  </si>
+  <si>
+    <t>Fabricacion Sensores</t>
+  </si>
+  <si>
+    <t>Sensores,Recepcion Sensores</t>
+  </si>
+  <si>
+    <t>1213459189207066</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor ot 4264,Planos preliminar,Check plano,Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213459189207067</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Planos definitivos,Ingenieria Y diseño</t>
+  </si>
+  <si>
+    <t>1213459189207068</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor ot 4264</t>
+  </si>
+  <si>
+    <t>Check plano</t>
+  </si>
+  <si>
+    <t>1213560053852552</t>
+  </si>
+  <si>
+    <t>Armado,Control de calidad Armado,Ingenieria y diseño:,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensor</t>
+  </si>
+  <si>
+    <t>1213560053852553</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>RE-PINTADO,Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>1213459189207069</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213459189207070</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:</t>
+  </si>
+  <si>
+    <t>1213459189207071</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega:,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1213459189207072</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1213459189207073</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>Caldereria:,Armado,Armado</t>
+  </si>
+  <si>
+    <t>1213459189207074</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Check plano</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213459189207075</t>
+  </si>
+  <si>
+    <t>Armado,Check plano</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>1213459189207076</t>
+  </si>
+  <si>
+    <t>Recepcion Sensores,Recepcion Rodete,Recepcion Tableros,Recepcion Alabe,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1213459189207079</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Alabe</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213459189153328</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe ot 4264</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe ot 4264,Alabe  ot 4264</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>1213459189153329</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe ot 4264</t>
-  </si>
-  <si>
-    <t>Alabe  ot 4264,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1213459189153330</t>
-  </si>
-  <si>
-    <t>Tablero ot 4265 - ot 4266</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros  ot 4265 - ot 4266,Fabricación Tablero  ot 4265 - ot 4266</t>
-  </si>
-  <si>
-    <t>1213459189153331</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros  ot 4265 - ot 4266</t>
-  </si>
-  <si>
-    <t>Fabricación Tablero  ot 4265 - ot 4266,Tablero ot 4265 - ot 4266</t>
-  </si>
-  <si>
-    <t>1213459189153332</t>
-  </si>
-  <si>
-    <t>Fabricación Tablero  ot 4265 - ot 4266</t>
-  </si>
-  <si>
-    <t>Tablero ot 4265 - ot 4266,Recepcion Tableros</t>
-  </si>
-  <si>
-    <t>1213459189153336</t>
-  </si>
-  <si>
-    <t>Motor ot 4264</t>
-  </si>
-  <si>
-    <t>Generación OC motor ot 4264,Fabricación motor ot 4264,Planos motor proveedor ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189207060</t>
-  </si>
-  <si>
-    <t>Generación OC motor ot 4264</t>
-  </si>
-  <si>
-    <t>Fabricación motor ot 4264,Motor ot 4264,Planos motor proveedor ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189207061</t>
-  </si>
-  <si>
-    <t>Fabricación motor ot 4264</t>
-  </si>
-  <si>
-    <t>Motor ot 4264,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1213459189207062</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor ot 4264</t>
-  </si>
-  <si>
-    <t>Motor ot 4264,Ingenieria y diseño:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1213459189153333</t>
-  </si>
-  <si>
-    <t>rodete ot 4264</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete ot 4264,Fabricación Rodete ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189153334</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete ot 4264</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete ot 4264,rodete ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189153335</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete ot 4264</t>
-  </si>
-  <si>
-    <t>rodete ot 4264,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1213459189207063</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento:</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales,Fabricacion a codigo y compras locales</t>
-  </si>
-  <si>
-    <t>1213459189207064</t>
-  </si>
-  <si>
-    <t>Generación OC materiales</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales,Materiales a codigo // compras locales aprovisionamientomiento:</t>
-  </si>
-  <si>
-    <t>1213459189207065</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento:,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213458788103037</t>
-  </si>
-  <si>
-    <t>Sensores</t>
-  </si>
-  <si>
-    <t>Generación OC Sensores,Fabricacion Sensores</t>
-  </si>
-  <si>
-    <t>1213458788103039</t>
-  </si>
-  <si>
-    <t>Generación OC Sensores</t>
-  </si>
-  <si>
-    <t>Fabricacion Sensores,Sensores</t>
-  </si>
-  <si>
-    <t>1213458788103040</t>
-  </si>
-  <si>
-    <t>Fabricacion Sensores</t>
-  </si>
-  <si>
-    <t>Sensores,Recepcion Sensores</t>
-  </si>
-  <si>
-    <t>1213459189207066</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor ot 4264,Planos preliminar,Check plano,Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213459189207067</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Planos definitivos,Ingenieria Y diseño</t>
-  </si>
-  <si>
-    <t>1213459189207068</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor ot 4264</t>
-  </si>
-  <si>
-    <t>Check plano</t>
-  </si>
-  <si>
-    <t>1213560053852552</t>
-  </si>
-  <si>
-    <t>Armado,Control de calidad Armado,Ingenieria y diseño:,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensor</t>
-  </si>
-  <si>
-    <t>1213560053852553</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>RE-PINTADO,Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>1213459189207069</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213459189207070</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:</t>
-  </si>
-  <si>
-    <t>1213459189207071</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega:,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1213459189207072</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1213459189207073</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Caldereria:,Armado,Armado</t>
-  </si>
-  <si>
-    <t>1213459189207074</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Check plano</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213459189207075</t>
-  </si>
-  <si>
-    <t>Armado,Check plano</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>1213459189207076</t>
-  </si>
-  <si>
-    <t>Recepcion Sensores,Recepcion Rodete,Recepcion Tableros,Recepcion Alabe,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1213459189207079</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Alabe</t>
   </si>
   <si>
     <t>1213459189207078</t>
@@ -3023,7 +3023,7 @@
         <v>46191.874819687495</v>
       </c>
       <c r="D28" s="5">
-        <v>46204.193195381944</v>
+        <v>46212.17176924768</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>109</v>
@@ -3073,13 +3073,13 @@
       <c r="T28" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U28" s="12" t="s">
-        <v>113</v>
+      <c r="U28" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46079.83530212963</v>
@@ -3091,7 +3091,7 @@
         <v>46169.848412384265</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3124,7 +3124,7 @@
         <v>83</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3135,12 +3135,12 @@
         <v>58</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46079.83530236111</v>
@@ -3152,7 +3152,7 @@
         <v>46191.87480704861</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3182,10 +3182,10 @@
         <v>109</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3196,12 +3196,12 @@
         <v>58</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B31" s="8">
         <v>46079.83530269676</v>
@@ -3213,7 +3213,7 @@
         <v>46198.19648104167</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3243,7 +3243,7 @@
         <v>106</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>106</v>
@@ -3266,7 +3266,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46079.83530295139</v>
@@ -3278,7 +3278,7 @@
         <v>46182.6792266088</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3305,13 +3305,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3322,12 +3322,12 @@
         <v>58</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46079.83530319444</v>
@@ -3339,7 +3339,7 @@
         <v>46191.874698125</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3366,13 +3366,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3383,12 +3383,12 @@
         <v>58</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46079.835301238425</v>
@@ -3400,7 +3400,7 @@
         <v>46191.874603414355</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3430,7 +3430,7 @@
         <v>106</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>106</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46079.835301493054</v>
@@ -3465,7 +3465,7 @@
         <v>46169.84848269676</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3492,13 +3492,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3509,12 +3509,12 @@
         <v>58</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46079.83530179398</v>
@@ -3526,7 +3526,7 @@
         <v>46191.87457655092</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3553,13 +3553,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3570,12 +3570,12 @@
         <v>58</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46079.83530215277</v>
@@ -3587,7 +3587,7 @@
         <v>46169.84849621527</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -3614,13 +3614,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3631,12 +3631,12 @@
         <v>58</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46079.83530342593</v>
@@ -3648,7 +3648,7 @@
         <v>46191.875013136574</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3678,7 +3678,7 @@
         <v>106</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>106</v>
@@ -3701,7 +3701,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46079.83530366898</v>
@@ -3713,7 +3713,7 @@
         <v>46191.87447540509</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
@@ -3740,13 +3740,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>92</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3757,12 +3757,12 @@
         <v>58</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46079.83530085648</v>
@@ -3774,7 +3774,7 @@
         <v>46191.87498288194</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -3801,13 +3801,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3818,12 +3818,12 @@
         <v>58</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>46079.835302418986</v>
@@ -3835,16 +3835,16 @@
         <v>46191.874875995374</v>
       </c>
       <c r="E41" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="9" t="s">
+      <c r="H41" s="9" t="s">
         <v>153</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>154</v>
       </c>
       <c r="I41" s="8">
         <v>46097</v>
@@ -3865,7 +3865,7 @@
         <v>106</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>106</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46079.83530269676</v>
@@ -3900,16 +3900,16 @@
         <v>46209.779950625</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I42" s="5">
         <v>46097</v>
@@ -3927,13 +3927,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3944,12 +3944,12 @@
         <v>58</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46079.835302962965</v>
@@ -3961,16 +3961,16 @@
         <v>46114.765690740736</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>153</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>154</v>
       </c>
       <c r="I43" s="8">
         <v>46115</v>
@@ -3988,13 +3988,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4005,12 +4005,12 @@
         <v>58</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46079.87449113426</v>
@@ -4022,16 +4022,16 @@
         <v>46204.18561212963</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I44" s="5">
         <v>46097</v>
@@ -4052,7 +4052,7 @@
         <v>106</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>106</v>
@@ -4075,7 +4075,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
         <v>46079.87456693287</v>
@@ -4087,16 +4087,16 @@
         <v>46191.80111972222</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>153</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>154</v>
       </c>
       <c r="I45" s="8">
         <v>46097</v>
@@ -4114,13 +4114,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>101</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4131,12 +4131,12 @@
         <v>58</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46079.8746696875</v>
@@ -4148,16 +4148,16 @@
         <v>46114.766096481486</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I46" s="5">
         <v>46126</v>
@@ -4175,13 +4175,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4192,12 +4192,12 @@
         <v>58</v>
       </c>
       <c r="U46" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46079.835303252315</v>
@@ -4207,7 +4207,7 @@
         <v>46127.68782663194</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>25</v>
@@ -4231,7 +4231,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>26</v>
@@ -4246,7 +4246,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B48" s="5">
         <v>46079.8353035301</v>
@@ -4258,16 +4258,16 @@
         <v>46114.79548327546</v>
       </c>
       <c r="E48" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="6" t="s">
+      <c r="H48" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="I48" s="5">
         <v>46093</v>
@@ -4285,13 +4285,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q48" s="5">
         <v>46093</v>
@@ -4311,7 +4311,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B49" s="8">
         <v>46079.83530068287</v>
@@ -4323,16 +4323,16 @@
         <v>46156.20046739583</v>
       </c>
       <c r="E49" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="9" t="s">
+      <c r="H49" s="9" t="s">
         <v>181</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>182</v>
       </c>
       <c r="I49" s="8">
         <v>46149</v>
@@ -4350,13 +4350,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O49" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="P49" s="9" t="s">
         <v>183</v>
-      </c>
-      <c r="P49" s="9" t="s">
-        <v>184</v>
       </c>
       <c r="Q49" s="8">
         <v>46149</v>
@@ -4376,7 +4376,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46087.628862847225</v>
@@ -4388,16 +4388,16 @@
         <v>46158.99592378472</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="I50" s="5">
         <v>46156</v>
@@ -4415,13 +4415,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q50" s="5">
         <v>46156</v>
@@ -4441,7 +4441,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B51" s="8">
         <v>46087.62890292824</v>
@@ -4451,16 +4451,16 @@
         <v>46127.69021349537</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>181</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>182</v>
       </c>
       <c r="I51" s="8">
         <v>46243</v>
@@ -4478,13 +4478,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O51" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="P51" s="9" t="s">
         <v>189</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>190</v>
       </c>
       <c r="Q51" s="8">
         <v>46243</v>
@@ -4499,22 +4499,24 @@
         <v>58</v>
       </c>
       <c r="U51" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5">
         <v>46079.835301053245</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46211.896528136574</v>
+      </c>
       <c r="D52" s="5">
-        <v>46209.78807094907</v>
+        <v>46211.90007753472</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4538,26 +4540,24 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
-      <c r="S52" s="6">
-        <v>1</v>
-      </c>
+      <c r="S52" s="6"/>
       <c r="T52" s="10" t="s">
         <v>31</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B53" s="8">
         <v>46079.835301342595</v>
@@ -4569,16 +4569,16 @@
         <v>46209.78806449074</v>
       </c>
       <c r="E53" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="F53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="9" t="s">
+      <c r="H53" s="9" t="s">
         <v>196</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>197</v>
       </c>
       <c r="I53" s="8">
         <v>46147</v>
@@ -4596,13 +4596,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q53" s="8">
         <v>46147</v>
@@ -4622,26 +4622,26 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46079.83530162037</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46209.78806983796</v>
+        <v>46211.896555671294</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I54" s="5">
         <v>46149</v>
@@ -4659,13 +4659,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="5">
         <v>46149</v>
@@ -4676,8 +4676,8 @@
       <c r="S54" s="6">
         <v>1</v>
       </c>
-      <c r="T54" s="12" t="s">
-        <v>81</v>
+      <c r="T54" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U54" s="11" t="s">
         <v>32</v>
@@ -4685,7 +4685,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B55" s="8">
         <v>46079.835301886575</v>
@@ -4695,7 +4695,7 @@
         <v>46080.57920532407</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4719,7 +4719,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4733,31 +4733,31 @@
         <v>58</v>
       </c>
       <c r="U55" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46079.835302164356</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46209.79160884259</v>
+        <v>46211.89656313657</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I56" s="5">
         <v>46153</v>
@@ -4775,13 +4775,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q56" s="5">
         <v>46153</v>
@@ -4801,7 +4801,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B57" s="8">
         <v>46079.835302418986</v>
@@ -4811,16 +4811,16 @@
         <v>46191.1671537963</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I57" s="8">
         <v>46162</v>
@@ -4838,13 +4838,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O57" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="P57" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="P57" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="Q57" s="8">
         <v>46162</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46079.835302673615</v>
@@ -4874,16 +4874,16 @@
         <v>46193.205434930554</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I58" s="5">
         <v>46191</v>
@@ -4901,13 +4901,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>216</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>217</v>
       </c>
       <c r="Q58" s="5">
         <v>46191</v>
@@ -4927,7 +4927,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B59" s="8">
         <v>46079.83530291667</v>
@@ -4937,7 +4937,7 @@
         <v>46158.99585525463</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -4961,7 +4961,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -4975,12 +4975,12 @@
         <v>58</v>
       </c>
       <c r="U59" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46079.83530225694</v>
@@ -4990,16 +4990,16 @@
         <v>46210.81198283564</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I60" s="5">
         <v>46212</v>
@@ -5017,13 +5017,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q60" s="5">
         <v>46212</v>
@@ -5038,7 +5038,7 @@
         <v>81</v>
       </c>
       <c r="U60" s="12" t="s">
-        <v>113</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5059,10 +5059,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>196</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>197</v>
       </c>
       <c r="I61" s="8">
         <v>46198</v>
@@ -5080,10 +5080,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>224</v>
@@ -5122,10 +5122,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I62" s="5">
         <v>46204</v>
@@ -5143,10 +5143,10 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>227</v>
@@ -5185,10 +5185,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>196</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>197</v>
       </c>
       <c r="I63" s="8">
         <v>46149</v>
@@ -5206,10 +5206,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>230</v>
@@ -5248,10 +5248,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I64" s="5">
         <v>46234</v>
@@ -5269,10 +5269,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>233</v>
@@ -5290,7 +5290,7 @@
         <v>81</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5343,7 +5343,7 @@
         <v>58</v>
       </c>
       <c r="U65" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5355,10 +5355,10 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46205.19330442129</v>
+        <v>46212.167524178236</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5388,7 +5388,7 @@
         <v>235</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>238</v>
@@ -5406,7 +5406,7 @@
         <v>58</v>
       </c>
       <c r="U66" s="12" t="s">
-        <v>113</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5469,7 +5469,7 @@
         <v>58</v>
       </c>
       <c r="U67" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5532,7 +5532,7 @@
         <v>58</v>
       </c>
       <c r="U68" s="12" t="s">
-        <v>113</v>
+        <v>222</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46127.68782931713</v>
+        <v>46212.201619583335</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>248</v>
@@ -5594,8 +5594,8 @@
       <c r="T69" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="U69" s="10" t="s">
-        <v>117</v>
+      <c r="U69" s="12" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5658,7 +5658,7 @@
         <v>58</v>
       </c>
       <c r="U70" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5673,7 +5673,7 @@
         <v>46158.99592372685</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5721,7 +5721,7 @@
         <v>58</v>
       </c>
       <c r="U71" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5766,7 +5766,7 @@
         <v>235</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>258</v>
@@ -5784,7 +5784,7 @@
         <v>58</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5892,7 +5892,7 @@
         <v>58</v>
       </c>
       <c r="U74" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5955,7 +5955,7 @@
         <v>58</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -5976,10 +5976,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I76" s="5">
         <v>46251</v>
@@ -6018,7 +6018,7 @@
         <v>58</v>
       </c>
       <c r="U76" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6039,10 +6039,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I77" s="8">
         <v>46252</v>
@@ -6081,7 +6081,7 @@
         <v>58</v>
       </c>
       <c r="U77" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6191,7 +6191,7 @@
         <v>58</v>
       </c>
       <c r="U79" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6254,7 +6254,7 @@
         <v>58</v>
       </c>
       <c r="U80" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6307,7 +6307,7 @@
         <v>58</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6370,7 +6370,7 @@
         <v>58</v>
       </c>
       <c r="U82" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6433,7 +6433,7 @@
         <v>58</v>
       </c>
       <c r="U83" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -4987,7 +4987,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46210.81198283564</v>
+        <v>46213.250424224534</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>220</v>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46212.167524178236</v>
+        <v>46213.187978657406</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>216</v>
@@ -5405,8 +5405,8 @@
       <c r="T66" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="U66" s="12" t="s">
-        <v>222</v>
+      <c r="U66" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -689,79 +689,79 @@
     <t>Bodega:,Montaje Alabe</t>
   </si>
   <si>
+    <t>1213459189207078</t>
+  </si>
+  <si>
+    <t>Bodega:,Revisión tableros pruebas,Ingenieria Servicios:</t>
+  </si>
+  <si>
+    <t>1213458788103048</t>
+  </si>
+  <si>
+    <t>Recepcion Sensores</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje sensor</t>
+  </si>
+  <si>
+    <t>1213459189207077</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1213459189207080</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje motor</t>
+  </si>
+  <si>
+    <t>1213459189207081</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje motor,Montaje Rodete,Montaje sensor,Montaje Alabe,Pruebas FAT,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1213459189207082</t>
+  </si>
+  <si>
+    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensor,Montaje:</t>
+  </si>
+  <si>
+    <t>1213459189207083</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion motor,Check plano</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,Montaje:</t>
+  </si>
+  <si>
+    <t>1213459189207084</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion Alabe,Check plano</t>
+  </si>
+  <si>
+    <t>Montaje Rodete,Pruebas FAT,Montaje:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213459189207078</t>
-  </si>
-  <si>
-    <t>Bodega:,Revisión tableros pruebas,Ingenieria Servicios:</t>
-  </si>
-  <si>
-    <t>1213458788103048</t>
-  </si>
-  <si>
-    <t>Recepcion Sensores</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje sensor</t>
-  </si>
-  <si>
-    <t>1213459189207077</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1213459189207080</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje motor</t>
-  </si>
-  <si>
-    <t>1213459189207081</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje motor,Montaje Rodete,Montaje sensor,Montaje Alabe,Pruebas FAT,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1213459189207082</t>
-  </si>
-  <si>
-    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensor,Montaje:</t>
-  </si>
-  <si>
-    <t>1213459189207083</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion motor,Check plano</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,Montaje:</t>
-  </si>
-  <si>
-    <t>1213459189207084</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion Alabe,Check plano</t>
-  </si>
-  <si>
-    <t>Montaje Rodete,Pruebas FAT,Montaje:</t>
   </si>
   <si>
     <t>1213459189207085</t>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46213.250424224534</v>
+        <v>46214.176594108794</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>220</v>
@@ -5037,13 +5037,13 @@
       <c r="T60" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="U60" s="12" t="s">
-        <v>222</v>
+      <c r="U60" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B61" s="8">
         <v>46079.835301851854</v>
@@ -5086,7 +5086,7 @@
         <v>127</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q61" s="8">
         <v>46198</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46079.87589787037</v>
@@ -5116,7 +5116,7 @@
         <v>46206.16743369213</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5149,7 +5149,7 @@
         <v>168</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q62" s="5">
         <v>46204</v>
@@ -5169,7 +5169,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B63" s="8">
         <v>46079.83530319444</v>
@@ -5179,7 +5179,7 @@
         <v>46191.87499096065</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
@@ -5212,7 +5212,7 @@
         <v>148</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q63" s="8">
         <v>46149</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B64" s="5">
         <v>46079.83530262731</v>
@@ -5242,7 +5242,7 @@
         <v>46191.874584930556</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5275,7 +5275,7 @@
         <v>136</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q64" s="5">
         <v>46234</v>
@@ -5295,7 +5295,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B65" s="8">
         <v>46079.835302962965</v>
@@ -5305,7 +5305,7 @@
         <v>46158.99592380787</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5329,7 +5329,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5348,7 +5348,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B66" s="5">
         <v>46079.83530328704</v>
@@ -5385,13 +5385,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>213</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q66" s="5">
         <v>46195</v>
@@ -5411,7 +5411,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B67" s="8">
         <v>46079.83530362268</v>
@@ -5421,7 +5421,7 @@
         <v>46127.6878281713</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5448,13 +5448,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O67" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="P67" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="P67" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="Q67" s="8">
         <v>46238</v>
@@ -5474,7 +5474,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46079.83530398148</v>
@@ -5484,7 +5484,7 @@
         <v>46210.19251728009</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5511,13 +5511,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>245</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>246</v>
       </c>
       <c r="Q68" s="5">
         <v>46216</v>
@@ -5532,7 +5532,7 @@
         <v>58</v>
       </c>
       <c r="U68" s="12" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5574,13 +5574,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O69" s="9" t="s">
         <v>249</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q69" s="8">
         <v>46218</v>
@@ -5595,7 +5595,7 @@
         <v>58</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5637,13 +5637,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>252</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5700,7 +5700,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>254</v>
@@ -5763,7 +5763,7 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>187</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46127.687829814815</v>
+        <v>46216.19986287037</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>251</v>
@@ -5657,8 +5657,8 @@
       <c r="T70" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="U70" s="10" t="s">
-        <v>116</v>
+      <c r="U70" s="12" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -4934,7 +4934,7 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46158.99585525463</v>
+        <v>46216.76549305556</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>191</v>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46200.20831664352</v>
+        <v>46216.766091377314</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>56</v>
@@ -5111,9 +5111,11 @@
       <c r="B62" s="5">
         <v>46079.87589787037</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46216.76548623842</v>
+      </c>
       <c r="D62" s="5">
-        <v>46206.16743369213</v>
+        <v>46216.765501898146</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>225</v>
@@ -5158,10 +5160,10 @@
         <v>46205</v>
       </c>
       <c r="S62" s="6">
-        <v>0</v>
-      </c>
-      <c r="T62" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="T62" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U62" s="11" t="s">
         <v>32</v>
@@ -5237,9 +5239,11 @@
       <c r="B64" s="5">
         <v>46079.83530262731</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46216.7654346412</v>
+      </c>
       <c r="D64" s="5">
-        <v>46191.874584930556</v>
+        <v>46216.765453831016</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5284,10 +5288,10 @@
         <v>46237</v>
       </c>
       <c r="S64" s="6">
-        <v>0</v>
-      </c>
-      <c r="T64" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="T64" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U64" s="10" t="s">
         <v>116</v>
@@ -5418,7 +5422,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46127.6878281713</v>
+        <v>46216.76544502315</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>239</v>
@@ -5607,7 +5611,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46216.19986287037</v>
+        <v>46216.765493900464</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>251</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -5485,7 +5485,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46210.19251728009</v>
+        <v>46217.16747002315</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>243</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -4513,7 +4513,7 @@
         <v>46211.896528136574</v>
       </c>
       <c r="D52" s="5">
-        <v>46211.90007753472</v>
+        <v>46217.8196680324</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4548,8 +4548,8 @@
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
       <c r="S52" s="6"/>
-      <c r="T52" s="10" t="s">
-        <v>31</v>
+      <c r="T52" s="12" t="s">
+        <v>81</v>
       </c>
       <c r="U52" s="10" t="s">
         <v>116</v>
@@ -4627,9 +4627,11 @@
       <c r="B54" s="5">
         <v>46079.83530162037</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46217.81965075231</v>
+      </c>
       <c r="D54" s="5">
-        <v>46211.896555671294</v>
+        <v>46217.81965280093</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4745,7 +4747,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46211.89656313657</v>
+        <v>46217.81965958333</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>205</v>
@@ -5050,7 +5052,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46216.766091377314</v>
+        <v>46217.768278020834</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>56</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -761,16 +761,16 @@
     <t>Montaje Rodete,Pruebas FAT,Montaje:</t>
   </si>
   <si>
+    <t>1213459189207085</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,Revestimiento,Recepcion Rodete,Check plano</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213459189207085</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,Revestimiento,Recepcion Rodete,Check plano</t>
   </si>
   <si>
     <t>1213458788103121</t>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46217.16747002315</v>
+        <v>46218.19199363426</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>243</v>
@@ -5537,13 +5537,13 @@
       <c r="T68" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="U68" s="12" t="s">
-        <v>246</v>
+      <c r="U68" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B69" s="8">
         <v>46079.835304293985</v>
@@ -5553,7 +5553,7 @@
         <v>46212.201619583335</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5583,7 +5583,7 @@
         <v>234</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>241</v>
@@ -5601,7 +5601,7 @@
         <v>58</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5664,7 +5664,7 @@
         <v>58</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="291">
   <si>
     <t>50001518 - EQ. CHAPARRAL</t>
   </si>
@@ -302,9 +302,6 @@
     <t>propuesta nucleo rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete ot 4264</t>
   </si>
   <si>
@@ -312,12 +309,6 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC materiales</t>
@@ -2719,11 +2710,9 @@
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>93</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H23" s="9"/>
       <c r="I23" s="8">
         <v>46093</v>
       </c>
@@ -2746,7 +2735,7 @@
         <v>66</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="8">
         <v>46093</v>
@@ -2766,7 +2755,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B24" s="5">
         <v>46079.83530122685</v>
@@ -2778,17 +2767,15 @@
         <v>46209.779943333335</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H24" s="6"/>
       <c r="I24" s="5">
         <v>46093</v>
       </c>
@@ -2811,7 +2798,7 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Q24" s="5">
         <v>46093</v>
@@ -2831,7 +2818,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B25" s="8">
         <v>46079.87430951389</v>
@@ -2843,7 +2830,7 @@
         <v>46191.801115636576</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -2876,7 +2863,7 @@
         <v>69</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q25" s="8">
         <v>46093</v>
@@ -2896,7 +2883,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B26" s="5">
         <v>46080.51039956018</v>
@@ -2908,7 +2895,7 @@
         <v>46191.80112726852</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -2961,7 +2948,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B27" s="8">
         <v>46079.83530158565</v>
@@ -2973,7 +2960,7 @@
         <v>46209.709468483794</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>25</v>
@@ -2997,7 +2984,7 @@
         <v>26</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>26</v>
@@ -3014,7 +3001,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B28" s="5">
         <v>46079.83530186342</v>
@@ -3026,16 +3013,16 @@
         <v>46212.17176924768</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I28" s="5">
         <v>46097</v>
@@ -3053,13 +3040,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="Q28" s="5">
         <v>46097</v>
@@ -3079,7 +3066,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B29" s="8">
         <v>46079.83530212963</v>
@@ -3091,16 +3078,16 @@
         <v>46169.848412384265</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I29" s="8">
         <v>46097</v>
@@ -3118,13 +3105,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>83</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3135,12 +3122,12 @@
         <v>58</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B30" s="5">
         <v>46079.83530236111</v>
@@ -3152,16 +3139,16 @@
         <v>46191.87480704861</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I30" s="5">
         <v>46099</v>
@@ -3179,13 +3166,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3196,12 +3183,12 @@
         <v>58</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B31" s="8">
         <v>46079.83530269676</v>
@@ -3213,16 +3200,16 @@
         <v>46198.19648104167</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I31" s="8">
         <v>46091</v>
@@ -3240,13 +3227,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="Q31" s="8">
         <v>46091</v>
@@ -3266,7 +3253,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B32" s="5">
         <v>46079.83530295139</v>
@@ -3278,16 +3265,16 @@
         <v>46182.6792266088</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I32" s="5">
         <v>46091</v>
@@ -3305,13 +3292,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3322,12 +3309,12 @@
         <v>58</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B33" s="8">
         <v>46079.83530319444</v>
@@ -3339,16 +3326,16 @@
         <v>46191.874698125</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I33" s="8">
         <v>46100</v>
@@ -3366,13 +3353,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="O33" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="O33" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="P33" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3383,12 +3370,12 @@
         <v>58</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5">
         <v>46079.835301238425</v>
@@ -3400,16 +3387,16 @@
         <v>46191.874603414355</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I34" s="5">
         <v>46090</v>
@@ -3427,13 +3414,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="Q34" s="5">
         <v>46090</v>
@@ -3453,7 +3440,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B35" s="8">
         <v>46079.835301493054</v>
@@ -3465,16 +3452,16 @@
         <v>46169.84848269676</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I35" s="8">
         <v>46090</v>
@@ -3492,13 +3479,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3509,12 +3496,12 @@
         <v>58</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46079.83530179398</v>
@@ -3526,16 +3513,16 @@
         <v>46191.87457655092</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I36" s="5">
         <v>46108</v>
@@ -3553,13 +3540,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="O36" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="O36" s="6" t="s">
-        <v>133</v>
-      </c>
       <c r="P36" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3570,12 +3557,12 @@
         <v>58</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B37" s="8">
         <v>46079.83530215277</v>
@@ -3587,16 +3574,16 @@
         <v>46169.84849621527</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I37" s="8">
         <v>46108</v>
@@ -3614,13 +3601,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O37" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="O37" s="9" t="s">
-        <v>133</v>
-      </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3631,12 +3618,12 @@
         <v>58</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46079.83530342593</v>
@@ -3648,16 +3635,16 @@
         <v>46191.875013136574</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I38" s="5">
         <v>46097</v>
@@ -3675,13 +3662,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="Q38" s="5">
         <v>46097</v>
@@ -3701,7 +3688,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B39" s="8">
         <v>46079.83530366898</v>
@@ -3713,16 +3700,16 @@
         <v>46191.87447540509</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I39" s="8">
         <v>46097</v>
@@ -3740,13 +3727,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>92</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3757,12 +3744,12 @@
         <v>58</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46079.83530085648</v>
@@ -3774,16 +3761,16 @@
         <v>46191.87498288194</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I40" s="5">
         <v>46099</v>
@@ -3801,13 +3788,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="O40" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="O40" s="6" t="s">
-        <v>145</v>
-      </c>
       <c r="P40" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3818,12 +3805,12 @@
         <v>58</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B41" s="8">
         <v>46079.835302418986</v>
@@ -3835,16 +3822,16 @@
         <v>46191.874875995374</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I41" s="8">
         <v>46097</v>
@@ -3862,13 +3849,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="Q41" s="8">
         <v>46097</v>
@@ -3888,7 +3875,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46079.83530269676</v>
@@ -3900,16 +3887,16 @@
         <v>46209.779950625</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I42" s="5">
         <v>46097</v>
@@ -3927,13 +3914,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3944,12 +3931,12 @@
         <v>58</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B43" s="8">
         <v>46079.835302962965</v>
@@ -3961,16 +3948,16 @@
         <v>46114.765690740736</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I43" s="8">
         <v>46115</v>
@@ -3988,13 +3975,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4005,12 +3992,12 @@
         <v>58</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B44" s="5">
         <v>46079.87449113426</v>
@@ -4022,16 +4009,16 @@
         <v>46204.18561212963</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I44" s="5">
         <v>46097</v>
@@ -4049,13 +4036,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="Q44" s="5">
         <v>46097</v>
@@ -4075,7 +4062,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B45" s="8">
         <v>46079.87456693287</v>
@@ -4087,16 +4074,16 @@
         <v>46191.80111972222</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I45" s="8">
         <v>46097</v>
@@ -4114,13 +4101,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4131,12 +4118,12 @@
         <v>58</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B46" s="5">
         <v>46079.8746696875</v>
@@ -4148,16 +4135,16 @@
         <v>46114.766096481486</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I46" s="5">
         <v>46126</v>
@@ -4175,13 +4162,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O46" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="O46" s="6" t="s">
-        <v>165</v>
-      </c>
       <c r="P46" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4192,12 +4179,12 @@
         <v>58</v>
       </c>
       <c r="U46" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B47" s="8">
         <v>46079.835303252315</v>
@@ -4207,7 +4194,7 @@
         <v>46127.68782663194</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>25</v>
@@ -4231,7 +4218,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>26</v>
@@ -4246,7 +4233,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B48" s="5">
         <v>46079.8353035301</v>
@@ -4258,16 +4245,16 @@
         <v>46114.79548327546</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I48" s="5">
         <v>46093</v>
@@ -4285,13 +4272,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Q48" s="5">
         <v>46093</v>
@@ -4311,7 +4298,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B49" s="8">
         <v>46079.83530068287</v>
@@ -4323,16 +4310,16 @@
         <v>46156.20046739583</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I49" s="8">
         <v>46149</v>
@@ -4350,13 +4337,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Q49" s="8">
         <v>46149</v>
@@ -4376,7 +4363,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B50" s="5">
         <v>46087.628862847225</v>
@@ -4388,16 +4375,16 @@
         <v>46158.99592378472</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I50" s="5">
         <v>46156</v>
@@ -4415,13 +4402,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="Q50" s="5">
         <v>46156</v>
@@ -4441,7 +4428,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B51" s="8">
         <v>46087.62890292824</v>
@@ -4451,16 +4438,16 @@
         <v>46127.69021349537</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I51" s="8">
         <v>46243</v>
@@ -4478,13 +4465,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q51" s="8">
         <v>46243</v>
@@ -4499,12 +4486,12 @@
         <v>58</v>
       </c>
       <c r="U51" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B52" s="5">
         <v>46079.835301053245</v>
@@ -4516,7 +4503,7 @@
         <v>46217.8196680324</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4540,7 +4527,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4552,12 +4539,12 @@
         <v>81</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B53" s="8">
         <v>46079.835301342595</v>
@@ -4569,16 +4556,16 @@
         <v>46209.78806449074</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I53" s="8">
         <v>46147</v>
@@ -4596,13 +4583,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="Q53" s="8">
         <v>46147</v>
@@ -4622,7 +4609,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46079.83530162037</v>
@@ -4634,16 +4621,16 @@
         <v>46217.81965280093</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I54" s="5">
         <v>46149</v>
@@ -4661,13 +4648,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="O54" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="O54" s="6" t="s">
-        <v>194</v>
-      </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="Q54" s="5">
         <v>46149</v>
@@ -4687,7 +4674,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B55" s="8">
         <v>46079.835301886575</v>
@@ -4697,7 +4684,7 @@
         <v>46080.57920532407</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4721,7 +4708,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4735,12 +4722,12 @@
         <v>58</v>
       </c>
       <c r="U55" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B56" s="5">
         <v>46079.835302164356</v>
@@ -4750,16 +4737,16 @@
         <v>46217.81965958333</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>205</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="I56" s="5">
         <v>46153</v>
@@ -4777,13 +4764,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q56" s="5">
         <v>46153</v>
@@ -4803,7 +4790,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B57" s="8">
         <v>46079.835302418986</v>
@@ -4813,16 +4800,16 @@
         <v>46191.1671537963</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I57" s="8">
         <v>46162</v>
@@ -4840,13 +4827,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q57" s="8">
         <v>46162</v>
@@ -4866,7 +4853,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B58" s="5">
         <v>46079.835302673615</v>
@@ -4876,16 +4863,16 @@
         <v>46193.205434930554</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I58" s="5">
         <v>46191</v>
@@ -4903,13 +4890,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q58" s="5">
         <v>46191</v>
@@ -4929,7 +4916,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B59" s="8">
         <v>46079.83530291667</v>
@@ -4939,7 +4926,7 @@
         <v>46216.76549305556</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -4963,7 +4950,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -4977,12 +4964,12 @@
         <v>58</v>
       </c>
       <c r="U59" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
         <v>46079.83530225694</v>
@@ -4992,16 +4979,16 @@
         <v>46214.176594108794</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I60" s="5">
         <v>46212</v>
@@ -5019,13 +5006,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Q60" s="5">
         <v>46212</v>
@@ -5045,7 +5032,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B61" s="8">
         <v>46079.835301851854</v>
@@ -5061,10 +5048,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I61" s="8">
         <v>46198</v>
@@ -5082,13 +5069,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q61" s="8">
         <v>46198</v>
@@ -5108,7 +5095,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B62" s="5">
         <v>46079.87589787037</v>
@@ -5120,16 +5107,16 @@
         <v>46216.765501898146</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I62" s="5">
         <v>46204</v>
@@ -5147,13 +5134,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Q62" s="5">
         <v>46204</v>
@@ -5173,7 +5160,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B63" s="8">
         <v>46079.83530319444</v>
@@ -5183,16 +5170,16 @@
         <v>46191.87499096065</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I63" s="8">
         <v>46149</v>
@@ -5210,13 +5197,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Q63" s="8">
         <v>46149</v>
@@ -5236,7 +5223,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B64" s="5">
         <v>46079.83530262731</v>
@@ -5248,16 +5235,16 @@
         <v>46216.765453831016</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I64" s="5">
         <v>46234</v>
@@ -5275,13 +5262,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Q64" s="5">
         <v>46234</v>
@@ -5296,12 +5283,12 @@
         <v>31</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B65" s="8">
         <v>46079.835302962965</v>
@@ -5311,7 +5298,7 @@
         <v>46158.99592380787</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5335,7 +5322,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5349,12 +5336,12 @@
         <v>58</v>
       </c>
       <c r="U65" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B66" s="5">
         <v>46079.83530328704</v>
@@ -5364,17 +5351,15 @@
         <v>46213.187978657406</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>93</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H66" s="6"/>
       <c r="I66" s="5">
         <v>46195</v>
       </c>
@@ -5391,13 +5376,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="O66" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="O66" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="Q66" s="5">
         <v>46195</v>
@@ -5417,7 +5402,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B67" s="8">
         <v>46079.83530362268</v>
@@ -5427,17 +5412,15 @@
         <v>46216.76544502315</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>93</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H67" s="9"/>
       <c r="I67" s="8">
         <v>46238</v>
       </c>
@@ -5454,13 +5437,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Q67" s="8">
         <v>46238</v>
@@ -5475,12 +5458,12 @@
         <v>58</v>
       </c>
       <c r="U67" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B68" s="5">
         <v>46079.83530398148</v>
@@ -5490,17 +5473,15 @@
         <v>46218.19199363426</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>93</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H68" s="6"/>
       <c r="I68" s="5">
         <v>46216</v>
       </c>
@@ -5517,13 +5498,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Q68" s="5">
         <v>46216</v>
@@ -5543,7 +5524,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B69" s="8">
         <v>46079.835304293985</v>
@@ -5553,17 +5534,15 @@
         <v>46212.201619583335</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>93</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H69" s="9"/>
       <c r="I69" s="8">
         <v>46218</v>
       </c>
@@ -5580,13 +5559,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Q69" s="8">
         <v>46218</v>
@@ -5601,12 +5580,12 @@
         <v>58</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B70" s="5">
         <v>46080.49271868056</v>
@@ -5616,17 +5595,15 @@
         <v>46216.765493900464</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>93</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H70" s="6"/>
       <c r="I70" s="5">
         <v>46220</v>
       </c>
@@ -5643,13 +5620,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5664,12 +5641,12 @@
         <v>58</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B71" s="8">
         <v>46079.83530460648</v>
@@ -5679,17 +5656,15 @@
         <v>46158.99592372685</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>93</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H71" s="9"/>
       <c r="I71" s="8">
         <v>46240</v>
       </c>
@@ -5706,13 +5681,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="Q71" s="8">
         <v>46240</v>
@@ -5727,12 +5702,12 @@
         <v>58</v>
       </c>
       <c r="U71" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B72" s="5">
         <v>46079.83530493056</v>
@@ -5742,17 +5717,15 @@
         <v>46090.804674259256</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>93</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H72" s="6"/>
       <c r="I72" s="5">
         <v>46244</v>
       </c>
@@ -5769,13 +5742,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q72" s="5">
         <v>46244</v>
@@ -5790,12 +5763,12 @@
         <v>58</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B73" s="8">
         <v>46079.83530144676</v>
@@ -5805,7 +5778,7 @@
         <v>46090.67671023148</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5829,7 +5802,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5842,7 +5815,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B74" s="5">
         <v>46079.83530181713</v>
@@ -5852,16 +5825,16 @@
         <v>46210.61678060185</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5877,13 +5850,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q74" s="5">
         <v>46245</v>
@@ -5898,12 +5871,12 @@
         <v>58</v>
       </c>
       <c r="U74" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B75" s="8">
         <v>46079.8353024074</v>
@@ -5919,11 +5892,9 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>93</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H75" s="9"/>
       <c r="I75" s="8">
         <v>46246</v>
       </c>
@@ -5940,13 +5911,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="Q75" s="8">
         <v>46246</v>
@@ -5961,12 +5932,12 @@
         <v>58</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B76" s="5">
         <v>46079.83530269676</v>
@@ -5976,16 +5947,16 @@
         <v>46090.80487153935</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I76" s="5">
         <v>46251</v>
@@ -6003,13 +5974,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>57</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q76" s="5">
         <v>46251</v>
@@ -6024,12 +5995,12 @@
         <v>58</v>
       </c>
       <c r="U76" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B77" s="8">
         <v>46079.83530306713</v>
@@ -6039,16 +6010,16 @@
         <v>46090.80495936342</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I77" s="8">
         <v>46252</v>
@@ -6066,13 +6037,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="Q77" s="8">
         <v>46252</v>
@@ -6087,12 +6058,12 @@
         <v>58</v>
       </c>
       <c r="U77" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B78" s="5">
         <v>46079.83530333333</v>
@@ -6102,7 +6073,7 @@
         <v>46090.67667782407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6126,7 +6097,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6139,7 +6110,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B79" s="8">
         <v>46079.83530363426</v>
@@ -6149,16 +6120,16 @@
         <v>46090.805033425924</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I79" s="8">
         <v>46253</v>
@@ -6176,13 +6147,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="O79" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="P79" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="Q79" s="8">
         <v>46252</v>
@@ -6197,12 +6168,12 @@
         <v>58</v>
       </c>
       <c r="U79" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B80" s="5">
         <v>46079.83530395833</v>
@@ -6212,16 +6183,16 @@
         <v>46114.51489402778</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6239,13 +6210,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q80" s="5">
         <v>46252</v>
@@ -6260,12 +6231,12 @@
         <v>58</v>
       </c>
       <c r="U80" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B81" s="8">
         <v>46090.6740474074</v>
@@ -6275,7 +6246,7 @@
         <v>46090.6782175</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>25</v>
@@ -6299,7 +6270,7 @@
         <v>26</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>26</v>
@@ -6313,12 +6284,12 @@
         <v>58</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B82" s="5">
         <v>46090.674231365745</v>
@@ -6328,7 +6299,7 @@
         <v>46090.80510871528</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6355,13 +6326,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="Q82" s="5">
         <v>46253</v>
@@ -6376,12 +6347,12 @@
         <v>58</v>
       </c>
       <c r="U82" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B83" s="8">
         <v>46090.67444209491</v>
@@ -6391,7 +6362,7 @@
         <v>46090.80510556713</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6418,13 +6389,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="O83" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="O83" s="9" t="s">
-        <v>290</v>
-      </c>
       <c r="P83" s="9" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="Q83" s="8">
         <v>46262</v>
@@ -6439,7 +6410,7 @@
         <v>58</v>
       </c>
       <c r="U83" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -761,16 +761,16 @@
     <t>Montaje Alabe,Revestimiento,Recepcion Rodete,Check plano</t>
   </si>
   <si>
+    <t>1213458788103121</t>
+  </si>
+  <si>
+    <t>Montaje sensor</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion Sensores,Check plano</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213458788103121</t>
-  </si>
-  <si>
-    <t>Montaje sensor</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion Sensores,Check plano</t>
   </si>
   <si>
     <t>1213459189207086</t>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46212.201619583335</v>
+        <v>46220.2056790625</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>244</v>
@@ -5579,13 +5579,13 @@
       <c r="T69" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="U69" s="12" t="s">
-        <v>246</v>
+      <c r="U69" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B70" s="5">
         <v>46080.49271868056</v>
@@ -5595,7 +5595,7 @@
         <v>46216.765493900464</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5623,7 +5623,7 @@
         <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>238</v>
@@ -5641,7 +5641,7 @@
         <v>58</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -2453,7 +2453,7 @@
         <v>46128.431861122684</v>
       </c>
       <c r="D19" s="8">
-        <v>46209.77994920139</v>
+        <v>46222.160672025464</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="292">
   <si>
     <t>50001518 - EQ. CHAPARRAL</t>
   </si>
@@ -300,6 +300,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete ot 4264</t>
@@ -2701,7 +2704,7 @@
         <v>46128.43184210648</v>
       </c>
       <c r="D23" s="8">
-        <v>46129.00161702547</v>
+        <v>46223.807620798616</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2710,9 +2713,11 @@
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="9"/>
+        <v>93</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="I23" s="8">
         <v>46093</v>
       </c>
@@ -2735,7 +2740,7 @@
         <v>66</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q23" s="8">
         <v>46093</v>
@@ -2755,7 +2760,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>46079.83530122685</v>
@@ -2764,18 +2769,20 @@
         <v>46209.77994163195</v>
       </c>
       <c r="D24" s="5">
-        <v>46209.779943333335</v>
+        <v>46223.80761667824</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="6"/>
+        <v>93</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="I24" s="5">
         <v>46093</v>
       </c>
@@ -2798,7 +2805,7 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q24" s="5">
         <v>46093</v>
@@ -2818,7 +2825,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25" s="8">
         <v>46079.87430951389</v>
@@ -2830,7 +2837,7 @@
         <v>46191.801115636576</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -2863,7 +2870,7 @@
         <v>69</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q25" s="8">
         <v>46093</v>
@@ -2883,7 +2890,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" s="5">
         <v>46080.51039956018</v>
@@ -2895,7 +2902,7 @@
         <v>46191.80112726852</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -2948,7 +2955,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B27" s="8">
         <v>46079.83530158565</v>
@@ -2960,7 +2967,7 @@
         <v>46209.709468483794</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>25</v>
@@ -2984,7 +2991,7 @@
         <v>26</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>26</v>
@@ -3001,7 +3008,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B28" s="5">
         <v>46079.83530186342</v>
@@ -3013,16 +3020,16 @@
         <v>46212.17176924768</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I28" s="5">
         <v>46097</v>
@@ -3040,13 +3047,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q28" s="5">
         <v>46097</v>
@@ -3066,7 +3073,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B29" s="8">
         <v>46079.83530212963</v>
@@ -3078,16 +3085,16 @@
         <v>46169.848412384265</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I29" s="8">
         <v>46097</v>
@@ -3105,13 +3112,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>83</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3122,12 +3129,12 @@
         <v>58</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46079.83530236111</v>
@@ -3139,16 +3146,16 @@
         <v>46191.87480704861</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I30" s="5">
         <v>46099</v>
@@ -3166,13 +3173,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3183,12 +3190,12 @@
         <v>58</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46079.83530269676</v>
@@ -3200,16 +3207,16 @@
         <v>46198.19648104167</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I31" s="8">
         <v>46091</v>
@@ -3227,13 +3234,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q31" s="8">
         <v>46091</v>
@@ -3253,7 +3260,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46079.83530295139</v>
@@ -3265,16 +3272,16 @@
         <v>46182.6792266088</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I32" s="5">
         <v>46091</v>
@@ -3292,13 +3299,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3309,12 +3316,12 @@
         <v>58</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B33" s="8">
         <v>46079.83530319444</v>
@@ -3326,16 +3333,16 @@
         <v>46191.874698125</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I33" s="8">
         <v>46100</v>
@@ -3353,13 +3360,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3370,12 +3377,12 @@
         <v>58</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B34" s="5">
         <v>46079.835301238425</v>
@@ -3387,16 +3394,16 @@
         <v>46191.874603414355</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I34" s="5">
         <v>46090</v>
@@ -3414,13 +3421,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q34" s="5">
         <v>46090</v>
@@ -3440,7 +3447,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B35" s="8">
         <v>46079.835301493054</v>
@@ -3452,16 +3459,16 @@
         <v>46169.84848269676</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I35" s="8">
         <v>46090</v>
@@ -3479,13 +3486,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3496,12 +3503,12 @@
         <v>58</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B36" s="5">
         <v>46079.83530179398</v>
@@ -3513,16 +3520,16 @@
         <v>46191.87457655092</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I36" s="5">
         <v>46108</v>
@@ -3540,13 +3547,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3557,12 +3564,12 @@
         <v>58</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B37" s="8">
         <v>46079.83530215277</v>
@@ -3574,16 +3581,16 @@
         <v>46169.84849621527</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I37" s="8">
         <v>46108</v>
@@ -3601,13 +3608,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3618,12 +3625,12 @@
         <v>58</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46079.83530342593</v>
@@ -3635,16 +3642,16 @@
         <v>46191.875013136574</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I38" s="5">
         <v>46097</v>
@@ -3662,13 +3669,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q38" s="5">
         <v>46097</v>
@@ -3688,7 +3695,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B39" s="8">
         <v>46079.83530366898</v>
@@ -3700,16 +3707,16 @@
         <v>46191.87447540509</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I39" s="8">
         <v>46097</v>
@@ -3727,13 +3734,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>92</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3744,12 +3751,12 @@
         <v>58</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B40" s="5">
         <v>46079.83530085648</v>
@@ -3761,16 +3768,16 @@
         <v>46191.87498288194</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I40" s="5">
         <v>46099</v>
@@ -3788,13 +3795,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3805,12 +3812,12 @@
         <v>58</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B41" s="8">
         <v>46079.835302418986</v>
@@ -3822,16 +3829,16 @@
         <v>46191.874875995374</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I41" s="8">
         <v>46097</v>
@@ -3849,13 +3856,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q41" s="8">
         <v>46097</v>
@@ -3875,7 +3882,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46079.83530269676</v>
@@ -3887,16 +3894,16 @@
         <v>46209.779950625</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I42" s="5">
         <v>46097</v>
@@ -3914,13 +3921,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3931,12 +3938,12 @@
         <v>58</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B43" s="8">
         <v>46079.835302962965</v>
@@ -3948,16 +3955,16 @@
         <v>46114.765690740736</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I43" s="8">
         <v>46115</v>
@@ -3975,13 +3982,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3992,12 +3999,12 @@
         <v>58</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46079.87449113426</v>
@@ -4009,16 +4016,16 @@
         <v>46204.18561212963</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I44" s="5">
         <v>46097</v>
@@ -4036,13 +4043,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q44" s="5">
         <v>46097</v>
@@ -4062,7 +4069,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B45" s="8">
         <v>46079.87456693287</v>
@@ -4074,16 +4081,16 @@
         <v>46191.80111972222</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I45" s="8">
         <v>46097</v>
@@ -4101,13 +4108,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4118,12 +4125,12 @@
         <v>58</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
         <v>46079.8746696875</v>
@@ -4135,16 +4142,16 @@
         <v>46114.766096481486</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I46" s="5">
         <v>46126</v>
@@ -4162,13 +4169,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4179,12 +4186,12 @@
         <v>58</v>
       </c>
       <c r="U46" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B47" s="8">
         <v>46079.835303252315</v>
@@ -4194,7 +4201,7 @@
         <v>46127.68782663194</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>25</v>
@@ -4218,7 +4225,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>26</v>
@@ -4233,7 +4240,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B48" s="5">
         <v>46079.8353035301</v>
@@ -4245,16 +4252,16 @@
         <v>46114.79548327546</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46093</v>
@@ -4272,13 +4279,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q48" s="5">
         <v>46093</v>
@@ -4298,7 +4305,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B49" s="8">
         <v>46079.83530068287</v>
@@ -4310,16 +4317,16 @@
         <v>46156.20046739583</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I49" s="8">
         <v>46149</v>
@@ -4337,13 +4344,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q49" s="8">
         <v>46149</v>
@@ -4363,7 +4370,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46087.628862847225</v>
@@ -4375,16 +4382,16 @@
         <v>46158.99592378472</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I50" s="5">
         <v>46156</v>
@@ -4402,13 +4409,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q50" s="5">
         <v>46156</v>
@@ -4428,7 +4435,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B51" s="8">
         <v>46087.62890292824</v>
@@ -4438,16 +4445,16 @@
         <v>46127.69021349537</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I51" s="8">
         <v>46243</v>
@@ -4465,13 +4472,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q51" s="8">
         <v>46243</v>
@@ -4486,12 +4493,12 @@
         <v>58</v>
       </c>
       <c r="U51" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B52" s="5">
         <v>46079.835301053245</v>
@@ -4503,7 +4510,7 @@
         <v>46217.8196680324</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4527,7 +4534,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4539,12 +4546,12 @@
         <v>81</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B53" s="8">
         <v>46079.835301342595</v>
@@ -4556,16 +4563,16 @@
         <v>46209.78806449074</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I53" s="8">
         <v>46147</v>
@@ -4583,13 +4590,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q53" s="8">
         <v>46147</v>
@@ -4609,7 +4616,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46079.83530162037</v>
@@ -4621,16 +4628,16 @@
         <v>46217.81965280093</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I54" s="5">
         <v>46149</v>
@@ -4648,13 +4655,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q54" s="5">
         <v>46149</v>
@@ -4674,7 +4681,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B55" s="8">
         <v>46079.835301886575</v>
@@ -4684,7 +4691,7 @@
         <v>46080.57920532407</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4708,7 +4715,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4722,12 +4729,12 @@
         <v>58</v>
       </c>
       <c r="U55" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B56" s="5">
         <v>46079.835302164356</v>
@@ -4737,16 +4744,16 @@
         <v>46217.81965958333</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I56" s="5">
         <v>46153</v>
@@ -4764,13 +4771,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q56" s="5">
         <v>46153</v>
@@ -4790,7 +4797,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B57" s="8">
         <v>46079.835302418986</v>
@@ -4800,16 +4807,16 @@
         <v>46191.1671537963</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I57" s="8">
         <v>46162</v>
@@ -4827,13 +4834,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q57" s="8">
         <v>46162</v>
@@ -4853,7 +4860,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B58" s="5">
         <v>46079.835302673615</v>
@@ -4863,16 +4870,16 @@
         <v>46193.205434930554</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I58" s="5">
         <v>46191</v>
@@ -4890,13 +4897,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q58" s="5">
         <v>46191</v>
@@ -4916,7 +4923,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B59" s="8">
         <v>46079.83530291667</v>
@@ -4926,7 +4933,7 @@
         <v>46216.76549305556</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -4950,7 +4957,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -4964,12 +4971,12 @@
         <v>58</v>
       </c>
       <c r="U59" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B60" s="5">
         <v>46079.83530225694</v>
@@ -4979,16 +4986,16 @@
         <v>46214.176594108794</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I60" s="5">
         <v>46212</v>
@@ -5006,13 +5013,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q60" s="5">
         <v>46212</v>
@@ -5032,7 +5039,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B61" s="8">
         <v>46079.835301851854</v>
@@ -5048,10 +5055,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I61" s="8">
         <v>46198</v>
@@ -5069,13 +5076,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q61" s="8">
         <v>46198</v>
@@ -5095,7 +5102,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B62" s="5">
         <v>46079.87589787037</v>
@@ -5107,16 +5114,16 @@
         <v>46216.765501898146</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I62" s="5">
         <v>46204</v>
@@ -5134,13 +5141,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q62" s="5">
         <v>46204</v>
@@ -5160,7 +5167,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B63" s="8">
         <v>46079.83530319444</v>
@@ -5170,16 +5177,16 @@
         <v>46191.87499096065</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I63" s="8">
         <v>46149</v>
@@ -5197,13 +5204,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q63" s="8">
         <v>46149</v>
@@ -5223,7 +5230,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B64" s="5">
         <v>46079.83530262731</v>
@@ -5235,16 +5242,16 @@
         <v>46216.765453831016</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I64" s="5">
         <v>46234</v>
@@ -5262,13 +5269,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q64" s="5">
         <v>46234</v>
@@ -5283,12 +5290,12 @@
         <v>31</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B65" s="8">
         <v>46079.835302962965</v>
@@ -5298,7 +5305,7 @@
         <v>46158.99592380787</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5322,7 +5329,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5336,30 +5343,32 @@
         <v>58</v>
       </c>
       <c r="U65" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B66" s="5">
         <v>46079.83530328704</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46213.187978657406</v>
+        <v>46223.807732870366</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H66" s="6"/>
+        <v>93</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="I66" s="5">
         <v>46195</v>
       </c>
@@ -5376,13 +5385,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q66" s="5">
         <v>46195</v>
@@ -5402,25 +5411,27 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B67" s="8">
         <v>46079.83530362268</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46216.76544502315</v>
+        <v>46223.80773233796</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H67" s="9"/>
+        <v>93</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="I67" s="8">
         <v>46238</v>
       </c>
@@ -5437,13 +5448,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q67" s="8">
         <v>46238</v>
@@ -5458,30 +5469,32 @@
         <v>58</v>
       </c>
       <c r="U67" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B68" s="5">
         <v>46079.83530398148</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46218.19199363426</v>
+        <v>46223.80773180556</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H68" s="6"/>
+        <v>93</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="I68" s="5">
         <v>46216</v>
       </c>
@@ -5498,13 +5511,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q68" s="5">
         <v>46216</v>
@@ -5524,25 +5537,27 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B69" s="8">
         <v>46079.835304293985</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46220.2056790625</v>
+        <v>46223.807731249995</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H69" s="9"/>
+        <v>93</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="I69" s="8">
         <v>46218</v>
       </c>
@@ -5559,13 +5574,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q69" s="8">
         <v>46218</v>
@@ -5585,25 +5600,27 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B70" s="5">
         <v>46080.49271868056</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46216.765493900464</v>
+        <v>46223.80773064814</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H70" s="6"/>
+        <v>93</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="I70" s="5">
         <v>46220</v>
       </c>
@@ -5620,13 +5637,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5641,30 +5658,32 @@
         <v>58</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B71" s="8">
         <v>46079.83530460648</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46158.99592372685</v>
+        <v>46223.8077300463</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H71" s="9"/>
+        <v>93</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="I71" s="8">
         <v>46240</v>
       </c>
@@ -5681,13 +5700,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q71" s="8">
         <v>46240</v>
@@ -5702,30 +5721,32 @@
         <v>58</v>
       </c>
       <c r="U71" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B72" s="5">
         <v>46079.83530493056</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46090.804674259256</v>
+        <v>46223.807729548615</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H72" s="6"/>
+        <v>93</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="I72" s="5">
         <v>46244</v>
       </c>
@@ -5742,13 +5763,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q72" s="5">
         <v>46244</v>
@@ -5763,12 +5784,12 @@
         <v>58</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B73" s="8">
         <v>46079.83530144676</v>
@@ -5778,7 +5799,7 @@
         <v>46090.67671023148</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5802,7 +5823,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5815,7 +5836,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B74" s="5">
         <v>46079.83530181713</v>
@@ -5825,16 +5846,16 @@
         <v>46210.61678060185</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5850,13 +5871,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q74" s="5">
         <v>46245</v>
@@ -5871,19 +5892,19 @@
         <v>58</v>
       </c>
       <c r="U74" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B75" s="8">
         <v>46079.8353024074</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46097.64290024305</v>
+        <v>46223.807789224535</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>57</v>
@@ -5892,9 +5913,11 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H75" s="9"/>
+        <v>93</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="I75" s="8">
         <v>46246</v>
       </c>
@@ -5911,13 +5934,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q75" s="8">
         <v>46246</v>
@@ -5932,12 +5955,12 @@
         <v>58</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B76" s="5">
         <v>46079.83530269676</v>
@@ -5947,16 +5970,16 @@
         <v>46090.80487153935</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I76" s="5">
         <v>46251</v>
@@ -5974,13 +5997,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>57</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q76" s="5">
         <v>46251</v>
@@ -5995,12 +6018,12 @@
         <v>58</v>
       </c>
       <c r="U76" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B77" s="8">
         <v>46079.83530306713</v>
@@ -6010,16 +6033,16 @@
         <v>46090.80495936342</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I77" s="8">
         <v>46252</v>
@@ -6037,13 +6060,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q77" s="8">
         <v>46252</v>
@@ -6058,12 +6081,12 @@
         <v>58</v>
       </c>
       <c r="U77" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B78" s="5">
         <v>46079.83530333333</v>
@@ -6073,7 +6096,7 @@
         <v>46090.67667782407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6097,7 +6120,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6110,7 +6133,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B79" s="8">
         <v>46079.83530363426</v>
@@ -6120,16 +6143,16 @@
         <v>46090.805033425924</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I79" s="8">
         <v>46253</v>
@@ -6147,13 +6170,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q79" s="8">
         <v>46252</v>
@@ -6168,12 +6191,12 @@
         <v>58</v>
       </c>
       <c r="U79" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B80" s="5">
         <v>46079.83530395833</v>
@@ -6183,16 +6206,16 @@
         <v>46114.51489402778</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6210,13 +6233,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q80" s="5">
         <v>46252</v>
@@ -6231,12 +6254,12 @@
         <v>58</v>
       </c>
       <c r="U80" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B81" s="8">
         <v>46090.6740474074</v>
@@ -6246,7 +6269,7 @@
         <v>46090.6782175</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>25</v>
@@ -6270,7 +6293,7 @@
         <v>26</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>26</v>
@@ -6284,12 +6307,12 @@
         <v>58</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B82" s="5">
         <v>46090.674231365745</v>
@@ -6299,7 +6322,7 @@
         <v>46090.80510871528</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6326,13 +6349,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q82" s="5">
         <v>46253</v>
@@ -6347,12 +6370,12 @@
         <v>58</v>
       </c>
       <c r="U82" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B83" s="8">
         <v>46090.67444209491</v>
@@ -6362,7 +6385,7 @@
         <v>46090.80510556713</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6389,13 +6412,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q83" s="8">
         <v>46262</v>
@@ -6410,7 +6433,7 @@
         <v>58</v>
       </c>
       <c r="U83" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="291">
   <si>
     <t>50001518 - EQ. CHAPARRAL</t>
   </si>
@@ -771,9 +771,6 @@
   </si>
   <si>
     <t>Revestimiento,Recepcion Sensores,Check plano</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213459189207086</t>
@@ -5607,7 +5604,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46223.80773064814</v>
+        <v>46224.20075512731</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>248</v>
@@ -5657,13 +5654,13 @@
       <c r="T70" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="U70" s="12" t="s">
-        <v>250</v>
+      <c r="U70" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B71" s="8">
         <v>46079.83530460648</v>
@@ -5703,10 +5700,10 @@
         <v>232</v>
       </c>
       <c r="O71" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="P71" s="9" t="s">
         <v>252</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>253</v>
       </c>
       <c r="Q71" s="8">
         <v>46240</v>
@@ -5726,7 +5723,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B72" s="5">
         <v>46079.83530493056</v>
@@ -5736,7 +5733,7 @@
         <v>46223.807729548615</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5769,7 +5766,7 @@
         <v>185</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q72" s="5">
         <v>46244</v>
@@ -5789,7 +5786,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B73" s="8">
         <v>46079.83530144676</v>
@@ -5799,7 +5796,7 @@
         <v>46090.67671023148</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5823,7 +5820,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5836,7 +5833,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B74" s="5">
         <v>46079.83530181713</v>
@@ -5846,16 +5843,16 @@
         <v>46210.61678060185</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="6" t="s">
+      <c r="H74" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5871,13 +5868,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q74" s="5">
         <v>46245</v>
@@ -5897,7 +5894,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B75" s="8">
         <v>46079.8353024074</v>
@@ -5934,13 +5931,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O75" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="P75" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="P75" s="9" t="s">
-        <v>267</v>
       </c>
       <c r="Q75" s="8">
         <v>46246</v>
@@ -5960,7 +5957,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B76" s="5">
         <v>46079.83530269676</v>
@@ -5970,7 +5967,7 @@
         <v>46090.80487153935</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5997,13 +5994,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>57</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q76" s="5">
         <v>46251</v>
@@ -6023,7 +6020,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B77" s="8">
         <v>46079.83530306713</v>
@@ -6033,7 +6030,7 @@
         <v>46090.80495936342</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6060,13 +6057,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q77" s="8">
         <v>46252</v>
@@ -6086,7 +6083,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B78" s="5">
         <v>46079.83530333333</v>
@@ -6096,7 +6093,7 @@
         <v>46090.67667782407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6120,7 +6117,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6133,7 +6130,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B79" s="8">
         <v>46079.83530363426</v>
@@ -6143,16 +6140,16 @@
         <v>46090.805033425924</v>
       </c>
       <c r="E79" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="F79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G79" s="9" t="s">
+      <c r="H79" s="9" t="s">
         <v>279</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>280</v>
       </c>
       <c r="I79" s="8">
         <v>46253</v>
@@ -6170,13 +6167,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q79" s="8">
         <v>46252</v>
@@ -6196,7 +6193,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B80" s="5">
         <v>46079.83530395833</v>
@@ -6206,16 +6203,16 @@
         <v>46114.51489402778</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>279</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>280</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6233,13 +6230,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q80" s="5">
         <v>46252</v>
@@ -6259,7 +6256,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B81" s="8">
         <v>46090.6740474074</v>
@@ -6269,7 +6266,7 @@
         <v>46090.6782175</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>25</v>
@@ -6293,7 +6290,7 @@
         <v>26</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>26</v>
@@ -6312,7 +6309,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B82" s="5">
         <v>46090.674231365745</v>
@@ -6322,7 +6319,7 @@
         <v>46090.80510871528</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6349,13 +6346,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q82" s="5">
         <v>46253</v>
@@ -6375,7 +6372,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B83" s="8">
         <v>46090.67444209491</v>
@@ -6385,7 +6382,7 @@
         <v>46090.80510556713</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6412,13 +6409,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q83" s="8">
         <v>46262</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="292">
   <si>
     <t>50001518 - EQ. CHAPARRAL</t>
   </si>
@@ -300,6 +300,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2713,7 +2716,7 @@
         <v>93</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I23" s="8">
         <v>46093</v>
@@ -2737,7 +2740,7 @@
         <v>66</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q23" s="8">
         <v>46093</v>
@@ -2757,7 +2760,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46079.83530122685</v>
@@ -2769,7 +2772,7 @@
         <v>46223.80761667824</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2778,7 +2781,7 @@
         <v>93</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I24" s="5">
         <v>46093</v>
@@ -2802,7 +2805,7 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="5">
         <v>46093</v>
@@ -2822,7 +2825,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B25" s="8">
         <v>46079.87430951389</v>
@@ -2834,7 +2837,7 @@
         <v>46191.801115636576</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -2867,7 +2870,7 @@
         <v>69</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q25" s="8">
         <v>46093</v>
@@ -2887,7 +2890,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B26" s="5">
         <v>46080.51039956018</v>
@@ -2899,7 +2902,7 @@
         <v>46191.80112726852</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -2952,7 +2955,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B27" s="8">
         <v>46079.83530158565</v>
@@ -2964,7 +2967,7 @@
         <v>46209.709468483794</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>25</v>
@@ -2988,7 +2991,7 @@
         <v>26</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>26</v>
@@ -3005,7 +3008,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B28" s="5">
         <v>46079.83530186342</v>
@@ -3017,16 +3020,16 @@
         <v>46212.17176924768</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I28" s="5">
         <v>46097</v>
@@ -3044,13 +3047,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q28" s="5">
         <v>46097</v>
@@ -3070,7 +3073,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B29" s="8">
         <v>46079.83530212963</v>
@@ -3082,16 +3085,16 @@
         <v>46169.848412384265</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I29" s="8">
         <v>46097</v>
@@ -3109,13 +3112,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>83</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3126,12 +3129,12 @@
         <v>58</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46079.83530236111</v>
@@ -3143,16 +3146,16 @@
         <v>46191.87480704861</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I30" s="5">
         <v>46099</v>
@@ -3170,13 +3173,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3187,12 +3190,12 @@
         <v>58</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="8">
         <v>46079.83530269676</v>
@@ -3204,16 +3207,16 @@
         <v>46198.19648104167</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I31" s="8">
         <v>46091</v>
@@ -3231,13 +3234,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q31" s="8">
         <v>46091</v>
@@ -3257,7 +3260,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46079.83530295139</v>
@@ -3269,16 +3272,16 @@
         <v>46182.6792266088</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I32" s="5">
         <v>46091</v>
@@ -3296,13 +3299,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3313,12 +3316,12 @@
         <v>58</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>46079.83530319444</v>
@@ -3330,16 +3333,16 @@
         <v>46191.874698125</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I33" s="8">
         <v>46100</v>
@@ -3357,13 +3360,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3374,12 +3377,12 @@
         <v>58</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46079.835301238425</v>
@@ -3391,16 +3394,16 @@
         <v>46191.874603414355</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I34" s="5">
         <v>46090</v>
@@ -3418,13 +3421,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q34" s="5">
         <v>46090</v>
@@ -3444,7 +3447,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46079.835301493054</v>
@@ -3456,16 +3459,16 @@
         <v>46169.84848269676</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I35" s="8">
         <v>46090</v>
@@ -3483,13 +3486,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3500,12 +3503,12 @@
         <v>58</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46079.83530179398</v>
@@ -3517,16 +3520,16 @@
         <v>46191.87457655092</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I36" s="5">
         <v>46108</v>
@@ -3544,13 +3547,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3561,12 +3564,12 @@
         <v>58</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B37" s="8">
         <v>46079.83530215277</v>
@@ -3578,16 +3581,16 @@
         <v>46169.84849621527</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I37" s="8">
         <v>46108</v>
@@ -3605,13 +3608,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3622,12 +3625,12 @@
         <v>58</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46079.83530342593</v>
@@ -3639,16 +3642,16 @@
         <v>46191.875013136574</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I38" s="5">
         <v>46097</v>
@@ -3666,13 +3669,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q38" s="5">
         <v>46097</v>
@@ -3692,7 +3695,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46079.83530366898</v>
@@ -3704,16 +3707,16 @@
         <v>46191.87447540509</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I39" s="8">
         <v>46097</v>
@@ -3731,13 +3734,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>92</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3748,12 +3751,12 @@
         <v>58</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46079.83530085648</v>
@@ -3765,16 +3768,16 @@
         <v>46191.87498288194</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I40" s="5">
         <v>46099</v>
@@ -3792,13 +3795,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3809,12 +3812,12 @@
         <v>58</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B41" s="8">
         <v>46079.835302418986</v>
@@ -3826,16 +3829,16 @@
         <v>46191.874875995374</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I41" s="8">
         <v>46097</v>
@@ -3853,13 +3856,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q41" s="8">
         <v>46097</v>
@@ -3879,7 +3882,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46079.83530269676</v>
@@ -3891,16 +3894,16 @@
         <v>46209.779950625</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I42" s="5">
         <v>46097</v>
@@ -3918,13 +3921,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3935,12 +3938,12 @@
         <v>58</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" s="8">
         <v>46079.835302962965</v>
@@ -3952,16 +3955,16 @@
         <v>46114.765690740736</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I43" s="8">
         <v>46115</v>
@@ -3979,13 +3982,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3996,12 +3999,12 @@
         <v>58</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46079.87449113426</v>
@@ -4013,16 +4016,16 @@
         <v>46204.18561212963</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I44" s="5">
         <v>46097</v>
@@ -4040,13 +4043,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q44" s="5">
         <v>46097</v>
@@ -4066,7 +4069,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B45" s="8">
         <v>46079.87456693287</v>
@@ -4078,16 +4081,16 @@
         <v>46191.80111972222</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I45" s="8">
         <v>46097</v>
@@ -4105,13 +4108,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4122,12 +4125,12 @@
         <v>58</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46079.8746696875</v>
@@ -4139,16 +4142,16 @@
         <v>46114.766096481486</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I46" s="5">
         <v>46126</v>
@@ -4166,13 +4169,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4183,12 +4186,12 @@
         <v>58</v>
       </c>
       <c r="U46" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46079.835303252315</v>
@@ -4198,7 +4201,7 @@
         <v>46127.68782663194</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>25</v>
@@ -4222,7 +4225,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>26</v>
@@ -4237,7 +4240,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B48" s="5">
         <v>46079.8353035301</v>
@@ -4249,16 +4252,16 @@
         <v>46114.79548327546</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46093</v>
@@ -4276,13 +4279,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q48" s="5">
         <v>46093</v>
@@ -4302,7 +4305,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B49" s="8">
         <v>46079.83530068287</v>
@@ -4314,16 +4317,16 @@
         <v>46156.20046739583</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I49" s="8">
         <v>46149</v>
@@ -4341,13 +4344,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="8">
         <v>46149</v>
@@ -4367,7 +4370,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46087.628862847225</v>
@@ -4379,16 +4382,16 @@
         <v>46158.99592378472</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I50" s="5">
         <v>46156</v>
@@ -4406,13 +4409,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q50" s="5">
         <v>46156</v>
@@ -4432,7 +4435,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46087.62890292824</v>
@@ -4442,16 +4445,16 @@
         <v>46127.69021349537</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I51" s="8">
         <v>46243</v>
@@ -4469,13 +4472,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q51" s="8">
         <v>46243</v>
@@ -4490,12 +4493,12 @@
         <v>58</v>
       </c>
       <c r="U51" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46079.835301053245</v>
@@ -4507,7 +4510,7 @@
         <v>46217.8196680324</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4531,7 +4534,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4543,12 +4546,12 @@
         <v>81</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B53" s="8">
         <v>46079.835301342595</v>
@@ -4560,16 +4563,16 @@
         <v>46209.78806449074</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I53" s="8">
         <v>46147</v>
@@ -4587,13 +4590,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q53" s="8">
         <v>46147</v>
@@ -4613,7 +4616,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46079.83530162037</v>
@@ -4625,16 +4628,16 @@
         <v>46217.81965280093</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I54" s="5">
         <v>46149</v>
@@ -4652,13 +4655,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46149</v>
@@ -4678,7 +4681,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B55" s="8">
         <v>46079.835301886575</v>
@@ -4688,7 +4691,7 @@
         <v>46080.57920532407</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4712,7 +4715,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4726,12 +4729,12 @@
         <v>58</v>
       </c>
       <c r="U55" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5">
         <v>46079.835302164356</v>
@@ -4741,16 +4744,16 @@
         <v>46217.81965958333</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I56" s="5">
         <v>46153</v>
@@ -4768,13 +4771,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q56" s="5">
         <v>46153</v>
@@ -4794,7 +4797,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B57" s="8">
         <v>46079.835302418986</v>
@@ -4804,16 +4807,16 @@
         <v>46191.1671537963</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I57" s="8">
         <v>46162</v>
@@ -4831,13 +4834,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="8">
         <v>46162</v>
@@ -4857,7 +4860,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46079.835302673615</v>
@@ -4867,16 +4870,16 @@
         <v>46193.205434930554</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I58" s="5">
         <v>46191</v>
@@ -4894,13 +4897,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q58" s="5">
         <v>46191</v>
@@ -4920,7 +4923,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B59" s="8">
         <v>46079.83530291667</v>
@@ -4930,7 +4933,7 @@
         <v>46216.76549305556</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -4954,7 +4957,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -4968,12 +4971,12 @@
         <v>58</v>
       </c>
       <c r="U59" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B60" s="5">
         <v>46079.83530225694</v>
@@ -4983,16 +4986,16 @@
         <v>46214.176594108794</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I60" s="5">
         <v>46212</v>
@@ -5010,13 +5013,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q60" s="5">
         <v>46212</v>
@@ -5036,7 +5039,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B61" s="8">
         <v>46079.835301851854</v>
@@ -5052,10 +5055,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I61" s="8">
         <v>46198</v>
@@ -5073,13 +5076,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q61" s="8">
         <v>46198</v>
@@ -5099,7 +5102,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B62" s="5">
         <v>46079.87589787037</v>
@@ -5111,16 +5114,16 @@
         <v>46216.765501898146</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I62" s="5">
         <v>46204</v>
@@ -5138,13 +5141,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q62" s="5">
         <v>46204</v>
@@ -5164,7 +5167,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B63" s="8">
         <v>46079.83530319444</v>
@@ -5174,16 +5177,16 @@
         <v>46191.87499096065</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I63" s="8">
         <v>46149</v>
@@ -5201,13 +5204,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q63" s="8">
         <v>46149</v>
@@ -5227,7 +5230,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46079.83530262731</v>
@@ -5239,16 +5242,16 @@
         <v>46216.765453831016</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I64" s="5">
         <v>46234</v>
@@ -5266,13 +5269,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q64" s="5">
         <v>46234</v>
@@ -5287,12 +5290,12 @@
         <v>31</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B65" s="8">
         <v>46079.835302962965</v>
@@ -5302,7 +5305,7 @@
         <v>46158.99592380787</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5326,7 +5329,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5340,12 +5343,12 @@
         <v>58</v>
       </c>
       <c r="U65" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B66" s="5">
         <v>46079.83530328704</v>
@@ -5355,7 +5358,7 @@
         <v>46223.807732870366</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5364,7 +5367,7 @@
         <v>93</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I66" s="5">
         <v>46195</v>
@@ -5382,13 +5385,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q66" s="5">
         <v>46195</v>
@@ -5408,7 +5411,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B67" s="8">
         <v>46079.83530362268</v>
@@ -5418,7 +5421,7 @@
         <v>46223.80773233796</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5427,7 +5430,7 @@
         <v>93</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I67" s="8">
         <v>46238</v>
@@ -5445,13 +5448,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q67" s="8">
         <v>46238</v>
@@ -5466,12 +5469,12 @@
         <v>58</v>
       </c>
       <c r="U67" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B68" s="5">
         <v>46079.83530398148</v>
@@ -5481,7 +5484,7 @@
         <v>46223.80773180556</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5490,7 +5493,7 @@
         <v>93</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I68" s="5">
         <v>46216</v>
@@ -5508,13 +5511,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q68" s="5">
         <v>46216</v>
@@ -5534,7 +5537,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B69" s="8">
         <v>46079.835304293985</v>
@@ -5544,7 +5547,7 @@
         <v>46223.807731249995</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5553,7 +5556,7 @@
         <v>93</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I69" s="8">
         <v>46218</v>
@@ -5571,13 +5574,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q69" s="8">
         <v>46218</v>
@@ -5597,7 +5600,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B70" s="5">
         <v>46080.49271868056</v>
@@ -5607,7 +5610,7 @@
         <v>46224.20075512731</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5616,7 +5619,7 @@
         <v>93</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5634,13 +5637,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5660,7 +5663,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B71" s="8">
         <v>46079.83530460648</v>
@@ -5670,7 +5673,7 @@
         <v>46223.8077300463</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5679,7 +5682,7 @@
         <v>93</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I71" s="8">
         <v>46240</v>
@@ -5697,13 +5700,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q71" s="8">
         <v>46240</v>
@@ -5718,12 +5721,12 @@
         <v>58</v>
       </c>
       <c r="U71" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B72" s="5">
         <v>46079.83530493056</v>
@@ -5733,7 +5736,7 @@
         <v>46223.807729548615</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5742,7 +5745,7 @@
         <v>93</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I72" s="5">
         <v>46244</v>
@@ -5760,13 +5763,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q72" s="5">
         <v>46244</v>
@@ -5781,12 +5784,12 @@
         <v>58</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B73" s="8">
         <v>46079.83530144676</v>
@@ -5796,7 +5799,7 @@
         <v>46090.67671023148</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5820,7 +5823,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5833,7 +5836,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B74" s="5">
         <v>46079.83530181713</v>
@@ -5843,16 +5846,16 @@
         <v>46210.61678060185</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5868,13 +5871,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q74" s="5">
         <v>46245</v>
@@ -5889,12 +5892,12 @@
         <v>58</v>
       </c>
       <c r="U74" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B75" s="8">
         <v>46079.8353024074</v>
@@ -5913,7 +5916,7 @@
         <v>93</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I75" s="8">
         <v>46246</v>
@@ -5931,13 +5934,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q75" s="8">
         <v>46246</v>
@@ -5952,12 +5955,12 @@
         <v>58</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B76" s="5">
         <v>46079.83530269676</v>
@@ -5967,16 +5970,16 @@
         <v>46090.80487153935</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I76" s="5">
         <v>46251</v>
@@ -5994,13 +5997,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>57</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q76" s="5">
         <v>46251</v>
@@ -6015,12 +6018,12 @@
         <v>58</v>
       </c>
       <c r="U76" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B77" s="8">
         <v>46079.83530306713</v>
@@ -6030,16 +6033,16 @@
         <v>46090.80495936342</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I77" s="8">
         <v>46252</v>
@@ -6057,13 +6060,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q77" s="8">
         <v>46252</v>
@@ -6078,12 +6081,12 @@
         <v>58</v>
       </c>
       <c r="U77" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B78" s="5">
         <v>46079.83530333333</v>
@@ -6093,7 +6096,7 @@
         <v>46090.67667782407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6117,7 +6120,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6130,7 +6133,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B79" s="8">
         <v>46079.83530363426</v>
@@ -6140,16 +6143,16 @@
         <v>46090.805033425924</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I79" s="8">
         <v>46253</v>
@@ -6167,13 +6170,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q79" s="8">
         <v>46252</v>
@@ -6188,12 +6191,12 @@
         <v>58</v>
       </c>
       <c r="U79" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B80" s="5">
         <v>46079.83530395833</v>
@@ -6203,16 +6206,16 @@
         <v>46114.51489402778</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6230,13 +6233,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q80" s="5">
         <v>46252</v>
@@ -6251,12 +6254,12 @@
         <v>58</v>
       </c>
       <c r="U80" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B81" s="8">
         <v>46090.6740474074</v>
@@ -6266,7 +6269,7 @@
         <v>46090.6782175</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>25</v>
@@ -6290,7 +6293,7 @@
         <v>26</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>26</v>
@@ -6304,12 +6307,12 @@
         <v>58</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B82" s="5">
         <v>46090.674231365745</v>
@@ -6319,7 +6322,7 @@
         <v>46090.80510871528</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6346,13 +6349,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q82" s="5">
         <v>46253</v>
@@ -6367,12 +6370,12 @@
         <v>58</v>
       </c>
       <c r="U82" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B83" s="8">
         <v>46090.67444209491</v>
@@ -6382,7 +6385,7 @@
         <v>46090.80510556713</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6409,13 +6412,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q83" s="8">
         <v>46262</v>
@@ -6430,7 +6433,7 @@
         <v>58</v>
       </c>
       <c r="U83" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="293">
   <si>
     <t>50001518 - EQ. CHAPARRAL</t>
   </si>
@@ -717,6 +717,9 @@
   </si>
   <si>
     <t>Bodega:,Montaje motor</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1213459189207081</t>
@@ -1529,7 +1532,7 @@
         <v>46092.71525421296</v>
       </c>
       <c r="D4" s="5">
-        <v>46128.59644841435</v>
+        <v>46228.85387450231</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -5239,7 +5242,7 @@
         <v>46216.7654346412</v>
       </c>
       <c r="D64" s="5">
-        <v>46216.765453831016</v>
+        <v>46230.175846087965</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5289,13 +5292,13 @@
       <c r="T64" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U64" s="10" t="s">
-        <v>115</v>
+      <c r="U64" s="12" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B65" s="8">
         <v>46079.835302962965</v>
@@ -5305,7 +5308,7 @@
         <v>46158.99592380787</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5329,7 +5332,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5348,7 +5351,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B66" s="5">
         <v>46079.83530328704</v>
@@ -5385,13 +5388,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>212</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q66" s="5">
         <v>46195</v>
@@ -5411,7 +5414,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B67" s="8">
         <v>46079.83530362268</v>
@@ -5421,7 +5424,7 @@
         <v>46223.80773233796</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5448,13 +5451,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q67" s="8">
         <v>46238</v>
@@ -5474,7 +5477,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46079.83530398148</v>
@@ -5484,7 +5487,7 @@
         <v>46223.80773180556</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5511,13 +5514,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q68" s="5">
         <v>46216</v>
@@ -5537,7 +5540,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B69" s="8">
         <v>46079.835304293985</v>
@@ -5547,7 +5550,7 @@
         <v>46223.807731249995</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5574,13 +5577,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q69" s="8">
         <v>46218</v>
@@ -5600,7 +5603,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B70" s="5">
         <v>46080.49271868056</v>
@@ -5610,7 +5613,7 @@
         <v>46224.20075512731</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5637,13 +5640,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5663,7 +5666,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B71" s="8">
         <v>46079.83530460648</v>
@@ -5700,13 +5703,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q71" s="8">
         <v>46240</v>
@@ -5726,7 +5729,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B72" s="5">
         <v>46079.83530493056</v>
@@ -5736,7 +5739,7 @@
         <v>46223.807729548615</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5763,13 +5766,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>186</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q72" s="5">
         <v>46244</v>
@@ -5789,7 +5792,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B73" s="8">
         <v>46079.83530144676</v>
@@ -5799,7 +5802,7 @@
         <v>46090.67671023148</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5823,7 +5826,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5836,7 +5839,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B74" s="5">
         <v>46079.83530181713</v>
@@ -5846,16 +5849,16 @@
         <v>46210.61678060185</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5871,13 +5874,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q74" s="5">
         <v>46245</v>
@@ -5897,7 +5900,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B75" s="8">
         <v>46079.8353024074</v>
@@ -5934,13 +5937,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q75" s="8">
         <v>46246</v>
@@ -5960,7 +5963,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B76" s="5">
         <v>46079.83530269676</v>
@@ -5970,7 +5973,7 @@
         <v>46090.80487153935</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5997,13 +6000,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>57</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q76" s="5">
         <v>46251</v>
@@ -6023,7 +6026,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B77" s="8">
         <v>46079.83530306713</v>
@@ -6033,7 +6036,7 @@
         <v>46090.80495936342</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6060,13 +6063,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q77" s="8">
         <v>46252</v>
@@ -6086,7 +6089,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B78" s="5">
         <v>46079.83530333333</v>
@@ -6096,7 +6099,7 @@
         <v>46090.67667782407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6120,7 +6123,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6133,7 +6136,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B79" s="8">
         <v>46079.83530363426</v>
@@ -6143,16 +6146,16 @@
         <v>46090.805033425924</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I79" s="8">
         <v>46253</v>
@@ -6170,13 +6173,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q79" s="8">
         <v>46252</v>
@@ -6196,7 +6199,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B80" s="5">
         <v>46079.83530395833</v>
@@ -6206,16 +6209,16 @@
         <v>46114.51489402778</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6233,13 +6236,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q80" s="5">
         <v>46252</v>
@@ -6259,7 +6262,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B81" s="8">
         <v>46090.6740474074</v>
@@ -6269,7 +6272,7 @@
         <v>46090.6782175</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>25</v>
@@ -6293,7 +6296,7 @@
         <v>26</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>26</v>
@@ -6312,7 +6315,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B82" s="5">
         <v>46090.674231365745</v>
@@ -6322,7 +6325,7 @@
         <v>46090.80510871528</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6349,13 +6352,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q82" s="5">
         <v>46253</v>
@@ -6375,7 +6378,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B83" s="8">
         <v>46090.67444209491</v>
@@ -6385,7 +6388,7 @@
         <v>46090.80510556713</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6412,13 +6415,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q83" s="8">
         <v>46262</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -5421,7 +5421,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46223.80773233796</v>
+        <v>46232.17142269676</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>239</v>
@@ -5471,8 +5471,8 @@
       <c r="T67" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="U67" s="10" t="s">
-        <v>115</v>
+      <c r="U67" s="12" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="295">
   <si>
     <t>50001518 - EQ. CHAPARRAL</t>
   </si>
@@ -191,181 +191,187 @@
     <t>Revisión tableros pruebas</t>
   </si>
   <si>
+    <t>sergio saavedra fernandez</t>
+  </si>
+  <si>
+    <t>sergio.saavedra@zitron.com</t>
+  </si>
+  <si>
     <t>Recepcion Tableros</t>
   </si>
   <si>
     <t>Embalaje</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1213459189153314</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Damper,Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete,Analisis de costeo</t>
+  </si>
+  <si>
+    <t>1213459189153315</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
+  </si>
+  <si>
+    <t>1213459189153317</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
+  </si>
+  <si>
+    <t>1213459189153318</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta compras a codigo // aprovisionamiento,Propuesta Sensores,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1213458011369803</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Damper</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Propuesta Damper,Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>1213459189153319</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Damper,Ingenieria Basica Motor,Ingenieria Detalle,Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Costos</t>
+  </si>
+  <si>
+    <t>1213459189153320</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta motor,propuesta alabes,propuesta nucleo rodete,propuesta tableros,propuesta compras a codigo // aprovisionamiento,Propuesta Sensores</t>
+  </si>
+  <si>
+    <t>1213459189153321</t>
+  </si>
+  <si>
+    <t>propuesta alabes</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189153322</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC motor ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189153323</t>
+  </si>
+  <si>
+    <t>propuesta tableros</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Tableros  ot 4265 - ot 4266</t>
+  </si>
+  <si>
+    <t>1213459189153324</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189153325</t>
+  </si>
+  <si>
+    <t>propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales</t>
+  </si>
+  <si>
+    <t>1213458788103036</t>
+  </si>
+  <si>
+    <t>Propuesta Sensores</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Sensores</t>
+  </si>
+  <si>
+    <t>1213458011369804</t>
+  </si>
+  <si>
+    <t>Propuesta Damper</t>
+  </si>
+  <si>
+    <t>1213459189153326</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Sensores,Materiales a codigo // compras locales aprovisionamientomiento:,rodete ot 4264,Tablero ot 4265 - ot 4266,Motor ot 4264,Alabe  ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189153327</t>
+  </si>
+  <si>
+    <t>Alabe  ot 4264</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe ot 4264,Fabricación Alabe ot 4264</t>
+  </si>
+  <si>
+    <t>1213459189153328</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe ot 4264</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe ot 4264,Alabe  ot 4264</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1213459189153314</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Damper,Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213459189153315</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
-  </si>
-  <si>
-    <t>1213459189153317</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
-  </si>
-  <si>
-    <t>1213459189153318</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta compras a codigo // aprovisionamiento,Propuesta Sensores,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1213458011369803</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Damper</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Propuesta Damper,Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>1213459189153319</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Damper,Ingenieria Basica Motor,Ingenieria Detalle,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>1213459189153320</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta motor,propuesta alabes,propuesta nucleo rodete,propuesta tableros,propuesta compras a codigo // aprovisionamiento,Propuesta Sensores</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213459189153321</t>
-  </si>
-  <si>
-    <t>propuesta alabes</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189153322</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC motor ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189153323</t>
-  </si>
-  <si>
-    <t>propuesta tableros</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Tableros  ot 4265 - ot 4266</t>
-  </si>
-  <si>
-    <t>1213459189153324</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete</t>
-  </si>
-  <si>
-    <t>NATALYA ESPINOZA</t>
-  </si>
-  <si>
-    <t>nespinoza@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189153325</t>
-  </si>
-  <si>
-    <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales</t>
-  </si>
-  <si>
-    <t>1213458788103036</t>
-  </si>
-  <si>
-    <t>Propuesta Sensores</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Sensores</t>
-  </si>
-  <si>
-    <t>1213458011369804</t>
-  </si>
-  <si>
-    <t>Propuesta Damper</t>
-  </si>
-  <si>
-    <t>1213459189153326</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Sensores,Materiales a codigo // compras locales aprovisionamientomiento:,rodete ot 4264,Tablero ot 4265 - ot 4266,Motor ot 4264,Alabe  ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189153327</t>
-  </si>
-  <si>
-    <t>Alabe  ot 4264</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe ot 4264,Fabricación Alabe ot 4264</t>
-  </si>
-  <si>
-    <t>1213459189153328</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe ot 4264</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe ot 4264,Alabe  ot 4264</t>
   </si>
   <si>
     <t>Baja</t>
@@ -2016,7 +2022,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46207.20142103009</v>
+        <v>46233.51949121528</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2025,10 +2031,10 @@
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="I12" s="5">
         <v>46202</v>
@@ -2049,10 +2055,10 @@
         <v>46</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q12" s="5">
         <v>46202</v>
@@ -2063,8 +2069,8 @@
       <c r="S12" s="6">
         <v>0</v>
       </c>
-      <c r="T12" s="11" t="s">
-        <v>58</v>
+      <c r="T12" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="U12" s="11" t="s">
         <v>32</v>
@@ -2072,7 +2078,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B13" s="8">
         <v>46079.83530335648</v>
@@ -2084,7 +2090,7 @@
         <v>46114.51491809028</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2108,7 +2114,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2125,7 +2131,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B14" s="5">
         <v>46079.83530126157</v>
@@ -2137,7 +2143,7 @@
         <v>46114.5143725</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2164,13 +2170,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Q14" s="5">
         <v>46084</v>
@@ -2190,7 +2196,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B15" s="8">
         <v>46079.83530193287</v>
@@ -2202,7 +2208,7 @@
         <v>46111.79282915509</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2229,13 +2235,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>40</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Q15" s="8">
         <v>46084</v>
@@ -2255,7 +2261,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B16" s="5">
         <v>46079.83530225694</v>
@@ -2267,7 +2273,7 @@
         <v>46114.51447722223</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2294,13 +2300,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q16" s="5">
         <v>46084</v>
@@ -2320,7 +2326,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B17" s="8">
         <v>46080.51025131944</v>
@@ -2332,7 +2338,7 @@
         <v>46114.51483395833</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
@@ -2359,13 +2365,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O17" s="9" t="s">
         <v>40</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q17" s="8">
         <v>46084</v>
@@ -2385,7 +2391,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B18" s="5">
         <v>46079.83530255787</v>
@@ -2397,7 +2403,7 @@
         <v>46114.51490420139</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2424,13 +2430,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="5">
         <v>46084</v>
@@ -2450,7 +2456,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B19" s="8">
         <v>46079.83530284722</v>
@@ -2462,7 +2468,7 @@
         <v>46222.160672025464</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>25</v>
@@ -2486,7 +2492,7 @@
         <v>26</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P19" s="9" t="s">
         <v>26</v>
@@ -2497,13 +2503,13 @@
         <v>1</v>
       </c>
       <c r="T19" s="12" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="U19" s="9"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" s="5">
         <v>46079.83530313657</v>
@@ -2515,7 +2521,7 @@
         <v>46111.79283396991</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2542,13 +2548,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="5">
         <v>46093</v>
@@ -2560,7 +2566,7 @@
         <v>1</v>
       </c>
       <c r="T20" s="12" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="U20" s="11" t="s">
         <v>32</v>
@@ -2568,7 +2574,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B21" s="8">
         <v>46079.8353034375</v>
@@ -2580,7 +2586,7 @@
         <v>46114.514961354165</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
@@ -2607,13 +2613,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q21" s="8">
         <v>46086</v>
@@ -2633,7 +2639,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46079.83530375</v>
@@ -2645,7 +2651,7 @@
         <v>46142.66126559028</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2672,13 +2678,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>49</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="5">
         <v>46087</v>
@@ -2698,7 +2704,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="8">
         <v>46079.835304050925</v>
@@ -2710,16 +2716,16 @@
         <v>46223.807620798616</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I23" s="8">
         <v>46093</v>
@@ -2737,13 +2743,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q23" s="8">
         <v>46093</v>
@@ -2763,7 +2769,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46079.83530122685</v>
@@ -2775,16 +2781,16 @@
         <v>46223.80761667824</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I24" s="5">
         <v>46093</v>
@@ -2802,13 +2808,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="5">
         <v>46093</v>
@@ -2828,7 +2834,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B25" s="8">
         <v>46079.87430951389</v>
@@ -2840,7 +2846,7 @@
         <v>46191.801115636576</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -2867,13 +2873,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q25" s="8">
         <v>46093</v>
@@ -2893,7 +2899,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46080.51039956018</v>
@@ -2905,7 +2911,7 @@
         <v>46191.80112726852</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -2932,10 +2938,10 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>26</v>
@@ -2958,7 +2964,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B27" s="8">
         <v>46079.83530158565</v>
@@ -2970,7 +2976,7 @@
         <v>46209.709468483794</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>25</v>
@@ -2994,7 +3000,7 @@
         <v>26</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>26</v>
@@ -3011,7 +3017,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B28" s="5">
         <v>46079.83530186342</v>
@@ -3023,16 +3029,16 @@
         <v>46212.17176924768</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I28" s="5">
         <v>46097</v>
@@ -3050,13 +3056,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q28" s="5">
         <v>46097</v>
@@ -3076,7 +3082,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46079.83530212963</v>
@@ -3088,16 +3094,16 @@
         <v>46169.848412384265</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I29" s="8">
         <v>46097</v>
@@ -3115,13 +3121,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3129,15 +3135,15 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46079.83530236111</v>
@@ -3149,16 +3155,16 @@
         <v>46191.87480704861</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I30" s="5">
         <v>46099</v>
@@ -3176,13 +3182,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3190,15 +3196,15 @@
         <v>0</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B31" s="8">
         <v>46079.83530269676</v>
@@ -3210,16 +3216,16 @@
         <v>46198.19648104167</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I31" s="8">
         <v>46091</v>
@@ -3237,13 +3243,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q31" s="8">
         <v>46091</v>
@@ -3263,7 +3269,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46079.83530295139</v>
@@ -3275,16 +3281,16 @@
         <v>46182.6792266088</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I32" s="5">
         <v>46091</v>
@@ -3302,13 +3308,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3316,15 +3322,15 @@
         <v>0</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46079.83530319444</v>
@@ -3336,16 +3342,16 @@
         <v>46191.874698125</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I33" s="8">
         <v>46100</v>
@@ -3363,13 +3369,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3377,15 +3383,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46079.835301238425</v>
@@ -3397,16 +3403,16 @@
         <v>46191.874603414355</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I34" s="5">
         <v>46090</v>
@@ -3424,13 +3430,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q34" s="5">
         <v>46090</v>
@@ -3442,7 +3448,7 @@
         <v>1</v>
       </c>
       <c r="T34" s="12" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="U34" s="11" t="s">
         <v>32</v>
@@ -3450,7 +3456,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B35" s="8">
         <v>46079.835301493054</v>
@@ -3462,16 +3468,16 @@
         <v>46169.84848269676</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I35" s="8">
         <v>46090</v>
@@ -3489,13 +3495,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3503,15 +3509,15 @@
         <v>0</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46079.83530179398</v>
@@ -3523,16 +3529,16 @@
         <v>46191.87457655092</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I36" s="5">
         <v>46108</v>
@@ -3550,13 +3556,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3564,15 +3570,15 @@
         <v>0</v>
       </c>
       <c r="T36" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B37" s="8">
         <v>46079.83530215277</v>
@@ -3584,16 +3590,16 @@
         <v>46169.84849621527</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I37" s="8">
         <v>46108</v>
@@ -3611,13 +3617,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3625,15 +3631,15 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46079.83530342593</v>
@@ -3645,16 +3651,16 @@
         <v>46191.875013136574</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I38" s="5">
         <v>46097</v>
@@ -3672,13 +3678,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q38" s="5">
         <v>46097</v>
@@ -3698,7 +3704,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>46079.83530366898</v>
@@ -3710,16 +3716,16 @@
         <v>46191.87447540509</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I39" s="8">
         <v>46097</v>
@@ -3737,13 +3743,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3751,15 +3757,15 @@
         <v>0</v>
       </c>
       <c r="T39" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46079.83530085648</v>
@@ -3771,16 +3777,16 @@
         <v>46191.87498288194</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I40" s="5">
         <v>46099</v>
@@ -3798,13 +3804,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3812,15 +3818,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46079.835302418986</v>
@@ -3832,16 +3838,16 @@
         <v>46191.874875995374</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I41" s="8">
         <v>46097</v>
@@ -3859,13 +3865,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q41" s="8">
         <v>46097</v>
@@ -3885,7 +3891,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46079.83530269676</v>
@@ -3897,16 +3903,16 @@
         <v>46209.779950625</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I42" s="5">
         <v>46097</v>
@@ -3924,13 +3930,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3938,15 +3944,15 @@
         <v>0</v>
       </c>
       <c r="T42" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46079.835302962965</v>
@@ -3958,16 +3964,16 @@
         <v>46114.765690740736</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I43" s="8">
         <v>46115</v>
@@ -3985,13 +3991,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3999,15 +4005,15 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46079.87449113426</v>
@@ -4019,16 +4025,16 @@
         <v>46204.18561212963</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I44" s="5">
         <v>46097</v>
@@ -4046,13 +4052,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q44" s="5">
         <v>46097</v>
@@ -4072,7 +4078,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46079.87456693287</v>
@@ -4084,16 +4090,16 @@
         <v>46191.80111972222</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I45" s="8">
         <v>46097</v>
@@ -4111,13 +4117,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4125,15 +4131,15 @@
         <v>0</v>
       </c>
       <c r="T45" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46079.8746696875</v>
@@ -4145,16 +4151,16 @@
         <v>46114.766096481486</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I46" s="5">
         <v>46126</v>
@@ -4172,13 +4178,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4186,15 +4192,15 @@
         <v>0</v>
       </c>
       <c r="T46" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U46" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46079.835303252315</v>
@@ -4204,7 +4210,7 @@
         <v>46127.68782663194</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>25</v>
@@ -4228,7 +4234,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>26</v>
@@ -4237,13 +4243,13 @@
       <c r="R47" s="9"/>
       <c r="S47" s="9"/>
       <c r="T47" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U47" s="9"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46079.8353035301</v>
@@ -4255,16 +4261,16 @@
         <v>46114.79548327546</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I48" s="5">
         <v>46093</v>
@@ -4282,13 +4288,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="5">
         <v>46093</v>
@@ -4308,7 +4314,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46079.83530068287</v>
@@ -4320,16 +4326,16 @@
         <v>46156.20046739583</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I49" s="8">
         <v>46149</v>
@@ -4347,13 +4353,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="8">
         <v>46149</v>
@@ -4373,7 +4379,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46087.628862847225</v>
@@ -4385,16 +4391,16 @@
         <v>46158.99592378472</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I50" s="5">
         <v>46156</v>
@@ -4412,13 +4418,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q50" s="5">
         <v>46156</v>
@@ -4438,7 +4444,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B51" s="8">
         <v>46087.62890292824</v>
@@ -4448,16 +4454,16 @@
         <v>46127.69021349537</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I51" s="8">
         <v>46243</v>
@@ -4475,13 +4481,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="8">
         <v>46243</v>
@@ -4493,15 +4499,15 @@
         <v>0</v>
       </c>
       <c r="T51" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U51" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46079.835301053245</v>
@@ -4513,7 +4519,7 @@
         <v>46217.8196680324</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4537,7 +4543,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4546,15 +4552,15 @@
       <c r="R52" s="6"/>
       <c r="S52" s="6"/>
       <c r="T52" s="12" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46079.835301342595</v>
@@ -4566,16 +4572,16 @@
         <v>46209.78806449074</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I53" s="8">
         <v>46147</v>
@@ -4593,13 +4599,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q53" s="8">
         <v>46147</v>
@@ -4619,7 +4625,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46079.83530162037</v>
@@ -4631,16 +4637,16 @@
         <v>46217.81965280093</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I54" s="5">
         <v>46149</v>
@@ -4658,13 +4664,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q54" s="5">
         <v>46149</v>
@@ -4684,7 +4690,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B55" s="8">
         <v>46079.835301886575</v>
@@ -4694,7 +4700,7 @@
         <v>46080.57920532407</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4718,7 +4724,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4729,15 +4735,15 @@
         <v>0</v>
       </c>
       <c r="T55" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U55" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46079.835302164356</v>
@@ -4747,16 +4753,16 @@
         <v>46217.81965958333</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I56" s="5">
         <v>46153</v>
@@ -4774,13 +4780,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="5">
         <v>46153</v>
@@ -4792,7 +4798,7 @@
         <v>0</v>
       </c>
       <c r="T56" s="12" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="U56" s="11" t="s">
         <v>32</v>
@@ -4800,7 +4806,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B57" s="8">
         <v>46079.835302418986</v>
@@ -4810,16 +4816,16 @@
         <v>46191.1671537963</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I57" s="8">
         <v>46162</v>
@@ -4837,13 +4843,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q57" s="8">
         <v>46162</v>
@@ -4855,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="T57" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U57" s="11" t="s">
         <v>32</v>
@@ -4863,7 +4869,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B58" s="5">
         <v>46079.835302673615</v>
@@ -4873,16 +4879,16 @@
         <v>46193.205434930554</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I58" s="5">
         <v>46191</v>
@@ -4900,13 +4906,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q58" s="5">
         <v>46191</v>
@@ -4918,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U58" s="11" t="s">
         <v>32</v>
@@ -4926,7 +4932,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B59" s="8">
         <v>46079.83530291667</v>
@@ -4936,7 +4942,7 @@
         <v>46216.76549305556</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -4960,7 +4966,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -4971,15 +4977,15 @@
         <v>0</v>
       </c>
       <c r="T59" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U59" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
         <v>46079.83530225694</v>
@@ -4989,16 +4995,16 @@
         <v>46214.176594108794</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I60" s="5">
         <v>46212</v>
@@ -5016,13 +5022,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q60" s="5">
         <v>46212</v>
@@ -5034,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="T60" s="12" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="U60" s="11" t="s">
         <v>32</v>
@@ -5042,7 +5048,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B61" s="8">
         <v>46079.835301851854</v>
@@ -5052,16 +5058,16 @@
         <v>46217.768278020834</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I61" s="8">
         <v>46198</v>
@@ -5079,13 +5085,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q61" s="8">
         <v>46198</v>
@@ -5097,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="T61" s="12" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="U61" s="11" t="s">
         <v>32</v>
@@ -5105,7 +5111,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
         <v>46079.87589787037</v>
@@ -5117,16 +5123,16 @@
         <v>46216.765501898146</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I62" s="5">
         <v>46204</v>
@@ -5144,13 +5150,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q62" s="5">
         <v>46204</v>
@@ -5170,7 +5176,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B63" s="8">
         <v>46079.83530319444</v>
@@ -5180,16 +5186,16 @@
         <v>46191.87499096065</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I63" s="8">
         <v>46149</v>
@@ -5207,13 +5213,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q63" s="8">
         <v>46149</v>
@@ -5225,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="T63" s="12" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="U63" s="11" t="s">
         <v>32</v>
@@ -5233,7 +5239,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B64" s="5">
         <v>46079.83530262731</v>
@@ -5245,16 +5251,16 @@
         <v>46230.175846087965</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I64" s="5">
         <v>46234</v>
@@ -5272,13 +5278,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q64" s="5">
         <v>46234</v>
@@ -5293,12 +5299,12 @@
         <v>31</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B65" s="8">
         <v>46079.835302962965</v>
@@ -5308,7 +5314,7 @@
         <v>46158.99592380787</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5332,7 +5338,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5343,15 +5349,15 @@
         <v>0</v>
       </c>
       <c r="T65" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U65" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B66" s="5">
         <v>46079.83530328704</v>
@@ -5361,16 +5367,16 @@
         <v>46223.807732870366</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I66" s="5">
         <v>46195</v>
@@ -5388,13 +5394,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q66" s="5">
         <v>46195</v>
@@ -5406,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="T66" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U66" s="11" t="s">
         <v>32</v>
@@ -5414,7 +5420,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B67" s="8">
         <v>46079.83530362268</v>
@@ -5424,16 +5430,16 @@
         <v>46232.17142269676</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I67" s="8">
         <v>46238</v>
@@ -5451,13 +5457,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q67" s="8">
         <v>46238</v>
@@ -5469,15 +5475,15 @@
         <v>0</v>
       </c>
       <c r="T67" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B68" s="5">
         <v>46079.83530398148</v>
@@ -5487,16 +5493,16 @@
         <v>46223.80773180556</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I68" s="5">
         <v>46216</v>
@@ -5514,13 +5520,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q68" s="5">
         <v>46216</v>
@@ -5532,7 +5538,7 @@
         <v>0</v>
       </c>
       <c r="T68" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U68" s="11" t="s">
         <v>32</v>
@@ -5540,7 +5546,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B69" s="8">
         <v>46079.835304293985</v>
@@ -5550,16 +5556,16 @@
         <v>46223.807731249995</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I69" s="8">
         <v>46218</v>
@@ -5577,13 +5583,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q69" s="8">
         <v>46218</v>
@@ -5595,7 +5601,7 @@
         <v>0</v>
       </c>
       <c r="T69" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U69" s="11" t="s">
         <v>32</v>
@@ -5603,7 +5609,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B70" s="5">
         <v>46080.49271868056</v>
@@ -5613,16 +5619,16 @@
         <v>46224.20075512731</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5640,13 +5646,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5658,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="T70" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U70" s="11" t="s">
         <v>32</v>
@@ -5666,26 +5672,26 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B71" s="8">
         <v>46079.83530460648</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46223.8077300463</v>
+        <v>46233.198124745366</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I71" s="8">
         <v>46240</v>
@@ -5703,13 +5709,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q71" s="8">
         <v>46240</v>
@@ -5721,15 +5727,15 @@
         <v>0</v>
       </c>
       <c r="T71" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="U71" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="U71" s="12" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B72" s="5">
         <v>46079.83530493056</v>
@@ -5739,16 +5745,16 @@
         <v>46223.807729548615</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I72" s="5">
         <v>46244</v>
@@ -5766,13 +5772,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q72" s="5">
         <v>46244</v>
@@ -5784,15 +5790,15 @@
         <v>0</v>
       </c>
       <c r="T72" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B73" s="8">
         <v>46079.83530144676</v>
@@ -5802,7 +5808,7 @@
         <v>46090.67671023148</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5826,7 +5832,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5839,7 +5845,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B74" s="5">
         <v>46079.83530181713</v>
@@ -5849,16 +5855,16 @@
         <v>46210.61678060185</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5874,13 +5880,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q74" s="5">
         <v>46245</v>
@@ -5892,15 +5898,15 @@
         <v>0</v>
       </c>
       <c r="T74" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U74" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B75" s="8">
         <v>46079.8353024074</v>
@@ -5910,16 +5916,16 @@
         <v>46223.807789224535</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I75" s="8">
         <v>46246</v>
@@ -5937,13 +5943,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q75" s="8">
         <v>46246</v>
@@ -5955,15 +5961,15 @@
         <v>0</v>
       </c>
       <c r="T75" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B76" s="5">
         <v>46079.83530269676</v>
@@ -5973,16 +5979,16 @@
         <v>46090.80487153935</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I76" s="5">
         <v>46251</v>
@@ -6000,13 +6006,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q76" s="5">
         <v>46251</v>
@@ -6018,15 +6024,15 @@
         <v>0</v>
       </c>
       <c r="T76" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U76" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B77" s="8">
         <v>46079.83530306713</v>
@@ -6036,16 +6042,16 @@
         <v>46090.80495936342</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I77" s="8">
         <v>46252</v>
@@ -6063,13 +6069,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q77" s="8">
         <v>46252</v>
@@ -6081,15 +6087,15 @@
         <v>0</v>
       </c>
       <c r="T77" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U77" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B78" s="5">
         <v>46079.83530333333</v>
@@ -6099,7 +6105,7 @@
         <v>46090.67667782407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6123,7 +6129,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6136,7 +6142,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B79" s="8">
         <v>46079.83530363426</v>
@@ -6146,16 +6152,16 @@
         <v>46090.805033425924</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I79" s="8">
         <v>46253</v>
@@ -6173,13 +6179,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q79" s="8">
         <v>46252</v>
@@ -6191,15 +6197,15 @@
         <v>0</v>
       </c>
       <c r="T79" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U79" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B80" s="5">
         <v>46079.83530395833</v>
@@ -6209,16 +6215,16 @@
         <v>46114.51489402778</v>
       </c>
       <c r="E80" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>281</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6236,13 +6242,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q80" s="5">
         <v>46252</v>
@@ -6254,15 +6260,15 @@
         <v>0</v>
       </c>
       <c r="T80" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U80" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B81" s="8">
         <v>46090.6740474074</v>
@@ -6272,7 +6278,7 @@
         <v>46090.6782175</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>25</v>
@@ -6296,7 +6302,7 @@
         <v>26</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>26</v>
@@ -6307,15 +6313,15 @@
         <v>0</v>
       </c>
       <c r="T81" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B82" s="5">
         <v>46090.674231365745</v>
@@ -6325,7 +6331,7 @@
         <v>46090.80510871528</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6352,13 +6358,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q82" s="5">
         <v>46253</v>
@@ -6370,15 +6376,15 @@
         <v>0</v>
       </c>
       <c r="T82" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U82" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B83" s="8">
         <v>46090.67444209491</v>
@@ -6388,7 +6394,7 @@
         <v>46090.80510556713</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6415,13 +6421,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q83" s="8">
         <v>46262</v>
@@ -6433,10 +6439,10 @@
         <v>0</v>
       </c>
       <c r="T83" s="11" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="U83" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -596,6 +596,9 @@
     <t>RE-PINTADO,Ingenieria y diseño:</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1213459189207069</t>
   </si>
   <si>
@@ -723,9 +726,6 @@
   </si>
   <si>
     <t>Bodega:,Montaje motor</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213459189207081</t>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46127.69021349537</v>
+        <v>46236.20194324074</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>188</v>
@@ -4501,13 +4501,13 @@
       <c r="T51" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U51" s="10" t="s">
-        <v>117</v>
+      <c r="U51" s="12" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46079.835301053245</v>
@@ -4519,7 +4519,7 @@
         <v>46217.8196680324</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4543,7 +4543,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="8">
         <v>46079.835301342595</v>
@@ -4572,16 +4572,16 @@
         <v>46209.78806449074</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I53" s="8">
         <v>46147</v>
@@ -4599,13 +4599,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>160</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q53" s="8">
         <v>46147</v>
@@ -4625,7 +4625,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B54" s="5">
         <v>46079.83530162037</v>
@@ -4637,16 +4637,16 @@
         <v>46217.81965280093</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I54" s="5">
         <v>46149</v>
@@ -4664,13 +4664,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q54" s="5">
         <v>46149</v>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B55" s="8">
         <v>46079.835301886575</v>
@@ -4700,7 +4700,7 @@
         <v>46080.57920532407</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4724,7 +4724,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4743,7 +4743,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
         <v>46079.835302164356</v>
@@ -4753,16 +4753,16 @@
         <v>46217.81965958333</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I56" s="5">
         <v>46153</v>
@@ -4780,13 +4780,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q56" s="5">
         <v>46153</v>
@@ -4806,7 +4806,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B57" s="8">
         <v>46079.835302418986</v>
@@ -4816,16 +4816,16 @@
         <v>46191.1671537963</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I57" s="8">
         <v>46162</v>
@@ -4843,13 +4843,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q57" s="8">
         <v>46162</v>
@@ -4869,7 +4869,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B58" s="5">
         <v>46079.835302673615</v>
@@ -4879,16 +4879,16 @@
         <v>46193.205434930554</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46191</v>
@@ -4906,13 +4906,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q58" s="5">
         <v>46191</v>
@@ -4932,7 +4932,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B59" s="8">
         <v>46079.83530291667</v>
@@ -4942,7 +4942,7 @@
         <v>46216.76549305556</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -4966,7 +4966,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -4985,7 +4985,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B60" s="5">
         <v>46079.83530225694</v>
@@ -4995,16 +4995,16 @@
         <v>46214.176594108794</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I60" s="5">
         <v>46212</v>
@@ -5022,13 +5022,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>119</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q60" s="5">
         <v>46212</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B61" s="8">
         <v>46079.835301851854</v>
@@ -5064,10 +5064,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I61" s="8">
         <v>46198</v>
@@ -5085,13 +5085,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>128</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q61" s="8">
         <v>46198</v>
@@ -5111,7 +5111,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B62" s="5">
         <v>46079.87589787037</v>
@@ -5123,16 +5123,16 @@
         <v>46216.765501898146</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I62" s="5">
         <v>46204</v>
@@ -5150,13 +5150,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>169</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q62" s="5">
         <v>46204</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B63" s="8">
         <v>46079.83530319444</v>
@@ -5186,16 +5186,16 @@
         <v>46191.87499096065</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I63" s="8">
         <v>46149</v>
@@ -5213,13 +5213,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>149</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q63" s="8">
         <v>46149</v>
@@ -5239,7 +5239,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B64" s="5">
         <v>46079.83530262731</v>
@@ -5251,16 +5251,16 @@
         <v>46230.175846087965</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I64" s="5">
         <v>46234</v>
@@ -5278,13 +5278,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>137</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q64" s="5">
         <v>46234</v>
@@ -5299,7 +5299,7 @@
         <v>31</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>234</v>
+        <v>191</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5367,7 +5367,7 @@
         <v>46223.807732870366</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5397,7 +5397,7 @@
         <v>236</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>239</v>
@@ -5478,7 +5478,7 @@
         <v>116</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>234</v>
+        <v>191</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5730,7 +5730,7 @@
         <v>116</v>
       </c>
       <c r="U71" s="12" t="s">
-        <v>234</v>
+        <v>191</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5985,10 +5985,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I76" s="5">
         <v>46251</v>
@@ -6048,10 +6048,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I77" s="8">
         <v>46252</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -2465,7 +2465,7 @@
         <v>46128.431861122684</v>
       </c>
       <c r="D19" s="8">
-        <v>46222.160672025464</v>
+        <v>46237.510839675924</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>81</v>
@@ -2502,8 +2502,8 @@
       <c r="S19" s="9">
         <v>1</v>
       </c>
-      <c r="T19" s="12" t="s">
-        <v>60</v>
+      <c r="T19" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U19" s="9"/>
     </row>
@@ -2518,7 +2518,7 @@
         <v>46097.54399693287</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.79283396991</v>
+        <v>46237.51069966435</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>84</v>
@@ -2565,8 +2565,8 @@
       <c r="S20" s="6">
         <v>1</v>
       </c>
-      <c r="T20" s="12" t="s">
-        <v>60</v>
+      <c r="T20" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U20" s="11" t="s">
         <v>32</v>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.1671537963</v>
+        <v>46237.51101253473</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>213</v>
@@ -4860,8 +4860,8 @@
       <c r="S57" s="9">
         <v>0</v>
       </c>
-      <c r="T57" s="11" t="s">
-        <v>116</v>
+      <c r="T57" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="U57" s="11" t="s">
         <v>32</v>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46193.205434930554</v>
+        <v>46237.511034675925</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4923,8 +4923,8 @@
       <c r="S58" s="6">
         <v>0</v>
       </c>
-      <c r="T58" s="11" t="s">
-        <v>116</v>
+      <c r="T58" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="U58" s="11" t="s">
         <v>32</v>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46223.807729548615</v>
+        <v>46237.19014446759</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>258</v>
@@ -5792,8 +5792,8 @@
       <c r="T72" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U72" s="10" t="s">
-        <v>117</v>
+      <c r="U72" s="12" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -2022,7 +2022,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46233.51949121528</v>
+        <v>46238.491149560185</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2067,7 +2067,7 @@
         <v>46206</v>
       </c>
       <c r="S12" s="6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T12" s="12" t="s">
         <v>60</v>
@@ -5248,7 +5248,7 @@
         <v>46216.7654346412</v>
       </c>
       <c r="D64" s="5">
-        <v>46230.175846087965</v>
+        <v>46238.1728743287</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>233</v>
@@ -5298,8 +5298,8 @@
       <c r="T64" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U64" s="12" t="s">
-        <v>191</v>
+      <c r="U64" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46210.61678060185</v>
+        <v>46238.2035983449</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>264</v>
@@ -5900,8 +5900,8 @@
       <c r="T74" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U74" s="10" t="s">
-        <v>117</v>
+      <c r="U74" s="12" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -5427,7 +5427,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46232.17142269676</v>
+        <v>46239.16743914352</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -5427,7 +5427,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46239.16743914352</v>
+        <v>46240.19951064815</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5477,8 +5477,8 @@
       <c r="T67" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U67" s="12" t="s">
-        <v>191</v>
+      <c r="U67" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46233.198124745366</v>
+        <v>46240.167355439815</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>189</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="287">
   <si>
     <t>50001518 - EQ. CHAPARRAL</t>
   </si>
@@ -851,7 +851,7 @@
     <t>Despacho</t>
   </si>
   <si>
-    <t>Gestion,Costos,Logistica:,Instalación de Componentes,Instalación de componentes</t>
+    <t>Gestion,Costos,Logistica:</t>
   </si>
   <si>
     <t>1213459189153338</t>
@@ -882,30 +882,6 @@
   </si>
   <si>
     <t>Despacho,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213575386156289</t>
-  </si>
-  <si>
-    <t>Puesta en marcha Servicios</t>
-  </si>
-  <si>
-    <t>Instalación de Componentes,Pruebas de instalación Componentes</t>
-  </si>
-  <si>
-    <t>1213575386156293</t>
-  </si>
-  <si>
-    <t>Instalación de Componentes</t>
-  </si>
-  <si>
-    <t>Pruebas de instalación Componentes,Puesta en marcha Servicios</t>
-  </si>
-  <si>
-    <t>1213575386156295</t>
-  </si>
-  <si>
-    <t>Pruebas de instalación Componentes</t>
   </si>
 </sst>
 </file>
@@ -1429,7 +1405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U83"/>
+  <dimension ref="A1:U80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -6039,7 +6015,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46090.80495936342</v>
+        <v>46240.72128056713</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>275</v>
@@ -6263,185 +6239,6 @@
         <v>116</v>
       </c>
       <c r="U80" s="10" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="B81" s="8">
-        <v>46090.6740474074</v>
-      </c>
-      <c r="C81" s="9"/>
-      <c r="D81" s="8">
-        <v>46090.6782175</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="9"/>
-      <c r="I81" s="9"/>
-      <c r="J81" s="9"/>
-      <c r="K81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M81" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O81" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="P81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q81" s="9"/>
-      <c r="R81" s="9"/>
-      <c r="S81" s="9">
-        <v>0</v>
-      </c>
-      <c r="T81" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="U81" s="10" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="B82" s="5">
-        <v>46090.674231365745</v>
-      </c>
-      <c r="C82" s="6"/>
-      <c r="D82" s="5">
-        <v>46090.80510871528</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="F82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I82" s="5">
-        <v>46253</v>
-      </c>
-      <c r="J82" s="5">
-        <v>46261</v>
-      </c>
-      <c r="K82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N82" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q82" s="5">
-        <v>46253</v>
-      </c>
-      <c r="R82" s="5">
-        <v>46261</v>
-      </c>
-      <c r="S82" s="6">
-        <v>0</v>
-      </c>
-      <c r="T82" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="U82" s="10" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="B83" s="8">
-        <v>46090.67444209491</v>
-      </c>
-      <c r="C83" s="9"/>
-      <c r="D83" s="8">
-        <v>46090.80510556713</v>
-      </c>
-      <c r="E83" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I83" s="8">
-        <v>46262</v>
-      </c>
-      <c r="J83" s="8">
-        <v>46272</v>
-      </c>
-      <c r="K83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N83" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="O83" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q83" s="8">
-        <v>46262</v>
-      </c>
-      <c r="R83" s="8">
-        <v>46272</v>
-      </c>
-      <c r="S83" s="9">
-        <v>0</v>
-      </c>
-      <c r="T83" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="U83" s="10" t="s">
         <v>117</v>
       </c>
     </row>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -5655,7 +5655,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46240.167355439815</v>
+        <v>46241.1946021412</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>189</v>
@@ -5705,8 +5705,8 @@
       <c r="T71" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U71" s="12" t="s">
-        <v>191</v>
+      <c r="U71" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46223.807789224535</v>
+        <v>46241.20193481482</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>59</v>
@@ -5939,8 +5939,8 @@
       <c r="T75" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U75" s="10" t="s">
-        <v>117</v>
+      <c r="U75" s="12" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -4427,7 +4427,7 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46236.20194324074</v>
+        <v>46243.16677869213</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>188</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -596,211 +596,211 @@
     <t>RE-PINTADO,Ingenieria y diseño:</t>
   </si>
   <si>
+    <t>1213459189207069</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213459189207070</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:</t>
+  </si>
+  <si>
+    <t>1213459189207071</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega:,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1213459189207072</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1213459189207073</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>Caldereria:,Armado,Armado</t>
+  </si>
+  <si>
+    <t>1213459189207074</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Check plano</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213459189207075</t>
+  </si>
+  <si>
+    <t>Armado,Check plano</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>1213459189207076</t>
+  </si>
+  <si>
+    <t>Recepcion Sensores,Recepcion Rodete,Recepcion Tableros,Recepcion Alabe,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1213459189207079</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1213459189207078</t>
+  </si>
+  <si>
+    <t>Bodega:,Revisión tableros pruebas,Ingenieria Servicios:</t>
+  </si>
+  <si>
+    <t>1213458788103048</t>
+  </si>
+  <si>
+    <t>Recepcion Sensores</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje sensor</t>
+  </si>
+  <si>
+    <t>1213459189207077</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1213459189207080</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje motor</t>
+  </si>
+  <si>
+    <t>1213459189207081</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje motor,Montaje Rodete,Montaje sensor,Montaje Alabe,Pruebas FAT,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1213459189207082</t>
+  </si>
+  <si>
+    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensor,Montaje:</t>
+  </si>
+  <si>
+    <t>1213459189207083</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion motor,Check plano</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,Montaje:</t>
+  </si>
+  <si>
+    <t>1213459189207084</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion Alabe,Check plano</t>
+  </si>
+  <si>
+    <t>Montaje Rodete,Pruebas FAT,Montaje:</t>
+  </si>
+  <si>
+    <t>1213459189207085</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,Revestimiento,Recepcion Rodete,Check plano</t>
+  </si>
+  <si>
+    <t>1213458788103121</t>
+  </si>
+  <si>
+    <t>Montaje sensor</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion Sensores,Check plano</t>
+  </si>
+  <si>
+    <t>1213459189207086</t>
+  </si>
+  <si>
+    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensor</t>
+  </si>
+  <si>
+    <t>Montaje:,Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213459189207087</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Montaje:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213459189207069</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213459189207070</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:</t>
-  </si>
-  <si>
-    <t>1213459189207071</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega:,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1213459189207072</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1213459189207073</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Caldereria:,Armado,Armado</t>
-  </si>
-  <si>
-    <t>1213459189207074</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Check plano</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213459189207075</t>
-  </si>
-  <si>
-    <t>Armado,Check plano</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>1213459189207076</t>
-  </si>
-  <si>
-    <t>Recepcion Sensores,Recepcion Rodete,Recepcion Tableros,Recepcion Alabe,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1213459189207079</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1213459189207078</t>
-  </si>
-  <si>
-    <t>Bodega:,Revisión tableros pruebas,Ingenieria Servicios:</t>
-  </si>
-  <si>
-    <t>1213458788103048</t>
-  </si>
-  <si>
-    <t>Recepcion Sensores</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje sensor</t>
-  </si>
-  <si>
-    <t>1213459189207077</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1213459189207080</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje motor</t>
-  </si>
-  <si>
-    <t>1213459189207081</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje motor,Montaje Rodete,Montaje sensor,Montaje Alabe,Pruebas FAT,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1213459189207082</t>
-  </si>
-  <si>
-    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensor,Montaje:</t>
-  </si>
-  <si>
-    <t>1213459189207083</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion motor,Check plano</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,Montaje:</t>
-  </si>
-  <si>
-    <t>1213459189207084</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion Alabe,Check plano</t>
-  </si>
-  <si>
-    <t>Montaje Rodete,Pruebas FAT,Montaje:</t>
-  </si>
-  <si>
-    <t>1213459189207085</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,Revestimiento,Recepcion Rodete,Check plano</t>
-  </si>
-  <si>
-    <t>1213458788103121</t>
-  </si>
-  <si>
-    <t>Montaje sensor</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion Sensores,Check plano</t>
-  </si>
-  <si>
-    <t>1213459189207086</t>
-  </si>
-  <si>
-    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensor</t>
-  </si>
-  <si>
-    <t>Montaje:,Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213459189207087</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Montaje:</t>
   </si>
   <si>
     <t>1213459189207088</t>
@@ -2949,7 +2949,7 @@
         <v>46209.70945200232</v>
       </c>
       <c r="D27" s="8">
-        <v>46209.709468483794</v>
+        <v>46244.07001481482</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>106</v>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46243.16677869213</v>
+        <v>46244.17012701389</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>188</v>
@@ -4477,13 +4477,13 @@
       <c r="T51" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U51" s="12" t="s">
-        <v>191</v>
+      <c r="U51" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46079.835301053245</v>
@@ -4495,7 +4495,7 @@
         <v>46217.8196680324</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4519,7 +4519,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4536,7 +4536,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46079.835301342595</v>
@@ -4548,16 +4548,16 @@
         <v>46209.78806449074</v>
       </c>
       <c r="E53" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="F53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="9" t="s">
+      <c r="H53" s="9" t="s">
         <v>197</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>198</v>
       </c>
       <c r="I53" s="8">
         <v>46147</v>
@@ -4575,13 +4575,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>160</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q53" s="8">
         <v>46147</v>
@@ -4601,7 +4601,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46079.83530162037</v>
@@ -4613,16 +4613,16 @@
         <v>46217.81965280093</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I54" s="5">
         <v>46149</v>
@@ -4640,13 +4640,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q54" s="5">
         <v>46149</v>
@@ -4666,7 +4666,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B55" s="8">
         <v>46079.835301886575</v>
@@ -4676,7 +4676,7 @@
         <v>46080.57920532407</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4700,7 +4700,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4719,7 +4719,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46079.835302164356</v>
@@ -4729,16 +4729,16 @@
         <v>46217.81965958333</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I56" s="5">
         <v>46153</v>
@@ -4756,13 +4756,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="5">
         <v>46153</v>
@@ -4782,7 +4782,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B57" s="8">
         <v>46079.835302418986</v>
@@ -4792,16 +4792,16 @@
         <v>46237.51101253473</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I57" s="8">
         <v>46162</v>
@@ -4819,13 +4819,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O57" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="P57" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="P57" s="9" t="s">
-        <v>215</v>
       </c>
       <c r="Q57" s="8">
         <v>46162</v>
@@ -4845,7 +4845,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B58" s="5">
         <v>46079.835302673615</v>
@@ -4855,16 +4855,16 @@
         <v>46237.511034675925</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46191</v>
@@ -4882,13 +4882,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>217</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>218</v>
       </c>
       <c r="Q58" s="5">
         <v>46191</v>
@@ -4908,17 +4908,17 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B59" s="8">
         <v>46079.83530291667</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46216.76549305556</v>
+        <v>46244.07001476852</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -4942,7 +4942,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -4961,7 +4961,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
         <v>46079.83530225694</v>
@@ -4971,16 +4971,16 @@
         <v>46214.176594108794</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="I60" s="5">
         <v>46212</v>
@@ -4998,13 +4998,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>119</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q60" s="5">
         <v>46212</v>
@@ -5024,7 +5024,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B61" s="8">
         <v>46079.835301851854</v>
@@ -5040,10 +5040,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>197</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>198</v>
       </c>
       <c r="I61" s="8">
         <v>46198</v>
@@ -5061,13 +5061,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>128</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q61" s="8">
         <v>46198</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
         <v>46079.87589787037</v>
@@ -5099,16 +5099,16 @@
         <v>46216.765501898146</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="I62" s="5">
         <v>46204</v>
@@ -5126,13 +5126,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>169</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q62" s="5">
         <v>46204</v>
@@ -5152,7 +5152,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B63" s="8">
         <v>46079.83530319444</v>
@@ -5162,16 +5162,16 @@
         <v>46191.87499096065</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>197</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>198</v>
       </c>
       <c r="I63" s="8">
         <v>46149</v>
@@ -5189,13 +5189,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>149</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q63" s="8">
         <v>46149</v>
@@ -5215,7 +5215,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B64" s="5">
         <v>46079.83530262731</v>
@@ -5227,16 +5227,16 @@
         <v>46238.1728743287</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="I64" s="5">
         <v>46234</v>
@@ -5254,13 +5254,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>137</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q64" s="5">
         <v>46234</v>
@@ -5280,17 +5280,17 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B65" s="8">
         <v>46079.835302962965</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46158.99592380787</v>
+        <v>46244.07004141204</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5314,7 +5314,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5333,7 +5333,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B66" s="5">
         <v>46079.83530328704</v>
@@ -5343,7 +5343,7 @@
         <v>46223.807732870366</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5370,13 +5370,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q66" s="5">
         <v>46195</v>
@@ -5396,7 +5396,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B67" s="8">
         <v>46079.83530362268</v>
@@ -5406,7 +5406,7 @@
         <v>46240.19951064815</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5433,13 +5433,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O67" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="P67" s="9" t="s">
         <v>242</v>
-      </c>
-      <c r="P67" s="9" t="s">
-        <v>243</v>
       </c>
       <c r="Q67" s="8">
         <v>46238</v>
@@ -5459,7 +5459,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B68" s="5">
         <v>46079.83530398148</v>
@@ -5469,7 +5469,7 @@
         <v>46223.80773180556</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5496,13 +5496,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>246</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>247</v>
       </c>
       <c r="Q68" s="5">
         <v>46216</v>
@@ -5522,7 +5522,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B69" s="8">
         <v>46079.835304293985</v>
@@ -5532,7 +5532,7 @@
         <v>46223.807731249995</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5559,13 +5559,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q69" s="8">
         <v>46218</v>
@@ -5585,7 +5585,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B70" s="5">
         <v>46080.49271868056</v>
@@ -5595,7 +5595,7 @@
         <v>46224.20075512731</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5622,13 +5622,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5648,7 +5648,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B71" s="8">
         <v>46079.83530460648</v>
@@ -5685,13 +5685,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O71" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="P71" s="9" t="s">
         <v>255</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>256</v>
       </c>
       <c r="Q71" s="8">
         <v>46240</v>
@@ -5711,17 +5711,17 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B72" s="5">
         <v>46079.83530493056</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46237.19014446759</v>
+        <v>46244.16760674768</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5748,13 +5748,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q72" s="5">
         <v>46244</v>
@@ -5769,7 +5769,7 @@
         <v>116</v>
       </c>
       <c r="U72" s="12" t="s">
-        <v>191</v>
+        <v>259</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5859,7 +5859,7 @@
         <v>261</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>267</v>
@@ -5877,7 +5877,7 @@
         <v>116</v>
       </c>
       <c r="U74" s="12" t="s">
-        <v>191</v>
+        <v>259</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5940,7 +5940,7 @@
         <v>116</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>191</v>
+        <v>259</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.80487153935</v>
+        <v>46244.19896359954</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>272</v>
@@ -5961,10 +5961,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I76" s="5">
         <v>46251</v>
@@ -6002,8 +6002,8 @@
       <c r="T76" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U76" s="10" t="s">
-        <v>117</v>
+      <c r="U76" s="12" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6024,10 +6024,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I77" s="8">
         <v>46252</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -800,31 +800,31 @@
     <t>Coordinacion Entrega con Cliente,Montaje:</t>
   </si>
   <si>
+    <t>1213459189207088</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
+  </si>
+  <si>
+    <t>1213459189207089</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>Embalaje,Logistica:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213459189207088</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
-  </si>
-  <si>
-    <t>1213459189207089</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>Embalaje,Logistica:</t>
   </si>
   <si>
     <t>1213459189207090</t>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46244.16760674768</v>
+        <v>46245.16678976852</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>257</v>
@@ -5768,13 +5768,13 @@
       <c r="T72" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U72" s="12" t="s">
-        <v>259</v>
+      <c r="U72" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B73" s="8">
         <v>46079.83530144676</v>
@@ -5784,7 +5784,7 @@
         <v>46090.67671023148</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5808,7 +5808,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5821,26 +5821,26 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B74" s="5">
         <v>46079.83530181713</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46238.2035983449</v>
+        <v>46245.16728820602</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="6" t="s">
+      <c r="H74" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5856,13 +5856,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>257</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q74" s="5">
         <v>46245</v>
@@ -5877,7 +5877,7 @@
         <v>116</v>
       </c>
       <c r="U74" s="12" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5919,7 +5919,7 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O75" s="9" t="s">
         <v>269</v>
@@ -5940,7 +5940,7 @@
         <v>116</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -5982,7 +5982,7 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>59</v>
@@ -6003,7 +6003,7 @@
         <v>116</v>
       </c>
       <c r="U76" s="12" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46240.72128056713</v>
+        <v>46245.205981631945</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>275</v>
@@ -6045,7 +6045,7 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>272</v>
@@ -6065,8 +6065,8 @@
       <c r="T77" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U77" s="10" t="s">
-        <v>117</v>
+      <c r="U77" s="12" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -824,16 +824,16 @@
     <t>Embalaje,Logistica:</t>
   </si>
   <si>
+    <t>1213459189207090</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Revisión tableros pruebas</t>
+  </si>
+  <si>
+    <t>PACKING LIST,Logistica:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213459189207090</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Revisión tableros pruebas</t>
-  </si>
-  <si>
-    <t>PACKING LIST,Logistica:</t>
   </si>
   <si>
     <t>1213459189207091</t>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46245.16728820602</v>
+        <v>46246.17437313657</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>263</v>
@@ -5876,13 +5876,13 @@
       <c r="T74" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U74" s="12" t="s">
-        <v>267</v>
+      <c r="U74" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B75" s="8">
         <v>46079.8353024074</v>
@@ -5922,10 +5922,10 @@
         <v>260</v>
       </c>
       <c r="O75" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="P75" s="9" t="s">
         <v>269</v>
-      </c>
-      <c r="P75" s="9" t="s">
-        <v>270</v>
       </c>
       <c r="Q75" s="8">
         <v>46246</v>
@@ -5940,7 +5940,7 @@
         <v>116</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6003,7 +6003,7 @@
         <v>116</v>
       </c>
       <c r="U76" s="12" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6066,7 +6066,7 @@
         <v>116</v>
       </c>
       <c r="U77" s="12" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="289">
   <si>
     <t>50001518 - EQ. CHAPARRAL</t>
   </si>
@@ -581,7 +581,7 @@
     <t>1213560053852552</t>
   </si>
   <si>
-    <t>Armado,Control de calidad Armado,Ingenieria y diseño:,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensor</t>
+    <t>Fabricación ,Control de calidad Armado,Ingenieria y diseño:,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensor</t>
   </si>
   <si>
     <t>1213560053852553</t>
@@ -632,214 +632,220 @@
     <t>nicolas.lopez@zitron.com</t>
   </si>
   <si>
-    <t>Bodega:,Preparación Materiales</t>
+    <t xml:space="preserve">Bodega:,Generación OC </t>
   </si>
   <si>
     <t>1213459189207072</t>
   </si>
   <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
+    <t>Fabricación externa :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC </t>
   </si>
   <si>
     <t>1213459189207073</t>
   </si>
   <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación externa :,Fabricación ,Armado</t>
+  </si>
+  <si>
+    <t>1213459189207074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación </t>
+  </si>
+  <si>
+    <t>Generación OC ,Check plano</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213459189207075</t>
+  </si>
+  <si>
+    <t>Fabricación ,Check plano</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>1213459189207076</t>
+  </si>
+  <si>
+    <t>Recepcion Sensores,Recepcion Rodete,Recepcion Tableros,Recepcion Alabe,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1213459189207079</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1213459189207078</t>
+  </si>
+  <si>
+    <t>Bodega:,Revisión tableros pruebas,Ingenieria Servicios:</t>
+  </si>
+  <si>
+    <t>1213458788103048</t>
+  </si>
+  <si>
+    <t>Recepcion Sensores</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje sensor</t>
+  </si>
+  <si>
+    <t>1213459189207077</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1213459189207080</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje motor</t>
+  </si>
+  <si>
+    <t>1213459189207081</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje motor,Montaje Rodete,Montaje sensor,Montaje Alabe,Pruebas FAT,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1213459189207082</t>
+  </si>
+  <si>
+    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensor,Montaje:</t>
+  </si>
+  <si>
+    <t>1213459189207083</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion motor,Check plano</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,Montaje:</t>
+  </si>
+  <si>
+    <t>1213459189207084</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion Alabe,Check plano</t>
+  </si>
+  <si>
+    <t>Montaje Rodete,Pruebas FAT,Montaje:</t>
+  </si>
+  <si>
+    <t>1213459189207085</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,Revestimiento,Recepcion Rodete,Check plano</t>
+  </si>
+  <si>
+    <t>1213458788103121</t>
+  </si>
+  <si>
+    <t>Montaje sensor</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion Sensores,Check plano</t>
+  </si>
+  <si>
+    <t>1213459189207086</t>
+  </si>
+  <si>
+    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensor</t>
+  </si>
+  <si>
+    <t>Montaje:,Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213459189207087</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Montaje:</t>
+  </si>
+  <si>
+    <t>1213459189207088</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
+  </si>
+  <si>
+    <t>1213459189207089</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>Embalaje,Logistica:</t>
+  </si>
+  <si>
+    <t>1213459189207090</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Revisión tableros pruebas</t>
+  </si>
+  <si>
+    <t>PACKING LIST,Logistica:</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1213459189207091</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
+  </si>
+  <si>
     <t>Nicolás Mol</t>
   </si>
   <si>
     <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Caldereria:,Armado,Armado</t>
-  </si>
-  <si>
-    <t>1213459189207074</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Check plano</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213459189207075</t>
-  </si>
-  <si>
-    <t>Armado,Check plano</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>1213459189207076</t>
-  </si>
-  <si>
-    <t>Recepcion Sensores,Recepcion Rodete,Recepcion Tableros,Recepcion Alabe,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1213459189207079</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1213459189207078</t>
-  </si>
-  <si>
-    <t>Bodega:,Revisión tableros pruebas,Ingenieria Servicios:</t>
-  </si>
-  <si>
-    <t>1213458788103048</t>
-  </si>
-  <si>
-    <t>Recepcion Sensores</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje sensor</t>
-  </si>
-  <si>
-    <t>1213459189207077</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1213459189207080</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje motor</t>
-  </si>
-  <si>
-    <t>1213459189207081</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje motor,Montaje Rodete,Montaje sensor,Montaje Alabe,Pruebas FAT,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1213459189207082</t>
-  </si>
-  <si>
-    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensor,Montaje:</t>
-  </si>
-  <si>
-    <t>1213459189207083</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion motor,Check plano</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,Montaje:</t>
-  </si>
-  <si>
-    <t>1213459189207084</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion Alabe,Check plano</t>
-  </si>
-  <si>
-    <t>Montaje Rodete,Pruebas FAT,Montaje:</t>
-  </si>
-  <si>
-    <t>1213459189207085</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,Revestimiento,Recepcion Rodete,Check plano</t>
-  </si>
-  <si>
-    <t>1213458788103121</t>
-  </si>
-  <si>
-    <t>Montaje sensor</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion Sensores,Check plano</t>
-  </si>
-  <si>
-    <t>1213459189207086</t>
-  </si>
-  <si>
-    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensor</t>
-  </si>
-  <si>
-    <t>Montaje:,Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213459189207087</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Montaje:</t>
-  </si>
-  <si>
-    <t>1213459189207088</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
-  </si>
-  <si>
-    <t>1213459189207089</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>Embalaje,Logistica:</t>
-  </si>
-  <si>
-    <t>1213459189207090</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Revisión tableros pruebas</t>
-  </si>
-  <si>
-    <t>PACKING LIST,Logistica:</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>1213459189207091</t>
-  </si>
-  <si>
-    <t>PACKING LIST</t>
   </si>
   <si>
     <t>Despacho,Logistica:</t>
@@ -4673,7 +4679,7 @@
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46080.57920532407</v>
+        <v>46246.791487766204</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4726,7 +4732,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46217.81965958333</v>
+        <v>46246.791789560186</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4789,7 +4795,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46237.51101253473</v>
+        <v>46246.79178846064</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>212</v>
@@ -4968,7 +4974,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46214.176594108794</v>
+        <v>46246.7938296412</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -5961,10 +5967,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>208</v>
+        <v>273</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="I76" s="5">
         <v>46251</v>
@@ -5988,7 +5994,7 @@
         <v>59</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q76" s="5">
         <v>46251</v>
@@ -6008,7 +6014,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B77" s="8">
         <v>46079.83530306713</v>
@@ -6018,16 +6024,16 @@
         <v>46245.205981631945</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>208</v>
+        <v>273</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="I77" s="8">
         <v>46252</v>
@@ -6051,7 +6057,7 @@
         <v>272</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q77" s="8">
         <v>46252</v>
@@ -6071,7 +6077,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B78" s="5">
         <v>46079.83530333333</v>
@@ -6081,7 +6087,7 @@
         <v>46090.67667782407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6105,7 +6111,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6118,7 +6124,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B79" s="8">
         <v>46079.83530363426</v>
@@ -6128,16 +6134,16 @@
         <v>46090.805033425924</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I79" s="8">
         <v>46253</v>
@@ -6155,13 +6161,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q79" s="8">
         <v>46252</v>
@@ -6181,7 +6187,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B80" s="5">
         <v>46079.83530395833</v>
@@ -6191,16 +6197,16 @@
         <v>46114.51489402778</v>
       </c>
       <c r="E80" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>285</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>283</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6218,13 +6224,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q80" s="5">
         <v>46252</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -4679,7 +4679,7 @@
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46246.791487766204</v>
+        <v>46246.86788697916</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4716,8 +4716,8 @@
       <c r="S55" s="9">
         <v>0</v>
       </c>
-      <c r="T55" s="11" t="s">
-        <v>116</v>
+      <c r="T55" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="U55" s="10" t="s">
         <v>117</v>
@@ -4730,9 +4730,11 @@
       <c r="B56" s="5">
         <v>46079.835302164356</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46246.867865057866</v>
+      </c>
       <c r="D56" s="5">
-        <v>46246.791789560186</v>
+        <v>46246.86788344907</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4777,10 +4779,10 @@
         <v>46161</v>
       </c>
       <c r="S56" s="6">
-        <v>0</v>
-      </c>
-      <c r="T56" s="12" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="T56" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U56" s="11" t="s">
         <v>32</v>
@@ -4793,9 +4795,11 @@
       <c r="B57" s="8">
         <v>46079.835302418986</v>
       </c>
-      <c r="C57" s="9"/>
+      <c r="C57" s="8">
+        <v>46246.86958221065</v>
+      </c>
       <c r="D57" s="8">
-        <v>46246.79178846064</v>
+        <v>46246.86959988426</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>212</v>
@@ -4840,10 +4844,10 @@
         <v>46190</v>
       </c>
       <c r="S57" s="9">
-        <v>0</v>
-      </c>
-      <c r="T57" s="12" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="T57" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U57" s="11" t="s">
         <v>32</v>
@@ -4858,7 +4862,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46237.511034675925</v>
+        <v>46246.86958899305</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -4972,9 +4976,11 @@
       <c r="B60" s="5">
         <v>46079.83530225694</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46246.87366135417</v>
+      </c>
       <c r="D60" s="5">
-        <v>46246.7938296412</v>
+        <v>46246.87366309028</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="289">
   <si>
     <t>50001518 - EQ. CHAPARRAL</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>Recepcion Tableros,Ingenieria electrica</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213459189153312</t>
@@ -201,9 +204,6 @@
   </si>
   <si>
     <t>Embalaje</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213459189153314</t>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46142.66126674769</v>
+        <v>46246.87440424769</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1927,12 +1927,14 @@
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
+      <c r="T10" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="U10" s="6"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="8">
         <v>46079.835302858795</v>
@@ -1944,16 +1946,16 @@
         <v>46142.661260625</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I11" s="8">
         <v>46084</v>
@@ -1965,7 +1967,7 @@
         <v>26</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M11" s="9" t="s">
         <v>26</v>
@@ -1977,7 +1979,7 @@
         <v>40</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q11" s="8">
         <v>46084</v>
@@ -1997,26 +1999,26 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="5">
         <v>46079.83530313657</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46238.491149560185</v>
+        <v>46246.87971918982</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I12" s="5">
         <v>46202</v>
@@ -2037,10 +2039,10 @@
         <v>46</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q12" s="5">
         <v>46202</v>
@@ -2052,7 +2054,7 @@
         <v>0.1</v>
       </c>
       <c r="T12" s="12" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="U12" s="11" t="s">
         <v>32</v>
@@ -2663,7 +2665,7 @@
         <v>81</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>91</v>
@@ -3430,7 +3432,7 @@
         <v>1</v>
       </c>
       <c r="T34" s="12" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="U34" s="11" t="s">
         <v>32</v>
@@ -4534,7 +4536,7 @@
       <c r="R52" s="6"/>
       <c r="S52" s="6"/>
       <c r="T52" s="12" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="U52" s="10" t="s">
         <v>117</v>
@@ -4717,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="T55" s="12" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="U55" s="10" t="s">
         <v>117</v>
@@ -4910,7 +4912,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="12" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="U58" s="11" t="s">
         <v>32</v>
@@ -4925,7 +4927,7 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46244.07001476852</v>
+        <v>46246.87439424769</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>192</v>
@@ -4976,11 +4978,9 @@
       <c r="B60" s="5">
         <v>46079.83530225694</v>
       </c>
-      <c r="C60" s="5">
-        <v>46246.87366135417</v>
-      </c>
+      <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46246.87366309028</v>
+        <v>46246.87417596065</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -5025,10 +5025,10 @@
         <v>46213</v>
       </c>
       <c r="S60" s="6">
-        <v>0</v>
-      </c>
-      <c r="T60" s="12" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="T60" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U60" s="11" t="s">
         <v>32</v>
@@ -5041,12 +5041,14 @@
       <c r="B61" s="8">
         <v>46079.835301851854</v>
       </c>
-      <c r="C61" s="9"/>
+      <c r="C61" s="8">
+        <v>46246.874389398145</v>
+      </c>
       <c r="D61" s="8">
-        <v>46217.768278020834</v>
+        <v>46246.87440410879</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -5088,10 +5090,10 @@
         <v>46199</v>
       </c>
       <c r="S61" s="9">
-        <v>0</v>
-      </c>
-      <c r="T61" s="12" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="T61" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U61" s="11" t="s">
         <v>32</v>
@@ -5219,7 +5221,7 @@
         <v>0</v>
       </c>
       <c r="T63" s="12" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="U63" s="11" t="s">
         <v>32</v>
@@ -5478,7 +5480,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46223.80773180556</v>
+        <v>46246.87418032407</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5904,7 +5906,7 @@
         <v>46241.20193481482</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5997,7 +5999,7 @@
         <v>260</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>275</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46246.87971918982</v>
+        <v>46247.879409166664</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46241.20193481482</v>
+        <v>46248.25032157407</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>60</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -833,22 +833,22 @@
     <t>PACKING LIST,Logistica:</t>
   </si>
   <si>
+    <t>1213459189207091</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>Despacho,Logistica:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213459189207091</t>
-  </si>
-  <si>
-    <t>PACKING LIST</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Despacho,Logistica:</t>
   </si>
   <si>
     <t>1213459189153337</t>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46248.25032157407</v>
+        <v>46249.19508818287</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>60</v>
@@ -5953,13 +5953,13 @@
       <c r="T75" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U75" s="12" t="s">
-        <v>270</v>
+      <c r="U75" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B76" s="5">
         <v>46079.83530269676</v>
@@ -5969,16 +5969,16 @@
         <v>46244.19896359954</v>
       </c>
       <c r="E76" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="F76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G76" s="6" t="s">
+      <c r="H76" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="I76" s="5">
         <v>46251</v>
@@ -6002,7 +6002,7 @@
         <v>60</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q76" s="5">
         <v>46251</v>
@@ -6017,7 +6017,7 @@
         <v>116</v>
       </c>
       <c r="U76" s="12" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6038,10 +6038,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>273</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>274</v>
       </c>
       <c r="I77" s="8">
         <v>46252</v>
@@ -6062,7 +6062,7 @@
         <v>260</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>278</v>
@@ -6080,7 +6080,7 @@
         <v>116</v>
       </c>
       <c r="U77" s="12" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -5966,7 +5966,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46244.19896359954</v>
+        <v>46251.250281608794</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>271</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -848,16 +848,16 @@
     <t>Despacho,Logistica:</t>
   </si>
   <si>
+    <t>1213459189153337</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>Gestion,Costos,Logistica:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213459189153337</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>Gestion,Costos,Logistica:</t>
   </si>
   <si>
     <t>1213459189153338</t>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46251.250281608794</v>
+        <v>46252.19153056713</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>271</v>
@@ -6016,23 +6016,23 @@
       <c r="T76" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U76" s="12" t="s">
-        <v>275</v>
+      <c r="U76" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B77" s="8">
         <v>46079.83530306713</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46245.205981631945</v>
+        <v>46252.25019825231</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6065,7 +6065,7 @@
         <v>271</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q77" s="8">
         <v>46252</v>
@@ -6080,7 +6080,7 @@
         <v>116</v>
       </c>
       <c r="U77" s="12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6172,7 +6172,7 @@
         <v>280</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>280</v>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -857,28 +857,28 @@
     <t>Gestion,Costos,Logistica:</t>
   </si>
   <si>
+    <t>1213459189153338</t>
+  </si>
+  <si>
+    <t>Cierre proyecto:</t>
+  </si>
+  <si>
+    <t>Gestion,Costos</t>
+  </si>
+  <si>
+    <t>1213459189153339</t>
+  </si>
+  <si>
+    <t>Gestion</t>
+  </si>
+  <si>
+    <t>Nicolás</t>
+  </si>
+  <si>
+    <t>nicolas.tello@zitron.com</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213459189153338</t>
-  </si>
-  <si>
-    <t>Cierre proyecto:</t>
-  </si>
-  <si>
-    <t>Gestion,Costos</t>
-  </si>
-  <si>
-    <t>1213459189153339</t>
-  </si>
-  <si>
-    <t>Gestion</t>
-  </si>
-  <si>
-    <t>Nicolás</t>
-  </si>
-  <si>
-    <t>nicolas.tello@zitron.com</t>
   </si>
   <si>
     <t>1213459189153340</t>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46252.25019825231</v>
+        <v>46253.19238331019</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>276</v>
@@ -6079,13 +6079,13 @@
       <c r="T77" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U77" s="12" t="s">
-        <v>278</v>
+      <c r="U77" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B78" s="5">
         <v>46079.83530333333</v>
@@ -6095,7 +6095,7 @@
         <v>46090.67667782407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6119,7 +6119,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6132,26 +6132,26 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B79" s="8">
         <v>46079.83530363426</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.805033425924</v>
+        <v>46253.19261353009</v>
       </c>
       <c r="E79" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="F79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G79" s="9" t="s">
+      <c r="H79" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I79" s="8">
         <v>46253</v>
@@ -6169,13 +6169,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O79" s="9" t="s">
         <v>276</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q79" s="8">
         <v>46252</v>
@@ -6189,8 +6189,8 @@
       <c r="T79" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U79" s="10" t="s">
-        <v>117</v>
+      <c r="U79" s="12" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46114.51489402778</v>
+        <v>46253.192614178246</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>287</v>
@@ -6211,10 +6211,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6232,13 +6232,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>288</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q80" s="5">
         <v>46252</v>
@@ -6252,8 +6252,8 @@
       <c r="T80" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U80" s="10" t="s">
-        <v>117</v>
+      <c r="U80" s="12" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001518 - EQ CHAPARRAL B.xlsx
+++ b/data/50001518 - EQ CHAPARRAL B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="288">
   <si>
     <t>50001518 - EQ. CHAPARRAL</t>
   </si>
@@ -876,9 +876,6 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213459189153340</t>
@@ -6139,7 +6136,7 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46253.19261353009</v>
+        <v>46261.205664016205</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>282</v>
@@ -6189,23 +6186,23 @@
       <c r="T79" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U79" s="12" t="s">
-        <v>285</v>
+      <c r="U79" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B80" s="5">
         <v>46079.83530395833</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46253.192614178246</v>
+        <v>46261.20566402777</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6235,7 +6232,7 @@
         <v>279</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>279</v>
@@ -6252,8 +6249,8 @@
       <c r="T80" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="U80" s="12" t="s">
-        <v>285</v>
+      <c r="U80" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
